--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="32">
   <si>
     <t>奖池ID</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>奖池系数</t>
+  </si>
+  <si>
+    <t>间隔时间</t>
   </si>
   <si>
     <t>int</t>
@@ -171,6 +174,9 @@
   </si>
   <si>
     <t>poolProp</t>
+  </si>
+  <si>
+    <t>min</t>
   </si>
   <si>
     <t>mini</t>
@@ -395,12 +401,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -412,7 +412,24 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -420,17 +437,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -937,7 +943,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -979,7 +985,6 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1356,51 +1361,60 @@
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" t="s">
-        <v>7</v>
-      </c>
       <c r="H2" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="I2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:9">
@@ -1408,7 +1422,7 @@
         <v>100100101</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" s="10">
         <v>10</v>
@@ -1420,13 +1434,16 @@
         <v>0</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G5" s="9">
         <v>1700</v>
       </c>
       <c r="H5" s="9">
         <v>15</v>
+      </c>
+      <c r="I5" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:9">
@@ -1434,7 +1451,7 @@
         <v>100100102</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="10">
         <v>20</v>
@@ -1446,13 +1463,16 @@
         <v>0</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6" s="9">
         <v>1700</v>
       </c>
       <c r="H6" s="9">
         <v>25</v>
+      </c>
+      <c r="I6" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
@@ -1460,7 +1480,7 @@
         <v>100100103</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="10">
         <v>50</v>
@@ -1472,13 +1492,16 @@
         <v>0</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G7" s="9">
         <v>1700</v>
       </c>
       <c r="H7" s="9">
         <v>60</v>
+      </c>
+      <c r="I7" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
@@ -1486,7 +1509,7 @@
         <v>100100104</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="10">
         <v>250</v>
@@ -1498,13 +1521,16 @@
         <v>0</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G8" s="9">
         <v>1700</v>
       </c>
       <c r="H8" s="9">
         <v>300</v>
+      </c>
+      <c r="I8" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:9">
@@ -1512,7 +1538,7 @@
         <v>100300101</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" s="14">
         <v>10</v>
@@ -1524,13 +1550,16 @@
         <v>0</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G9" s="13">
         <v>0</v>
       </c>
       <c r="H9" s="13">
         <v>15</v>
+      </c>
+      <c r="I9" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:9">
@@ -1538,7 +1567,7 @@
         <v>100300102</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" s="14">
         <v>20</v>
@@ -1550,13 +1579,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G10" s="13">
         <v>0</v>
       </c>
       <c r="H10" s="13">
         <v>25</v>
+      </c>
+      <c r="I10" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:9">
@@ -1564,7 +1596,7 @@
         <v>100300103</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C11" s="14">
         <v>50</v>
@@ -1576,13 +1608,16 @@
         <v>0</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G11" s="13">
         <v>0</v>
       </c>
       <c r="H11" s="13">
         <v>60</v>
+      </c>
+      <c r="I11" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
@@ -1590,7 +1625,7 @@
         <v>100300104</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C12" s="14">
         <v>250</v>
@@ -1602,13 +1637,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G12" s="13">
         <v>0</v>
       </c>
       <c r="H12" s="13">
         <v>300</v>
+      </c>
+      <c r="I12" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
@@ -1616,7 +1654,7 @@
         <v>101200101</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
@@ -1628,7 +1666,7 @@
         <v>1000</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G13" s="9">
         <v>0</v>
@@ -1636,14 +1674,16 @@
       <c r="H13" s="9">
         <v>1</v>
       </c>
-      <c r="I13" s="17"/>
+      <c r="I13" s="9">
+        <v>1440</v>
+      </c>
     </row>
     <row r="14" ht="16.5" spans="1:9">
       <c r="A14" s="9">
         <v>101400101</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C14" s="10">
         <v>0</v>
@@ -1655,7 +1695,7 @@
         <v>1000</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G14" s="9">
         <v>0</v>
@@ -1663,14 +1703,16 @@
       <c r="H14" s="9">
         <v>1</v>
       </c>
-      <c r="I14" s="17"/>
+      <c r="I14" s="9">
+        <v>1440</v>
+      </c>
     </row>
     <row r="15" ht="16.5" spans="1:9">
       <c r="A15" s="9">
         <v>102400101</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C15" s="10">
         <v>10</v>
@@ -1682,13 +1724,16 @@
         <v>0</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G15" s="9">
         <v>1700</v>
       </c>
       <c r="H15" s="9">
         <v>15</v>
+      </c>
+      <c r="I15" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
@@ -1696,7 +1741,7 @@
         <v>102400102</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C16" s="10">
         <v>20</v>
@@ -1708,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G16" s="9">
         <v>1700</v>
@@ -1716,13 +1761,16 @@
       <c r="H16" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:8">
+      <c r="I16" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:9">
       <c r="A17" s="9">
         <v>102400103</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C17" s="10">
         <v>50</v>
@@ -1734,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G17" s="9">
         <v>1700</v>
@@ -1742,13 +1790,16 @@
       <c r="H17" s="9">
         <v>60</v>
       </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:8">
+      <c r="I17" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:9">
       <c r="A18" s="9">
         <v>102400104</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C18" s="10">
         <v>250</v>
@@ -1760,7 +1811,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G18" s="9">
         <v>1700</v>
@@ -1768,13 +1819,16 @@
       <c r="H18" s="9">
         <v>300</v>
       </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:8">
+      <c r="I18" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:9">
       <c r="A19" s="9">
         <v>101700101</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C19" s="10">
         <v>10</v>
@@ -1786,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G19" s="9">
         <v>1700</v>
@@ -1794,13 +1848,16 @@
       <c r="H19" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:8">
+      <c r="I19" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:9">
       <c r="A20" s="9">
         <v>101700102</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C20" s="10">
         <v>20</v>
@@ -1812,7 +1869,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G20" s="9">
         <v>1700</v>
@@ -1820,13 +1877,16 @@
       <c r="H20" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:8">
+      <c r="I20" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:9">
       <c r="A21" s="9">
         <v>101700103</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C21" s="10">
         <v>50</v>
@@ -1838,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G21" s="9">
         <v>1700</v>
@@ -1846,13 +1906,16 @@
       <c r="H21" s="9">
         <v>60</v>
       </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:8">
+      <c r="I21" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:9">
       <c r="A22" s="9">
         <v>101700104</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C22" s="10">
         <v>250</v>
@@ -1864,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G22" s="9">
         <v>1700</v>
@@ -1872,13 +1935,16 @@
       <c r="H22" s="9">
         <v>300</v>
       </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:8">
+      <c r="I22" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:9">
       <c r="A23" s="9">
         <v>102200101</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C23" s="10">
         <v>10</v>
@@ -1890,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G23" s="9">
         <v>1700</v>
@@ -1898,13 +1964,16 @@
       <c r="H23" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:8">
+      <c r="I23" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:9">
       <c r="A24" s="9">
         <v>102200102</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C24" s="10">
         <v>20</v>
@@ -1916,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G24" s="9">
         <v>1700</v>
@@ -1924,13 +1993,16 @@
       <c r="H24" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:8">
+      <c r="I24" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:9">
       <c r="A25" s="9">
         <v>102200103</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C25" s="10">
         <v>50</v>
@@ -1942,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G25" s="9">
         <v>1700</v>
@@ -1950,13 +2022,16 @@
       <c r="H25" s="9">
         <v>60</v>
       </c>
-    </row>
-    <row r="26" ht="16.5" spans="1:8">
+      <c r="I25" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:9">
       <c r="A26" s="9">
         <v>102200104</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C26" s="10">
         <v>250</v>
@@ -1968,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G26" s="9">
         <v>1700</v>
@@ -1976,13 +2051,16 @@
       <c r="H26" s="9">
         <v>300</v>
       </c>
-    </row>
-    <row r="27" ht="16.5" spans="1:8">
+      <c r="I26" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" spans="1:9">
       <c r="A27" s="9">
         <v>102100101</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C27" s="10">
         <v>10</v>
@@ -1994,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G27" s="9">
         <v>1700</v>
@@ -2002,13 +2080,16 @@
       <c r="H27" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="28" ht="16.5" spans="1:8">
+      <c r="I27" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="1:9">
       <c r="A28" s="9">
         <v>102100102</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C28" s="10">
         <v>20</v>
@@ -2020,7 +2101,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G28" s="9">
         <v>1700</v>
@@ -2028,13 +2109,16 @@
       <c r="H28" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="29" ht="16.5" spans="1:8">
+      <c r="I28" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" spans="1:9">
       <c r="A29" s="9">
         <v>102100103</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C29" s="10">
         <v>50</v>
@@ -2046,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G29" s="9">
         <v>1700</v>
@@ -2054,13 +2138,16 @@
       <c r="H29" s="9">
         <v>60</v>
       </c>
-    </row>
-    <row r="30" ht="16.5" spans="1:8">
+      <c r="I29" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" spans="1:9">
       <c r="A30" s="9">
         <v>102100104</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C30" s="10">
         <v>250</v>
@@ -2072,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G30" s="9">
         <v>1700</v>
@@ -2080,13 +2167,16 @@
       <c r="H30" s="9">
         <v>300</v>
       </c>
-    </row>
-    <row r="31" ht="16.5" spans="1:8">
+      <c r="I30" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" spans="1:9">
       <c r="A31" s="9">
         <v>101800101</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C31" s="10">
         <v>10</v>
@@ -2098,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G31" s="9">
         <v>1700</v>
@@ -2106,13 +2196,16 @@
       <c r="H31" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="32" ht="16.5" spans="1:8">
+      <c r="I31" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" spans="1:9">
       <c r="A32" s="9">
         <v>101800102</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C32" s="10">
         <v>20</v>
@@ -2124,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G32" s="9">
         <v>1700</v>
@@ -2132,13 +2225,16 @@
       <c r="H32" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="33" ht="16.5" spans="1:8">
+      <c r="I32" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" spans="1:9">
       <c r="A33" s="9">
         <v>101800103</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C33" s="10">
         <v>50</v>
@@ -2150,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G33" s="9">
         <v>1700</v>
@@ -2158,13 +2254,16 @@
       <c r="H33" s="9">
         <v>60</v>
       </c>
-    </row>
-    <row r="34" ht="16.5" spans="1:8">
+      <c r="I33" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" spans="1:9">
       <c r="A34" s="9">
         <v>101800104</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C34" s="10">
         <v>250</v>
@@ -2176,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G34" s="9">
         <v>1700</v>
@@ -2184,13 +2283,16 @@
       <c r="H34" s="9">
         <v>300</v>
       </c>
-    </row>
-    <row r="35" ht="16.5" spans="1:8">
+      <c r="I34" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" spans="1:9">
       <c r="A35" s="9">
         <v>102500101</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C35" s="10">
         <v>10</v>
@@ -2202,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G35" s="9">
         <v>1700</v>
@@ -2210,13 +2312,16 @@
       <c r="H35" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="36" ht="16.5" spans="1:8">
+      <c r="I35" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" spans="1:9">
       <c r="A36" s="9">
         <v>102500102</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C36" s="10">
         <v>20</v>
@@ -2228,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G36" s="9">
         <v>1700</v>
@@ -2236,13 +2341,16 @@
       <c r="H36" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="37" ht="16.5" spans="1:8">
+      <c r="I36" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" spans="1:9">
       <c r="A37" s="9">
         <v>102500103</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C37" s="10">
         <v>50</v>
@@ -2254,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G37" s="9">
         <v>1700</v>
@@ -2262,13 +2370,16 @@
       <c r="H37" s="9">
         <v>60</v>
       </c>
-    </row>
-    <row r="38" ht="16.5" spans="1:8">
+      <c r="I37" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" spans="1:9">
       <c r="A38" s="9">
         <v>102500104</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C38" s="10">
         <v>250</v>
@@ -2280,7 +2391,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G38" s="9">
         <v>1700</v>
@@ -2288,13 +2399,16 @@
       <c r="H38" s="9">
         <v>300</v>
       </c>
-    </row>
-    <row r="39" ht="16.5" spans="1:8">
+      <c r="I38" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" spans="1:9">
       <c r="A39" s="9">
         <v>102300101</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C39" s="10">
         <v>10</v>
@@ -2306,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G39" s="9">
         <v>1700</v>
@@ -2314,13 +2428,16 @@
       <c r="H39" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="40" ht="16.5" spans="1:8">
+      <c r="I39" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="40" ht="16.5" spans="1:9">
       <c r="A40" s="9">
         <v>102300102</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C40" s="10">
         <v>20</v>
@@ -2332,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G40" s="9">
         <v>1700</v>
@@ -2340,13 +2457,16 @@
       <c r="H40" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="41" ht="16.5" spans="1:8">
+      <c r="I40" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" spans="1:9">
       <c r="A41" s="9">
         <v>102300103</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C41" s="10">
         <v>50</v>
@@ -2358,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G41" s="9">
         <v>1700</v>
@@ -2366,13 +2486,16 @@
       <c r="H41" s="9">
         <v>60</v>
       </c>
-    </row>
-    <row r="42" ht="16.5" spans="1:8">
+      <c r="I41" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" spans="1:9">
       <c r="A42" s="9">
         <v>102300104</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C42" s="10">
         <v>250</v>
@@ -2384,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G42" s="9">
         <v>1700</v>
@@ -2392,13 +2515,16 @@
       <c r="H42" s="9">
         <v>300</v>
       </c>
-    </row>
-    <row r="43" ht="16.5" spans="1:8">
+      <c r="I42" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" spans="1:9">
       <c r="A43" s="9">
         <v>103400101</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C43" s="10">
         <v>0</v>
@@ -2410,7 +2536,7 @@
         <v>1000</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G43" s="9">
         <v>0</v>
@@ -2418,13 +2544,16 @@
       <c r="H43" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" ht="16.5" spans="1:8">
+      <c r="I43" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:9">
       <c r="A44" s="9">
         <v>103401101</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C44" s="10">
         <v>0</v>
@@ -2436,7 +2565,7 @@
         <v>1000</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G44" s="9">
         <v>0</v>
@@ -2444,13 +2573,16 @@
       <c r="H44" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" ht="16.5" spans="1:8">
+      <c r="I44" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="1:9">
       <c r="A45" s="9">
         <v>103500101</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C45" s="10">
         <v>10</v>
@@ -2462,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G45" s="9">
         <v>1700</v>
@@ -2470,13 +2602,16 @@
       <c r="H45" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="46" ht="16.5" spans="1:8">
+      <c r="I45" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:9">
       <c r="A46" s="9">
         <v>103500102</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C46" s="10">
         <v>20</v>
@@ -2488,7 +2623,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G46" s="9">
         <v>1700</v>
@@ -2496,13 +2631,16 @@
       <c r="H46" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="47" ht="16.5" spans="1:8">
+      <c r="I46" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="1:9">
       <c r="A47" s="9">
         <v>103500103</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C47" s="10">
         <v>50</v>
@@ -2514,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G47" s="9">
         <v>1700</v>
@@ -2522,13 +2660,16 @@
       <c r="H47" s="9">
         <v>60</v>
       </c>
-    </row>
-    <row r="48" ht="16.5" spans="1:8">
+      <c r="I47" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:9">
       <c r="A48" s="9">
         <v>103500104</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C48" s="10">
         <v>250</v>
@@ -2540,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G48" s="9">
         <v>1700</v>
@@ -2548,13 +2689,16 @@
       <c r="H48" s="9">
         <v>300</v>
       </c>
-    </row>
-    <row r="49" ht="16.5" spans="1:8">
+      <c r="I48" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="1:9">
       <c r="A49" s="9">
         <v>103501101</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C49" s="10">
         <v>10</v>
@@ -2566,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G49" s="9">
         <v>1700</v>
@@ -2574,13 +2718,16 @@
       <c r="H49" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="50" ht="16.5" spans="1:8">
+      <c r="I49" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="1:9">
       <c r="A50" s="9">
         <v>103501102</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C50" s="10">
         <v>20</v>
@@ -2592,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G50" s="9">
         <v>1700</v>
@@ -2600,13 +2747,16 @@
       <c r="H50" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="51" ht="16.5" spans="1:8">
+      <c r="I50" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="1:9">
       <c r="A51" s="9">
         <v>103501103</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C51" s="10">
         <v>50</v>
@@ -2618,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G51" s="9">
         <v>1700</v>
@@ -2626,13 +2776,16 @@
       <c r="H51" s="9">
         <v>60</v>
       </c>
-    </row>
-    <row r="52" ht="16.5" spans="1:8">
+      <c r="I51" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" spans="1:9">
       <c r="A52" s="9">
         <v>103501104</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C52" s="10">
         <v>250</v>
@@ -2644,7 +2797,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G52" s="9">
         <v>1700</v>
@@ -2652,13 +2805,16 @@
       <c r="H52" s="9">
         <v>300</v>
       </c>
-    </row>
-    <row r="53" ht="16.5" spans="1:8">
+      <c r="I52" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" spans="1:9">
       <c r="A53" s="9">
         <v>103600101</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C53" s="10">
         <v>0</v>
@@ -2670,7 +2826,7 @@
         <v>1000</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G53" s="9">
         <v>0</v>
@@ -2678,13 +2834,16 @@
       <c r="H53" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" ht="16.5" spans="1:8">
+      <c r="I53" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="1:9">
       <c r="A54" s="9">
         <v>102800101</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C54" s="10">
         <v>10</v>
@@ -2696,7 +2855,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G54" s="9">
         <v>1700</v>
@@ -2704,13 +2863,16 @@
       <c r="H54" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="55" ht="16.5" spans="1:8">
+      <c r="I54" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" spans="1:9">
       <c r="A55" s="9">
         <v>102800102</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C55" s="10">
         <v>20</v>
@@ -2722,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G55" s="9">
         <v>1700</v>
@@ -2730,13 +2892,16 @@
       <c r="H55" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="56" ht="16.5" spans="1:8">
+      <c r="I55" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" spans="1:9">
       <c r="A56" s="9">
         <v>102800103</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C56" s="10">
         <v>50</v>
@@ -2748,7 +2913,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G56" s="9">
         <v>1700</v>
@@ -2756,13 +2921,16 @@
       <c r="H56" s="9">
         <v>60</v>
       </c>
-    </row>
-    <row r="57" ht="16.5" spans="1:8">
+      <c r="I56" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" spans="1:9">
       <c r="A57" s="9">
         <v>102800104</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C57" s="10">
         <v>250</v>
@@ -2774,7 +2942,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G57" s="9">
         <v>1700</v>
@@ -2782,13 +2950,16 @@
       <c r="H57" s="9">
         <v>300</v>
       </c>
-    </row>
-    <row r="58" ht="16.5" spans="1:8">
+      <c r="I57" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" spans="1:9">
       <c r="A58" s="9">
         <v>102000101</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C58" s="10">
         <v>10</v>
@@ -2800,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G58" s="9">
         <v>1700</v>
@@ -2808,13 +2979,16 @@
       <c r="H58" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="59" ht="16.5" spans="1:8">
+      <c r="I58" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="59" ht="16.5" spans="1:9">
       <c r="A59" s="9">
         <v>102000102</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C59" s="10">
         <v>20</v>
@@ -2826,7 +3000,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G59" s="9">
         <v>1700</v>
@@ -2834,13 +3008,16 @@
       <c r="H59" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="60" ht="16.5" spans="1:8">
+      <c r="I59" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="60" ht="16.5" spans="1:9">
       <c r="A60" s="9">
         <v>102000103</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C60" s="10">
         <v>50</v>
@@ -2852,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G60" s="9">
         <v>1700</v>
@@ -2860,13 +3037,16 @@
       <c r="H60" s="9">
         <v>60</v>
       </c>
-    </row>
-    <row r="61" ht="16.5" spans="1:8">
+      <c r="I60" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="61" ht="16.5" spans="1:9">
       <c r="A61" s="9">
         <v>102000104</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C61" s="10">
         <v>250</v>
@@ -2878,7 +3058,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G61" s="9">
         <v>1700</v>
@@ -2886,13 +3066,16 @@
       <c r="H61" s="9">
         <v>300</v>
       </c>
-    </row>
-    <row r="62" ht="16.5" spans="1:8">
+      <c r="I61" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="62" ht="16.5" spans="1:9">
       <c r="A62" s="9">
         <v>103800101</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C62" s="10">
         <v>10</v>
@@ -2904,7 +3087,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G62" s="9">
         <v>1700</v>
@@ -2912,13 +3095,16 @@
       <c r="H62" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="63" ht="16.5" spans="1:8">
+      <c r="I62" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" spans="1:9">
       <c r="A63" s="9">
         <v>103800102</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C63" s="10">
         <v>20</v>
@@ -2930,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G63" s="9">
         <v>1700</v>
@@ -2938,13 +3124,16 @@
       <c r="H63" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="64" ht="16.5" spans="1:8">
+      <c r="I63" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="64" ht="16.5" spans="1:9">
       <c r="A64" s="9">
         <v>103800103</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C64" s="10">
         <v>50</v>
@@ -2956,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G64" s="9">
         <v>1700</v>
@@ -2964,13 +3153,16 @@
       <c r="H64" s="9">
         <v>60</v>
       </c>
-    </row>
-    <row r="65" ht="16.5" spans="1:8">
+      <c r="I64" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="65" ht="16.5" spans="1:9">
       <c r="A65" s="9">
         <v>103800104</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C65" s="10">
         <v>250</v>
@@ -2982,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G65" s="9">
         <v>1700</v>
@@ -2990,13 +3182,16 @@
       <c r="H65" s="9">
         <v>300</v>
       </c>
-    </row>
-    <row r="66" ht="16.5" spans="1:8">
+      <c r="I65" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="66" ht="16.5" spans="1:9">
       <c r="A66" s="9">
         <v>102700101</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C66" s="10">
         <v>10</v>
@@ -3008,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G66" s="9">
         <v>1700</v>
@@ -3016,13 +3211,16 @@
       <c r="H66" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="67" ht="16.5" spans="1:8">
+      <c r="I66" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="67" ht="16.5" spans="1:9">
       <c r="A67" s="9">
         <v>102700102</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C67" s="10">
         <v>20</v>
@@ -3034,7 +3232,7 @@
         <v>0</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G67" s="9">
         <v>1700</v>
@@ -3042,13 +3240,16 @@
       <c r="H67" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="68" ht="16.5" spans="1:8">
+      <c r="I67" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="68" ht="16.5" spans="1:9">
       <c r="A68" s="9">
         <v>102700103</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C68" s="10">
         <v>50</v>
@@ -3060,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G68" s="9">
         <v>1700</v>
@@ -3068,13 +3269,16 @@
       <c r="H68" s="9">
         <v>60</v>
       </c>
-    </row>
-    <row r="69" ht="16.5" spans="1:8">
+      <c r="I68" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="69" ht="16.5" spans="1:9">
       <c r="A69" s="9">
         <v>102700104</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C69" s="10">
         <v>250</v>
@@ -3086,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G69" s="9">
         <v>1700</v>
@@ -3094,13 +3298,16 @@
       <c r="H69" s="9">
         <v>300</v>
       </c>
-    </row>
-    <row r="70" ht="16.5" spans="1:8">
+      <c r="I69" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="70" ht="16.5" spans="1:9">
       <c r="A70" s="9">
         <v>103700101</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C70" s="10">
         <v>0</v>
@@ -3112,7 +3319,7 @@
         <v>1000</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G70" s="9">
         <v>0</v>
@@ -3120,13 +3327,16 @@
       <c r="H70" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" ht="16.5" spans="1:8">
+      <c r="I70" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="71" ht="16.5" spans="1:9">
       <c r="A71" s="9">
         <v>103100101</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C71" s="10">
         <v>10</v>
@@ -3138,7 +3348,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G71" s="9">
         <v>1700</v>
@@ -3146,13 +3356,16 @@
       <c r="H71" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="72" ht="16.5" spans="1:8">
+      <c r="I71" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="72" ht="16.5" spans="1:9">
       <c r="A72" s="9">
         <v>103100102</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C72" s="10">
         <v>20</v>
@@ -3164,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G72" s="9">
         <v>1700</v>
@@ -3172,13 +3385,16 @@
       <c r="H72" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="73" ht="16.5" spans="1:8">
+      <c r="I72" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="73" ht="16.5" spans="1:9">
       <c r="A73" s="9">
         <v>103100103</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C73" s="10">
         <v>50</v>
@@ -3190,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G73" s="9">
         <v>1700</v>
@@ -3198,13 +3414,16 @@
       <c r="H73" s="9">
         <v>60</v>
       </c>
-    </row>
-    <row r="74" ht="16.5" spans="1:8">
+      <c r="I73" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="74" ht="16.5" spans="1:9">
       <c r="A74" s="9">
         <v>103100104</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C74" s="10">
         <v>250</v>
@@ -3216,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="F74" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G74" s="9">
         <v>1700</v>
@@ -3224,13 +3443,16 @@
       <c r="H74" s="9">
         <v>300</v>
       </c>
-    </row>
-    <row r="75" ht="16.5" spans="1:8">
+      <c r="I74" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="75" ht="16.5" spans="1:9">
       <c r="A75" s="9">
         <v>104000101</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C75" s="10">
         <v>10</v>
@@ -3242,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="F75" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G75" s="9">
         <v>1700</v>
@@ -3250,13 +3472,16 @@
       <c r="H75" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="76" ht="16.5" spans="1:8">
+      <c r="I75" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="76" ht="16.5" spans="1:9">
       <c r="A76" s="9">
         <v>104000102</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C76" s="10">
         <v>20</v>
@@ -3268,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="F76" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G76" s="9">
         <v>1700</v>
@@ -3276,13 +3501,16 @@
       <c r="H76" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="77" ht="16.5" spans="1:8">
+      <c r="I76" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="77" ht="16.5" spans="1:9">
       <c r="A77" s="9">
         <v>104000103</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C77" s="10">
         <v>50</v>
@@ -3294,7 +3522,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G77" s="9">
         <v>1700</v>
@@ -3302,13 +3530,16 @@
       <c r="H77" s="9">
         <v>60</v>
       </c>
-    </row>
-    <row r="78" ht="16.5" spans="1:8">
+      <c r="I77" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="78" ht="16.5" spans="1:9">
       <c r="A78" s="9">
         <v>104000104</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C78" s="10">
         <v>250</v>
@@ -3320,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="F78" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G78" s="9">
         <v>1700</v>
@@ -3328,13 +3559,16 @@
       <c r="H78" s="9">
         <v>300</v>
       </c>
-    </row>
-    <row r="79" ht="16.5" spans="1:8">
+      <c r="I78" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="79" ht="16.5" spans="1:9">
       <c r="A79" s="9">
         <v>103900101</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C79" s="10">
         <v>10</v>
@@ -3346,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G79" s="9">
         <v>1700</v>
@@ -3354,13 +3588,16 @@
       <c r="H79" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="80" ht="16.5" spans="1:8">
+      <c r="I79" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="80" ht="16.5" spans="1:9">
       <c r="A80" s="9">
         <v>103900102</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C80" s="10">
         <v>20</v>
@@ -3372,13 +3609,16 @@
         <v>0</v>
       </c>
       <c r="F80" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G80" s="9">
         <v>1700</v>
       </c>
       <c r="H80" s="9">
         <v>25</v>
+      </c>
+      <c r="I80" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="81" ht="16.5" spans="1:9">
@@ -3386,7 +3626,7 @@
         <v>103900103</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C81" s="10">
         <v>50</v>
@@ -3398,13 +3638,16 @@
         <v>0</v>
       </c>
       <c r="F81" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G81" s="9">
         <v>1700</v>
       </c>
       <c r="H81" s="9">
         <v>60</v>
+      </c>
+      <c r="I81" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:9">
@@ -3412,7 +3655,7 @@
         <v>103900104</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C82" s="10">
         <v>250</v>
@@ -3424,13 +3667,16 @@
         <v>0</v>
       </c>
       <c r="F82" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G82" s="9">
         <v>1700</v>
       </c>
       <c r="H82" s="9">
         <v>300</v>
+      </c>
+      <c r="I82" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:9">
@@ -3438,7 +3684,7 @@
         <v>101600101</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C83" s="10">
         <v>10</v>
@@ -3450,13 +3696,16 @@
         <v>0</v>
       </c>
       <c r="F83" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G83" s="9">
         <v>1700</v>
       </c>
       <c r="H83" s="9">
         <v>15</v>
+      </c>
+      <c r="I83" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="84" ht="16.5" spans="1:9">
@@ -3464,7 +3713,7 @@
         <v>101600102</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C84" s="10">
         <v>20</v>
@@ -3476,13 +3725,16 @@
         <v>0</v>
       </c>
       <c r="F84" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G84" s="9">
         <v>1700</v>
       </c>
       <c r="H84" s="9">
         <v>25</v>
+      </c>
+      <c r="I84" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="85" ht="16.5" spans="1:9">
@@ -3490,7 +3742,7 @@
         <v>101600103</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C85" s="10">
         <v>50</v>
@@ -3502,13 +3754,16 @@
         <v>0</v>
       </c>
       <c r="F85" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G85" s="9">
         <v>1700</v>
       </c>
       <c r="H85" s="9">
         <v>60</v>
+      </c>
+      <c r="I85" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="86" ht="16.5" spans="1:9">
@@ -3516,7 +3771,7 @@
         <v>101600104</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C86" s="10">
         <v>250</v>
@@ -3528,13 +3783,16 @@
         <v>0</v>
       </c>
       <c r="F86" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G86" s="9">
         <v>1700</v>
       </c>
       <c r="H86" s="9">
         <v>300</v>
+      </c>
+      <c r="I86" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="87" ht="16.5" spans="1:9">
@@ -3542,7 +3800,7 @@
         <v>101500101</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C87" s="10">
         <v>10</v>
@@ -3554,13 +3812,16 @@
         <v>0</v>
       </c>
       <c r="F87" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G87" s="9">
         <v>1700</v>
       </c>
       <c r="H87" s="9">
         <v>15</v>
+      </c>
+      <c r="I87" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="88" ht="16.5" spans="1:9">
@@ -3568,7 +3829,7 @@
         <v>101500102</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C88" s="10">
         <v>20</v>
@@ -3580,13 +3841,16 @@
         <v>0</v>
       </c>
       <c r="F88" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G88" s="9">
         <v>1700</v>
       </c>
       <c r="H88" s="9">
         <v>25</v>
+      </c>
+      <c r="I88" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="89" ht="16.5" spans="1:9">
@@ -3594,7 +3858,7 @@
         <v>101500103</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C89" s="10">
         <v>50</v>
@@ -3606,13 +3870,16 @@
         <v>0</v>
       </c>
       <c r="F89" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G89" s="9">
         <v>1700</v>
       </c>
       <c r="H89" s="9">
         <v>60</v>
+      </c>
+      <c r="I89" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:9">
@@ -3620,7 +3887,7 @@
         <v>101500104</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C90" s="10">
         <v>250</v>
@@ -3632,13 +3899,16 @@
         <v>0</v>
       </c>
       <c r="F90" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G90" s="9">
         <v>1700</v>
       </c>
       <c r="H90" s="9">
         <v>300</v>
+      </c>
+      <c r="I90" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:9">
@@ -3646,7 +3916,7 @@
         <v>102600101</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C91" s="10">
         <v>10</v>
@@ -3658,13 +3928,16 @@
         <v>0</v>
       </c>
       <c r="F91" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G91" s="9">
         <v>1700</v>
       </c>
       <c r="H91" s="9">
         <v>15</v>
+      </c>
+      <c r="I91" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:9">
@@ -3672,7 +3945,7 @@
         <v>102600102</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C92" s="10">
         <v>20</v>
@@ -3684,13 +3957,16 @@
         <v>0</v>
       </c>
       <c r="F92" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G92" s="9">
         <v>1700</v>
       </c>
       <c r="H92" s="9">
         <v>25</v>
+      </c>
+      <c r="I92" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:9">
@@ -3698,7 +3974,7 @@
         <v>102600103</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C93" s="10">
         <v>50</v>
@@ -3710,13 +3986,16 @@
         <v>0</v>
       </c>
       <c r="F93" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G93" s="9">
         <v>1700</v>
       </c>
       <c r="H93" s="9">
         <v>60</v>
+      </c>
+      <c r="I93" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:9">
@@ -3724,7 +4003,7 @@
         <v>102600104</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C94" s="10">
         <v>250</v>
@@ -3736,13 +4015,16 @@
         <v>0</v>
       </c>
       <c r="F94" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G94" s="9">
         <v>1700</v>
       </c>
       <c r="H94" s="9">
         <v>300</v>
+      </c>
+      <c r="I94" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="95" customFormat="1" ht="16.5" spans="1:9">
@@ -3750,7 +4032,7 @@
         <v>105000101</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C95" s="10">
         <v>10</v>
@@ -3762,7 +4044,7 @@
         <v>0</v>
       </c>
       <c r="F95" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G95" s="9">
         <v>1700</v>
@@ -3770,14 +4052,16 @@
       <c r="H95" s="9">
         <v>15</v>
       </c>
-      <c r="I95" s="3"/>
+      <c r="I95" s="9">
+        <v>1440</v>
+      </c>
     </row>
     <row r="96" customFormat="1" ht="16.5" spans="1:9">
       <c r="A96" s="9">
         <v>105000102</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C96" s="10">
         <v>20</v>
@@ -3789,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="F96" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G96" s="9">
         <v>1700</v>
@@ -3797,14 +4081,16 @@
       <c r="H96" s="9">
         <v>25</v>
       </c>
-      <c r="I96" s="3"/>
+      <c r="I96" s="9">
+        <v>1440</v>
+      </c>
     </row>
     <row r="97" customFormat="1" ht="16.5" spans="1:9">
       <c r="A97" s="9">
         <v>105000103</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C97" s="10">
         <v>50</v>
@@ -3816,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="F97" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G97" s="9">
         <v>1700</v>
@@ -3824,14 +4110,16 @@
       <c r="H97" s="9">
         <v>60</v>
       </c>
-      <c r="I97" s="3"/>
+      <c r="I97" s="9">
+        <v>1440</v>
+      </c>
     </row>
     <row r="98" customFormat="1" ht="16.5" spans="1:9">
       <c r="A98" s="9">
         <v>105000104</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C98" s="10">
         <v>250</v>
@@ -3843,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="F98" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G98" s="9">
         <v>1700</v>
@@ -3851,14 +4139,16 @@
       <c r="H98" s="9">
         <v>300</v>
       </c>
-      <c r="I98" s="3"/>
+      <c r="I98" s="9">
+        <v>1440</v>
+      </c>
     </row>
     <row r="99" customFormat="1" ht="16.5" spans="1:9">
       <c r="A99" s="9">
         <v>105100101</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C99" s="10">
         <v>10</v>
@@ -3870,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G99" s="9">
         <v>1700</v>
@@ -3878,14 +4168,16 @@
       <c r="H99" s="9">
         <v>15</v>
       </c>
-      <c r="I99" s="3"/>
+      <c r="I99" s="9">
+        <v>1440</v>
+      </c>
     </row>
     <row r="100" customFormat="1" ht="16.5" spans="1:9">
       <c r="A100" s="9">
         <v>105100102</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C100" s="10">
         <v>20</v>
@@ -3897,7 +4189,7 @@
         <v>0</v>
       </c>
       <c r="F100" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G100" s="9">
         <v>1700</v>
@@ -3905,14 +4197,16 @@
       <c r="H100" s="9">
         <v>25</v>
       </c>
-      <c r="I100" s="3"/>
+      <c r="I100" s="9">
+        <v>1440</v>
+      </c>
     </row>
     <row r="101" customFormat="1" ht="16.5" spans="1:9">
       <c r="A101" s="9">
         <v>105100103</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C101" s="10">
         <v>50</v>
@@ -3924,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G101" s="9">
         <v>1700</v>
@@ -3932,14 +4226,16 @@
       <c r="H101" s="9">
         <v>60</v>
       </c>
-      <c r="I101" s="3"/>
+      <c r="I101" s="9">
+        <v>1440</v>
+      </c>
     </row>
     <row r="102" customFormat="1" ht="16.5" spans="1:9">
       <c r="A102" s="9">
         <v>105100104</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C102" s="10">
         <v>250</v>
@@ -3951,7 +4247,7 @@
         <v>0</v>
       </c>
       <c r="F102" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G102" s="9">
         <v>1700</v>
@@ -3959,14 +4255,16 @@
       <c r="H102" s="9">
         <v>300</v>
       </c>
-      <c r="I102" s="3"/>
+      <c r="I102" s="9">
+        <v>1440</v>
+      </c>
     </row>
     <row r="103" customFormat="1" ht="16.5" spans="1:9">
       <c r="A103" s="9">
         <v>105400101</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C103" s="10">
         <v>10</v>
@@ -3978,13 +4276,16 @@
         <v>0</v>
       </c>
       <c r="F103" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G103" s="9">
         <v>1700</v>
       </c>
       <c r="H103" s="9">
         <v>1500</v>
+      </c>
+      <c r="I103" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="104" customFormat="1" ht="16.5" spans="1:9">
@@ -3992,7 +4293,7 @@
         <v>105400102</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C104" s="10">
         <v>20</v>
@@ -4004,13 +4305,16 @@
         <v>0</v>
       </c>
       <c r="F104" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G104" s="9">
         <v>1700</v>
       </c>
       <c r="H104" s="9">
         <v>2500</v>
+      </c>
+      <c r="I104" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="105" customFormat="1" ht="16.5" spans="1:9">
@@ -4018,7 +4322,7 @@
         <v>105400103</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C105" s="10">
         <v>50</v>
@@ -4030,13 +4334,16 @@
         <v>0</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G105" s="9">
         <v>1700</v>
       </c>
       <c r="H105" s="9">
         <v>6000</v>
+      </c>
+      <c r="I105" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="106" customFormat="1" ht="16.5" spans="1:9">
@@ -4044,7 +4351,7 @@
         <v>105400104</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C106" s="10">
         <v>250</v>
@@ -4056,21 +4363,24 @@
         <v>0</v>
       </c>
       <c r="F106" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G106" s="9">
         <v>1700</v>
       </c>
       <c r="H106" s="9">
         <v>30000</v>
+      </c>
+      <c r="I106" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="107" customFormat="1" ht="16.5" spans="1:9">
       <c r="A107" s="9">
         <v>100800101</v>
       </c>
-      <c r="B107" s="18" t="s">
-        <v>16</v>
+      <c r="B107" s="17" t="s">
+        <v>18</v>
       </c>
       <c r="C107" s="10">
         <v>10</v>
@@ -4082,21 +4392,24 @@
         <v>0</v>
       </c>
       <c r="F107" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G107" s="9">
         <v>1700</v>
       </c>
       <c r="H107" s="9">
         <v>1500</v>
+      </c>
+      <c r="I107" s="9">
+        <v>1440</v>
       </c>
     </row>
     <row r="108" customFormat="1" ht="16.5" spans="1:9">
       <c r="A108" s="9">
         <v>100800102</v>
       </c>
-      <c r="B108" s="18" t="s">
-        <v>18</v>
+      <c r="B108" s="17" t="s">
+        <v>20</v>
       </c>
       <c r="C108" s="10">
         <v>20</v>
@@ -4108,7 +4421,7 @@
         <v>0</v>
       </c>
       <c r="F108" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G108" s="9">
         <v>1700</v>
@@ -4116,13 +4429,16 @@
       <c r="H108" s="9">
         <v>2500</v>
       </c>
+      <c r="I108" s="9">
+        <v>1440</v>
+      </c>
     </row>
     <row r="109" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A109" s="19">
+      <c r="A109" s="18">
         <v>100800103</v>
       </c>
-      <c r="B109" s="18" t="s">
-        <v>20</v>
+      <c r="B109" s="17" t="s">
+        <v>22</v>
       </c>
       <c r="C109" s="10">
         <v>50</v>
@@ -4134,7 +4450,7 @@
         <v>0</v>
       </c>
       <c r="F109" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G109" s="9">
         <v>1700</v>
@@ -4142,13 +4458,16 @@
       <c r="H109" s="9">
         <v>6000</v>
       </c>
+      <c r="I109" s="9">
+        <v>1440</v>
+      </c>
     </row>
     <row r="110" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A110" s="19">
+      <c r="A110" s="18">
         <v>100800104</v>
       </c>
-      <c r="B110" s="18" t="s">
-        <v>22</v>
+      <c r="B110" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="C110" s="10">
         <v>250</v>
@@ -4160,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="F110" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G110" s="9">
         <v>1700</v>
@@ -4168,13 +4487,16 @@
       <c r="H110" s="9">
         <v>30000</v>
       </c>
+      <c r="I110" s="9">
+        <v>1440</v>
+      </c>
     </row>
     <row r="111" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A111" s="19">
+      <c r="A111" s="18">
         <v>105700101</v>
       </c>
-      <c r="B111" s="18" t="s">
-        <v>16</v>
+      <c r="B111" s="17" t="s">
+        <v>18</v>
       </c>
       <c r="C111" s="10">
         <v>10</v>
@@ -4186,7 +4508,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G111" s="9">
         <v>1700</v>
@@ -4194,13 +4516,16 @@
       <c r="H111" s="9">
         <v>1500</v>
       </c>
+      <c r="I111" s="9">
+        <v>1440</v>
+      </c>
     </row>
     <row r="112" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A112" s="19">
+      <c r="A112" s="18">
         <v>105700102</v>
       </c>
-      <c r="B112" s="18" t="s">
-        <v>18</v>
+      <c r="B112" s="17" t="s">
+        <v>20</v>
       </c>
       <c r="C112" s="10">
         <v>20</v>
@@ -4212,7 +4537,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G112" s="9">
         <v>1700</v>
@@ -4220,13 +4545,16 @@
       <c r="H112" s="9">
         <v>2500</v>
       </c>
-    </row>
-    <row r="113" customFormat="1" ht="16.5" spans="1:8">
-      <c r="A113" s="19">
+      <c r="I112" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="113" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A113" s="18">
         <v>105700103</v>
       </c>
-      <c r="B113" s="18" t="s">
-        <v>20</v>
+      <c r="B113" s="17" t="s">
+        <v>22</v>
       </c>
       <c r="C113" s="10">
         <v>50</v>
@@ -4238,7 +4566,7 @@
         <v>0</v>
       </c>
       <c r="F113" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G113" s="9">
         <v>1700</v>
@@ -4246,13 +4574,16 @@
       <c r="H113" s="9">
         <v>6000</v>
       </c>
-    </row>
-    <row r="114" customFormat="1" ht="16.5" spans="1:8">
-      <c r="A114" s="19">
+      <c r="I113" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="114" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A114" s="18">
         <v>105700104</v>
       </c>
-      <c r="B114" s="18" t="s">
-        <v>22</v>
+      <c r="B114" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="C114" s="10">
         <v>250</v>
@@ -4264,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="F114" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G114" s="9">
         <v>1700</v>
@@ -4272,13 +4603,16 @@
       <c r="H114" s="9">
         <v>30000</v>
       </c>
-    </row>
-    <row r="115" s="1" customFormat="1" ht="16.5" spans="1:8">
-      <c r="A115" s="19">
+      <c r="I114" s="9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="115" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A115" s="18">
         <v>105800101</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C115" s="10">
         <v>0</v>
@@ -4290,13 +4624,16 @@
         <v>5000</v>
       </c>
       <c r="F115" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G115" s="9">
         <v>0</v>
       </c>
       <c r="H115" s="9">
         <v>50</v>
+      </c>
+      <c r="I115" s="9">
+        <v>1440</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="32">
   <si>
     <t>奖池ID</t>
   </si>
@@ -233,7 +233,7 @@
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,8 +249,23 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -399,22 +414,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -430,13 +439,19 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="宋体"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -811,185 +826,191 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="51">
@@ -1324,7 +1345,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I115"/>
+  <dimension ref="A1:I116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -1332,36 +1353,36 @@
     <col min="3" max="3" width="18.75" customWidth="1"/>
     <col min="4" max="4" width="20.75" customWidth="1"/>
     <col min="5" max="5" width="20.125" customWidth="1"/>
-    <col min="6" max="6" width="20.25" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.25" style="3" customWidth="1"/>
     <col min="7" max="7" width="18.875" customWidth="1"/>
     <col min="8" max="8" width="10.625" customWidth="1"/>
-    <col min="9" max="9" width="9" style="3"/>
+    <col min="9" max="9" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:9">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="5" t="s">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1378,7 +1399,7 @@
       <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
@@ -1404,3235 +1425,3264 @@
       <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>15</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:9">
-      <c r="A5" s="9">
+      <c r="A5" s="10">
         <v>100100101</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="11">
         <v>10</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="12">
         <v>15</v>
       </c>
-      <c r="E5" s="11">
-        <v>0</v>
-      </c>
-      <c r="F5" s="12" t="s">
+      <c r="E5" s="12">
+        <v>0</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H5" s="9">
+      <c r="G5" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H5" s="10">
         <v>15</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:9">
-      <c r="A6" s="9">
+      <c r="A6" s="10">
         <v>100100102</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="10">
-        <v>20</v>
-      </c>
-      <c r="D6" s="11">
-        <v>25</v>
-      </c>
-      <c r="E6" s="11">
-        <v>0</v>
-      </c>
-      <c r="F6" s="12" t="s">
+      <c r="B6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="11">
+        <v>20</v>
+      </c>
+      <c r="D6" s="12">
+        <v>25</v>
+      </c>
+      <c r="E6" s="12">
+        <v>0</v>
+      </c>
+      <c r="F6" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H6" s="9">
-        <v>25</v>
-      </c>
-      <c r="I6" s="9">
+      <c r="G6" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H6" s="10">
+        <v>25</v>
+      </c>
+      <c r="I6" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
-      <c r="A7" s="9">
+      <c r="A7" s="10">
         <v>100100103</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="11">
         <v>50</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="12">
         <v>60</v>
       </c>
-      <c r="E7" s="11">
-        <v>0</v>
-      </c>
-      <c r="F7" s="12" t="s">
+      <c r="E7" s="12">
+        <v>0</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H7" s="9">
+      <c r="G7" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H7" s="10">
         <v>60</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
-      <c r="A8" s="9">
+      <c r="A8" s="10">
         <v>100100104</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="11">
         <v>250</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="12">
         <v>300</v>
       </c>
-      <c r="E8" s="11">
-        <v>0</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H8" s="9">
+      <c r="E8" s="12">
+        <v>0</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H8" s="10">
         <v>300</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:9">
-      <c r="A9" s="13">
+      <c r="A9" s="14">
         <v>100300101</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="15">
         <v>10</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="16">
         <v>15</v>
       </c>
-      <c r="E9" s="15">
-        <v>0</v>
-      </c>
-      <c r="F9" s="16" t="s">
+      <c r="E9" s="16">
+        <v>0</v>
+      </c>
+      <c r="F9" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="13">
-        <v>0</v>
-      </c>
-      <c r="H9" s="13">
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
         <v>15</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:9">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <v>100300102</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="14">
-        <v>20</v>
-      </c>
-      <c r="D10" s="15">
-        <v>25</v>
-      </c>
-      <c r="E10" s="15">
-        <v>0</v>
-      </c>
-      <c r="F10" s="16" t="s">
+      <c r="B10" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="15">
+        <v>20</v>
+      </c>
+      <c r="D10" s="16">
+        <v>25</v>
+      </c>
+      <c r="E10" s="16">
+        <v>0</v>
+      </c>
+      <c r="F10" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="13">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13">
-        <v>25</v>
-      </c>
-      <c r="I10" s="9">
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>25</v>
+      </c>
+      <c r="I10" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:9">
-      <c r="A11" s="13">
+      <c r="A11" s="14">
         <v>100300103</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="15">
         <v>50</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="16">
         <v>60</v>
       </c>
-      <c r="E11" s="15">
-        <v>0</v>
-      </c>
-      <c r="F11" s="16" t="s">
+      <c r="E11" s="16">
+        <v>0</v>
+      </c>
+      <c r="F11" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="13">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13">
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
         <v>60</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <v>100300104</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="15">
         <v>250</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="16">
         <v>300</v>
       </c>
-      <c r="E12" s="15">
-        <v>0</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" s="13">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13">
+      <c r="E12" s="16">
+        <v>0</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
         <v>300</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
-      <c r="A13" s="9">
+      <c r="A13" s="10">
         <v>101200101</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="10">
-        <v>0</v>
-      </c>
-      <c r="D13" s="11">
-        <v>0</v>
-      </c>
-      <c r="E13" s="11">
+      <c r="C13" s="11">
+        <v>0</v>
+      </c>
+      <c r="D13" s="12">
+        <v>0</v>
+      </c>
+      <c r="E13" s="12">
         <v>1000</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G13" s="9">
-        <v>0</v>
-      </c>
-      <c r="H13" s="9">
+      <c r="G13" s="10">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10">
         <v>1</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:9">
-      <c r="A14" s="9">
+      <c r="A14" s="10">
         <v>101400101</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="10">
-        <v>0</v>
-      </c>
-      <c r="D14" s="11">
-        <v>0</v>
-      </c>
-      <c r="E14" s="11">
+      <c r="C14" s="11">
+        <v>0</v>
+      </c>
+      <c r="D14" s="12">
+        <v>0</v>
+      </c>
+      <c r="E14" s="12">
         <v>1000</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="9">
-        <v>0</v>
-      </c>
-      <c r="H14" s="9">
+      <c r="G14" s="10">
+        <v>0</v>
+      </c>
+      <c r="H14" s="10">
         <v>1</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:9">
-      <c r="A15" s="9">
+      <c r="A15" s="10">
         <v>102400101</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="11">
         <v>10</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="12">
         <v>15</v>
       </c>
-      <c r="E15" s="11">
-        <v>0</v>
-      </c>
-      <c r="F15" s="12" t="s">
+      <c r="E15" s="12">
+        <v>0</v>
+      </c>
+      <c r="F15" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G15" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H15" s="9">
+      <c r="G15" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H15" s="10">
         <v>15</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
-      <c r="A16" s="9">
+      <c r="A16" s="10">
         <v>102400102</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="10">
-        <v>20</v>
-      </c>
-      <c r="D16" s="11">
-        <v>25</v>
-      </c>
-      <c r="E16" s="11">
-        <v>0</v>
-      </c>
-      <c r="F16" s="12" t="s">
+      <c r="B16" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="11">
+        <v>20</v>
+      </c>
+      <c r="D16" s="12">
+        <v>25</v>
+      </c>
+      <c r="E16" s="12">
+        <v>0</v>
+      </c>
+      <c r="F16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G16" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H16" s="9">
-        <v>25</v>
-      </c>
-      <c r="I16" s="9">
+      <c r="G16" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H16" s="10">
+        <v>25</v>
+      </c>
+      <c r="I16" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
-      <c r="A17" s="9">
+      <c r="A17" s="10">
         <v>102400103</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="11">
         <v>50</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="12">
         <v>60</v>
       </c>
-      <c r="E17" s="11">
-        <v>0</v>
-      </c>
-      <c r="F17" s="12" t="s">
+      <c r="E17" s="12">
+        <v>0</v>
+      </c>
+      <c r="F17" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H17" s="9">
+      <c r="G17" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H17" s="10">
         <v>60</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
-      <c r="A18" s="9">
+      <c r="A18" s="10">
         <v>102400104</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="11">
         <v>250</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="12">
         <v>300</v>
       </c>
-      <c r="E18" s="11">
-        <v>0</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H18" s="9">
+      <c r="E18" s="12">
+        <v>0</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H18" s="10">
         <v>300</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
-      <c r="A19" s="9">
+      <c r="A19" s="10">
         <v>101700101</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="11">
         <v>10</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="12">
         <v>15</v>
       </c>
-      <c r="E19" s="11">
-        <v>0</v>
-      </c>
-      <c r="F19" s="12" t="s">
+      <c r="E19" s="12">
+        <v>0</v>
+      </c>
+      <c r="F19" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H19" s="9">
+      <c r="G19" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H19" s="10">
         <v>15</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
-      <c r="A20" s="9">
+      <c r="A20" s="10">
         <v>101700102</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="10">
-        <v>20</v>
-      </c>
-      <c r="D20" s="11">
-        <v>25</v>
-      </c>
-      <c r="E20" s="11">
-        <v>0</v>
-      </c>
-      <c r="F20" s="12" t="s">
+      <c r="B20" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="11">
+        <v>20</v>
+      </c>
+      <c r="D20" s="12">
+        <v>25</v>
+      </c>
+      <c r="E20" s="12">
+        <v>0</v>
+      </c>
+      <c r="F20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G20" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H20" s="9">
-        <v>25</v>
-      </c>
-      <c r="I20" s="9">
+      <c r="G20" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H20" s="10">
+        <v>25</v>
+      </c>
+      <c r="I20" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:9">
-      <c r="A21" s="9">
+      <c r="A21" s="10">
         <v>101700103</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="11">
         <v>50</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="12">
         <v>60</v>
       </c>
-      <c r="E21" s="11">
-        <v>0</v>
-      </c>
-      <c r="F21" s="12" t="s">
+      <c r="E21" s="12">
+        <v>0</v>
+      </c>
+      <c r="F21" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H21" s="9">
+      <c r="G21" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H21" s="10">
         <v>60</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
-      <c r="A22" s="9">
+      <c r="A22" s="10">
         <v>101700104</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="11">
         <v>250</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="12">
         <v>300</v>
       </c>
-      <c r="E22" s="11">
-        <v>0</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G22" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H22" s="9">
+      <c r="E22" s="12">
+        <v>0</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H22" s="10">
         <v>300</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:9">
-      <c r="A23" s="9">
+      <c r="A23" s="10">
         <v>102200101</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="11">
         <v>10</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="12">
         <v>15</v>
       </c>
-      <c r="E23" s="11">
-        <v>0</v>
-      </c>
-      <c r="F23" s="12" t="s">
+      <c r="E23" s="12">
+        <v>0</v>
+      </c>
+      <c r="F23" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H23" s="9">
+      <c r="G23" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H23" s="10">
         <v>15</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:9">
-      <c r="A24" s="9">
+      <c r="A24" s="10">
         <v>102200102</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="10">
-        <v>20</v>
-      </c>
-      <c r="D24" s="11">
-        <v>25</v>
-      </c>
-      <c r="E24" s="11">
-        <v>0</v>
-      </c>
-      <c r="F24" s="12" t="s">
+      <c r="B24" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="11">
+        <v>20</v>
+      </c>
+      <c r="D24" s="12">
+        <v>25</v>
+      </c>
+      <c r="E24" s="12">
+        <v>0</v>
+      </c>
+      <c r="F24" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G24" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H24" s="9">
-        <v>25</v>
-      </c>
-      <c r="I24" s="9">
+      <c r="G24" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H24" s="10">
+        <v>25</v>
+      </c>
+      <c r="I24" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:9">
-      <c r="A25" s="9">
+      <c r="A25" s="10">
         <v>102200103</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="11">
         <v>50</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="12">
         <v>60</v>
       </c>
-      <c r="E25" s="11">
-        <v>0</v>
-      </c>
-      <c r="F25" s="12" t="s">
+      <c r="E25" s="12">
+        <v>0</v>
+      </c>
+      <c r="F25" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G25" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H25" s="9">
+      <c r="G25" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H25" s="10">
         <v>60</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:9">
-      <c r="A26" s="9">
+      <c r="A26" s="10">
         <v>102200104</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="11">
         <v>250</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="12">
         <v>300</v>
       </c>
-      <c r="E26" s="11">
-        <v>0</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G26" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H26" s="9">
+      <c r="E26" s="12">
+        <v>0</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H26" s="10">
         <v>300</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:9">
-      <c r="A27" s="9">
+      <c r="A27" s="10">
         <v>102100101</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="11">
         <v>10</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="12">
         <v>15</v>
       </c>
-      <c r="E27" s="11">
-        <v>0</v>
-      </c>
-      <c r="F27" s="12" t="s">
+      <c r="E27" s="12">
+        <v>0</v>
+      </c>
+      <c r="F27" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G27" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H27" s="9">
+      <c r="G27" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H27" s="10">
         <v>15</v>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:9">
-      <c r="A28" s="9">
+      <c r="A28" s="10">
         <v>102100102</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="10">
-        <v>20</v>
-      </c>
-      <c r="D28" s="11">
-        <v>25</v>
-      </c>
-      <c r="E28" s="11">
-        <v>0</v>
-      </c>
-      <c r="F28" s="12" t="s">
+      <c r="B28" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="11">
+        <v>20</v>
+      </c>
+      <c r="D28" s="12">
+        <v>25</v>
+      </c>
+      <c r="E28" s="12">
+        <v>0</v>
+      </c>
+      <c r="F28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G28" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H28" s="9">
-        <v>25</v>
-      </c>
-      <c r="I28" s="9">
+      <c r="G28" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H28" s="10">
+        <v>25</v>
+      </c>
+      <c r="I28" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:9">
-      <c r="A29" s="9">
+      <c r="A29" s="10">
         <v>102100103</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="11">
         <v>50</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="12">
         <v>60</v>
       </c>
-      <c r="E29" s="11">
-        <v>0</v>
-      </c>
-      <c r="F29" s="12" t="s">
+      <c r="E29" s="12">
+        <v>0</v>
+      </c>
+      <c r="F29" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G29" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H29" s="9">
+      <c r="G29" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H29" s="10">
         <v>60</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:9">
-      <c r="A30" s="9">
+      <c r="A30" s="10">
         <v>102100104</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="11">
         <v>250</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="12">
         <v>300</v>
       </c>
-      <c r="E30" s="11">
-        <v>0</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G30" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H30" s="9">
+      <c r="E30" s="12">
+        <v>0</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G30" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H30" s="10">
         <v>300</v>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:9">
-      <c r="A31" s="9">
+      <c r="A31" s="10">
         <v>101800101</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="11">
         <v>10</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="12">
         <v>15</v>
       </c>
-      <c r="E31" s="11">
-        <v>0</v>
-      </c>
-      <c r="F31" s="12" t="s">
+      <c r="E31" s="12">
+        <v>0</v>
+      </c>
+      <c r="F31" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G31" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H31" s="9">
+      <c r="G31" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H31" s="10">
         <v>15</v>
       </c>
-      <c r="I31" s="9">
+      <c r="I31" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:9">
-      <c r="A32" s="9">
+      <c r="A32" s="10">
         <v>101800102</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="10">
-        <v>20</v>
-      </c>
-      <c r="D32" s="11">
-        <v>25</v>
-      </c>
-      <c r="E32" s="11">
-        <v>0</v>
-      </c>
-      <c r="F32" s="12" t="s">
+      <c r="B32" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="11">
+        <v>20</v>
+      </c>
+      <c r="D32" s="12">
+        <v>25</v>
+      </c>
+      <c r="E32" s="12">
+        <v>0</v>
+      </c>
+      <c r="F32" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H32" s="9">
-        <v>25</v>
-      </c>
-      <c r="I32" s="9">
+      <c r="G32" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H32" s="10">
+        <v>25</v>
+      </c>
+      <c r="I32" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:9">
-      <c r="A33" s="9">
+      <c r="A33" s="10">
         <v>101800103</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="11">
         <v>50</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="12">
         <v>60</v>
       </c>
-      <c r="E33" s="11">
-        <v>0</v>
-      </c>
-      <c r="F33" s="12" t="s">
+      <c r="E33" s="12">
+        <v>0</v>
+      </c>
+      <c r="F33" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G33" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H33" s="9">
+      <c r="G33" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H33" s="10">
         <v>60</v>
       </c>
-      <c r="I33" s="9">
+      <c r="I33" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:9">
-      <c r="A34" s="9">
+      <c r="A34" s="10">
         <v>101800104</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="11">
         <v>250</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="12">
         <v>300</v>
       </c>
-      <c r="E34" s="11">
-        <v>0</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G34" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H34" s="9">
+      <c r="E34" s="12">
+        <v>0</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G34" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H34" s="10">
         <v>300</v>
       </c>
-      <c r="I34" s="9">
+      <c r="I34" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:9">
-      <c r="A35" s="9">
+      <c r="A35" s="10">
         <v>102500101</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="10">
+      <c r="C35" s="11">
         <v>10</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="12">
         <v>15</v>
       </c>
-      <c r="E35" s="11">
-        <v>0</v>
-      </c>
-      <c r="F35" s="12" t="s">
+      <c r="E35" s="12">
+        <v>0</v>
+      </c>
+      <c r="F35" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G35" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H35" s="9">
+      <c r="G35" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H35" s="10">
         <v>15</v>
       </c>
-      <c r="I35" s="9">
+      <c r="I35" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:9">
-      <c r="A36" s="9">
+      <c r="A36" s="10">
         <v>102500102</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="10">
-        <v>20</v>
-      </c>
-      <c r="D36" s="11">
-        <v>25</v>
-      </c>
-      <c r="E36" s="11">
-        <v>0</v>
-      </c>
-      <c r="F36" s="12" t="s">
+      <c r="B36" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="11">
+        <v>20</v>
+      </c>
+      <c r="D36" s="12">
+        <v>25</v>
+      </c>
+      <c r="E36" s="12">
+        <v>0</v>
+      </c>
+      <c r="F36" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G36" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H36" s="9">
-        <v>25</v>
-      </c>
-      <c r="I36" s="9">
+      <c r="G36" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H36" s="10">
+        <v>25</v>
+      </c>
+      <c r="I36" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:9">
-      <c r="A37" s="9">
+      <c r="A37" s="10">
         <v>102500103</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C37" s="10">
+      <c r="C37" s="11">
         <v>50</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="12">
         <v>60</v>
       </c>
-      <c r="E37" s="11">
-        <v>0</v>
-      </c>
-      <c r="F37" s="12" t="s">
+      <c r="E37" s="12">
+        <v>0</v>
+      </c>
+      <c r="F37" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G37" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H37" s="9">
+      <c r="G37" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H37" s="10">
         <v>60</v>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:9">
-      <c r="A38" s="9">
+      <c r="A38" s="10">
         <v>102500104</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="10">
+      <c r="C38" s="11">
         <v>250</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="12">
         <v>300</v>
       </c>
-      <c r="E38" s="11">
-        <v>0</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G38" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H38" s="9">
+      <c r="E38" s="12">
+        <v>0</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H38" s="10">
         <v>300</v>
       </c>
-      <c r="I38" s="9">
+      <c r="I38" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:9">
-      <c r="A39" s="9">
+      <c r="A39" s="10">
         <v>102300101</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="10">
+      <c r="C39" s="11">
         <v>10</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="12">
         <v>15</v>
       </c>
-      <c r="E39" s="11">
-        <v>0</v>
-      </c>
-      <c r="F39" s="12" t="s">
+      <c r="E39" s="12">
+        <v>0</v>
+      </c>
+      <c r="F39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G39" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H39" s="9">
+      <c r="G39" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H39" s="10">
         <v>15</v>
       </c>
-      <c r="I39" s="9">
+      <c r="I39" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:9">
-      <c r="A40" s="9">
+      <c r="A40" s="10">
         <v>102300102</v>
       </c>
-      <c r="B40" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40" s="10">
-        <v>20</v>
-      </c>
-      <c r="D40" s="11">
-        <v>25</v>
-      </c>
-      <c r="E40" s="11">
-        <v>0</v>
-      </c>
-      <c r="F40" s="12" t="s">
+      <c r="B40" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="11">
+        <v>20</v>
+      </c>
+      <c r="D40" s="12">
+        <v>25</v>
+      </c>
+      <c r="E40" s="12">
+        <v>0</v>
+      </c>
+      <c r="F40" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G40" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H40" s="9">
-        <v>25</v>
-      </c>
-      <c r="I40" s="9">
+      <c r="G40" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H40" s="10">
+        <v>25</v>
+      </c>
+      <c r="I40" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:9">
-      <c r="A41" s="9">
+      <c r="A41" s="10">
         <v>102300103</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C41" s="11">
         <v>50</v>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="12">
         <v>60</v>
       </c>
-      <c r="E41" s="11">
-        <v>0</v>
-      </c>
-      <c r="F41" s="12" t="s">
+      <c r="E41" s="12">
+        <v>0</v>
+      </c>
+      <c r="F41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G41" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H41" s="9">
+      <c r="G41" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H41" s="10">
         <v>60</v>
       </c>
-      <c r="I41" s="9">
+      <c r="I41" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:9">
-      <c r="A42" s="9">
+      <c r="A42" s="10">
         <v>102300104</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="10">
+      <c r="C42" s="11">
         <v>250</v>
       </c>
-      <c r="D42" s="11">
+      <c r="D42" s="12">
         <v>300</v>
       </c>
-      <c r="E42" s="11">
-        <v>0</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G42" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H42" s="9">
+      <c r="E42" s="12">
+        <v>0</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H42" s="10">
         <v>300</v>
       </c>
-      <c r="I42" s="9">
+      <c r="I42" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:9">
-      <c r="A43" s="9">
+      <c r="A43" s="10">
         <v>103400101</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C43" s="10">
-        <v>0</v>
-      </c>
-      <c r="D43" s="11">
-        <v>0</v>
-      </c>
-      <c r="E43" s="11">
+      <c r="C43" s="11">
+        <v>0</v>
+      </c>
+      <c r="D43" s="12">
+        <v>0</v>
+      </c>
+      <c r="E43" s="12">
         <v>1000</v>
       </c>
-      <c r="F43" s="12" t="s">
+      <c r="F43" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G43" s="9">
-        <v>0</v>
-      </c>
-      <c r="H43" s="9">
+      <c r="G43" s="10">
+        <v>0</v>
+      </c>
+      <c r="H43" s="10">
         <v>1</v>
       </c>
-      <c r="I43" s="9">
+      <c r="I43" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:9">
-      <c r="A44" s="9">
+      <c r="A44" s="10">
         <v>103401101</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="10">
-        <v>0</v>
-      </c>
-      <c r="D44" s="11">
-        <v>0</v>
-      </c>
-      <c r="E44" s="11">
+      <c r="C44" s="11">
+        <v>0</v>
+      </c>
+      <c r="D44" s="12">
+        <v>0</v>
+      </c>
+      <c r="E44" s="12">
         <v>1000</v>
       </c>
-      <c r="F44" s="12" t="s">
+      <c r="F44" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G44" s="9">
-        <v>0</v>
-      </c>
-      <c r="H44" s="9">
+      <c r="G44" s="10">
+        <v>0</v>
+      </c>
+      <c r="H44" s="10">
         <v>1</v>
       </c>
-      <c r="I44" s="9">
+      <c r="I44" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:9">
-      <c r="A45" s="9">
+      <c r="A45" s="10">
         <v>103500101</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C45" s="10">
+      <c r="C45" s="11">
         <v>10</v>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="12">
         <v>15</v>
       </c>
-      <c r="E45" s="11">
-        <v>0</v>
-      </c>
-      <c r="F45" s="12" t="s">
+      <c r="E45" s="12">
+        <v>0</v>
+      </c>
+      <c r="F45" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G45" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H45" s="9">
+      <c r="G45" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H45" s="10">
         <v>15</v>
       </c>
-      <c r="I45" s="9">
+      <c r="I45" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:9">
-      <c r="A46" s="9">
+      <c r="A46" s="10">
         <v>103500102</v>
       </c>
-      <c r="B46" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46" s="10">
-        <v>20</v>
-      </c>
-      <c r="D46" s="11">
-        <v>25</v>
-      </c>
-      <c r="E46" s="11">
-        <v>0</v>
-      </c>
-      <c r="F46" s="12" t="s">
+      <c r="B46" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="11">
+        <v>20</v>
+      </c>
+      <c r="D46" s="12">
+        <v>25</v>
+      </c>
+      <c r="E46" s="12">
+        <v>0</v>
+      </c>
+      <c r="F46" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G46" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H46" s="9">
-        <v>25</v>
-      </c>
-      <c r="I46" s="9">
+      <c r="G46" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H46" s="10">
+        <v>25</v>
+      </c>
+      <c r="I46" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:9">
-      <c r="A47" s="9">
+      <c r="A47" s="10">
         <v>103500103</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="10">
+      <c r="C47" s="11">
         <v>50</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="12">
         <v>60</v>
       </c>
-      <c r="E47" s="11">
-        <v>0</v>
-      </c>
-      <c r="F47" s="12" t="s">
+      <c r="E47" s="12">
+        <v>0</v>
+      </c>
+      <c r="F47" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G47" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H47" s="9">
+      <c r="G47" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H47" s="10">
         <v>60</v>
       </c>
-      <c r="I47" s="9">
+      <c r="I47" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:9">
-      <c r="A48" s="9">
+      <c r="A48" s="10">
         <v>103500104</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="10">
+      <c r="C48" s="11">
         <v>250</v>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="12">
         <v>300</v>
       </c>
-      <c r="E48" s="11">
-        <v>0</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G48" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H48" s="9">
+      <c r="E48" s="12">
+        <v>0</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H48" s="10">
         <v>300</v>
       </c>
-      <c r="I48" s="9">
+      <c r="I48" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:9">
-      <c r="A49" s="9">
+      <c r="A49" s="10">
         <v>103501101</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C49" s="10">
+      <c r="C49" s="11">
         <v>10</v>
       </c>
-      <c r="D49" s="11">
+      <c r="D49" s="12">
         <v>15</v>
       </c>
-      <c r="E49" s="11">
-        <v>0</v>
-      </c>
-      <c r="F49" s="12" t="s">
+      <c r="E49" s="12">
+        <v>0</v>
+      </c>
+      <c r="F49" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G49" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H49" s="9">
+      <c r="G49" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H49" s="10">
         <v>15</v>
       </c>
-      <c r="I49" s="9">
+      <c r="I49" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:9">
-      <c r="A50" s="9">
+      <c r="A50" s="10">
         <v>103501102</v>
       </c>
-      <c r="B50" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50" s="10">
-        <v>20</v>
-      </c>
-      <c r="D50" s="11">
-        <v>25</v>
-      </c>
-      <c r="E50" s="11">
-        <v>0</v>
-      </c>
-      <c r="F50" s="12" t="s">
+      <c r="B50" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="11">
+        <v>20</v>
+      </c>
+      <c r="D50" s="12">
+        <v>25</v>
+      </c>
+      <c r="E50" s="12">
+        <v>0</v>
+      </c>
+      <c r="F50" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G50" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H50" s="9">
-        <v>25</v>
-      </c>
-      <c r="I50" s="9">
+      <c r="G50" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H50" s="10">
+        <v>25</v>
+      </c>
+      <c r="I50" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:9">
-      <c r="A51" s="9">
+      <c r="A51" s="10">
         <v>103501103</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C51" s="10">
+      <c r="C51" s="11">
         <v>50</v>
       </c>
-      <c r="D51" s="11">
+      <c r="D51" s="12">
         <v>60</v>
       </c>
-      <c r="E51" s="11">
-        <v>0</v>
-      </c>
-      <c r="F51" s="12" t="s">
+      <c r="E51" s="12">
+        <v>0</v>
+      </c>
+      <c r="F51" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G51" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H51" s="9">
+      <c r="G51" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H51" s="10">
         <v>60</v>
       </c>
-      <c r="I51" s="9">
+      <c r="I51" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:9">
-      <c r="A52" s="9">
+      <c r="A52" s="10">
         <v>103501104</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C52" s="10">
+      <c r="C52" s="11">
         <v>250</v>
       </c>
-      <c r="D52" s="11">
+      <c r="D52" s="12">
         <v>300</v>
       </c>
-      <c r="E52" s="11">
-        <v>0</v>
-      </c>
-      <c r="F52" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G52" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H52" s="9">
+      <c r="E52" s="12">
+        <v>0</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G52" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H52" s="10">
         <v>300</v>
       </c>
-      <c r="I52" s="9">
+      <c r="I52" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:9">
-      <c r="A53" s="9">
+      <c r="A53" s="10">
         <v>103600101</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C53" s="10">
-        <v>0</v>
-      </c>
-      <c r="D53" s="11">
-        <v>0</v>
-      </c>
-      <c r="E53" s="11">
+      <c r="C53" s="11">
+        <v>0</v>
+      </c>
+      <c r="D53" s="12">
+        <v>0</v>
+      </c>
+      <c r="E53" s="12">
         <v>1000</v>
       </c>
-      <c r="F53" s="12" t="s">
+      <c r="F53" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G53" s="9">
-        <v>0</v>
-      </c>
-      <c r="H53" s="9">
+      <c r="G53" s="10">
+        <v>0</v>
+      </c>
+      <c r="H53" s="10">
         <v>1</v>
       </c>
-      <c r="I53" s="9">
+      <c r="I53" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:9">
-      <c r="A54" s="9">
+      <c r="A54" s="10">
         <v>102800101</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="10">
+      <c r="C54" s="11">
         <v>10</v>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="12">
         <v>15</v>
       </c>
-      <c r="E54" s="11">
-        <v>0</v>
-      </c>
-      <c r="F54" s="12" t="s">
+      <c r="E54" s="12">
+        <v>0</v>
+      </c>
+      <c r="F54" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G54" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H54" s="9">
+      <c r="G54" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H54" s="10">
         <v>15</v>
       </c>
-      <c r="I54" s="9">
+      <c r="I54" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:9">
-      <c r="A55" s="9">
+      <c r="A55" s="10">
         <v>102800102</v>
       </c>
-      <c r="B55" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C55" s="10">
-        <v>20</v>
-      </c>
-      <c r="D55" s="11">
-        <v>25</v>
-      </c>
-      <c r="E55" s="11">
-        <v>0</v>
-      </c>
-      <c r="F55" s="12" t="s">
+      <c r="B55" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" s="11">
+        <v>20</v>
+      </c>
+      <c r="D55" s="12">
+        <v>25</v>
+      </c>
+      <c r="E55" s="12">
+        <v>0</v>
+      </c>
+      <c r="F55" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G55" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H55" s="9">
-        <v>25</v>
-      </c>
-      <c r="I55" s="9">
+      <c r="G55" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H55" s="10">
+        <v>25</v>
+      </c>
+      <c r="I55" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="1:9">
-      <c r="A56" s="9">
+      <c r="A56" s="10">
         <v>102800103</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C56" s="10">
+      <c r="C56" s="11">
         <v>50</v>
       </c>
-      <c r="D56" s="11">
+      <c r="D56" s="12">
         <v>60</v>
       </c>
-      <c r="E56" s="11">
-        <v>0</v>
-      </c>
-      <c r="F56" s="12" t="s">
+      <c r="E56" s="12">
+        <v>0</v>
+      </c>
+      <c r="F56" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G56" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H56" s="9">
+      <c r="G56" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H56" s="10">
         <v>60</v>
       </c>
-      <c r="I56" s="9">
+      <c r="I56" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:9">
-      <c r="A57" s="9">
+      <c r="A57" s="10">
         <v>102800104</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C57" s="10">
+      <c r="C57" s="11">
         <v>250</v>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="12">
         <v>300</v>
       </c>
-      <c r="E57" s="11">
-        <v>0</v>
-      </c>
-      <c r="F57" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G57" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H57" s="9">
+      <c r="E57" s="12">
+        <v>0</v>
+      </c>
+      <c r="F57" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G57" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H57" s="10">
         <v>300</v>
       </c>
-      <c r="I57" s="9">
+      <c r="I57" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:9">
-      <c r="A58" s="9">
+      <c r="A58" s="10">
         <v>102000101</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C58" s="10">
+      <c r="C58" s="11">
         <v>10</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="12">
         <v>15</v>
       </c>
-      <c r="E58" s="11">
-        <v>0</v>
-      </c>
-      <c r="F58" s="12" t="s">
+      <c r="E58" s="12">
+        <v>0</v>
+      </c>
+      <c r="F58" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G58" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H58" s="9">
+      <c r="G58" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H58" s="10">
         <v>15</v>
       </c>
-      <c r="I58" s="9">
+      <c r="I58" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:9">
-      <c r="A59" s="9">
+      <c r="A59" s="10">
         <v>102000102</v>
       </c>
-      <c r="B59" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C59" s="10">
-        <v>20</v>
-      </c>
-      <c r="D59" s="11">
-        <v>25</v>
-      </c>
-      <c r="E59" s="11">
-        <v>0</v>
-      </c>
-      <c r="F59" s="12" t="s">
+      <c r="B59" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" s="11">
+        <v>20</v>
+      </c>
+      <c r="D59" s="12">
+        <v>25</v>
+      </c>
+      <c r="E59" s="12">
+        <v>0</v>
+      </c>
+      <c r="F59" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G59" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H59" s="9">
-        <v>25</v>
-      </c>
-      <c r="I59" s="9">
+      <c r="G59" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H59" s="10">
+        <v>25</v>
+      </c>
+      <c r="I59" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:9">
-      <c r="A60" s="9">
+      <c r="A60" s="10">
         <v>102000103</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C60" s="10">
+      <c r="C60" s="11">
         <v>50</v>
       </c>
-      <c r="D60" s="11">
+      <c r="D60" s="12">
         <v>60</v>
       </c>
-      <c r="E60" s="11">
-        <v>0</v>
-      </c>
-      <c r="F60" s="12" t="s">
+      <c r="E60" s="12">
+        <v>0</v>
+      </c>
+      <c r="F60" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G60" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H60" s="9">
+      <c r="G60" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H60" s="10">
         <v>60</v>
       </c>
-      <c r="I60" s="9">
+      <c r="I60" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:9">
-      <c r="A61" s="9">
+      <c r="A61" s="10">
         <v>102000104</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C61" s="10">
+      <c r="C61" s="11">
         <v>250</v>
       </c>
-      <c r="D61" s="11">
+      <c r="D61" s="12">
         <v>300</v>
       </c>
-      <c r="E61" s="11">
-        <v>0</v>
-      </c>
-      <c r="F61" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G61" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H61" s="9">
+      <c r="E61" s="12">
+        <v>0</v>
+      </c>
+      <c r="F61" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G61" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H61" s="10">
         <v>300</v>
       </c>
-      <c r="I61" s="9">
+      <c r="I61" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:9">
-      <c r="A62" s="9">
+      <c r="A62" s="10">
         <v>103800101</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C62" s="10">
+      <c r="C62" s="11">
         <v>10</v>
       </c>
-      <c r="D62" s="11">
+      <c r="D62" s="12">
         <v>15</v>
       </c>
-      <c r="E62" s="11">
-        <v>0</v>
-      </c>
-      <c r="F62" s="12" t="s">
+      <c r="E62" s="12">
+        <v>0</v>
+      </c>
+      <c r="F62" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G62" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H62" s="9">
+      <c r="G62" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H62" s="10">
         <v>15</v>
       </c>
-      <c r="I62" s="9">
+      <c r="I62" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:9">
-      <c r="A63" s="9">
+      <c r="A63" s="10">
         <v>103800102</v>
       </c>
-      <c r="B63" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C63" s="10">
-        <v>20</v>
-      </c>
-      <c r="D63" s="11">
-        <v>25</v>
-      </c>
-      <c r="E63" s="11">
-        <v>0</v>
-      </c>
-      <c r="F63" s="12" t="s">
+      <c r="B63" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" s="11">
+        <v>20</v>
+      </c>
+      <c r="D63" s="12">
+        <v>25</v>
+      </c>
+      <c r="E63" s="12">
+        <v>0</v>
+      </c>
+      <c r="F63" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G63" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H63" s="9">
-        <v>25</v>
-      </c>
-      <c r="I63" s="9">
+      <c r="G63" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H63" s="10">
+        <v>25</v>
+      </c>
+      <c r="I63" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:9">
-      <c r="A64" s="9">
+      <c r="A64" s="10">
         <v>103800103</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C64" s="10">
+      <c r="C64" s="11">
         <v>50</v>
       </c>
-      <c r="D64" s="11">
+      <c r="D64" s="12">
         <v>60</v>
       </c>
-      <c r="E64" s="11">
-        <v>0</v>
-      </c>
-      <c r="F64" s="12" t="s">
+      <c r="E64" s="12">
+        <v>0</v>
+      </c>
+      <c r="F64" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G64" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H64" s="9">
+      <c r="G64" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H64" s="10">
         <v>60</v>
       </c>
-      <c r="I64" s="9">
+      <c r="I64" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:9">
-      <c r="A65" s="9">
+      <c r="A65" s="10">
         <v>103800104</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C65" s="10">
+      <c r="C65" s="11">
         <v>250</v>
       </c>
-      <c r="D65" s="11">
+      <c r="D65" s="12">
         <v>300</v>
       </c>
-      <c r="E65" s="11">
-        <v>0</v>
-      </c>
-      <c r="F65" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G65" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H65" s="9">
+      <c r="E65" s="12">
+        <v>0</v>
+      </c>
+      <c r="F65" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G65" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H65" s="10">
         <v>300</v>
       </c>
-      <c r="I65" s="9">
+      <c r="I65" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:9">
-      <c r="A66" s="9">
+      <c r="A66" s="10">
         <v>102700101</v>
       </c>
-      <c r="B66" s="9" t="s">
+      <c r="B66" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C66" s="10">
+      <c r="C66" s="11">
         <v>10</v>
       </c>
-      <c r="D66" s="11">
+      <c r="D66" s="12">
         <v>15</v>
       </c>
-      <c r="E66" s="11">
-        <v>0</v>
-      </c>
-      <c r="F66" s="12" t="s">
+      <c r="E66" s="12">
+        <v>0</v>
+      </c>
+      <c r="F66" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G66" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H66" s="9">
+      <c r="G66" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H66" s="10">
         <v>15</v>
       </c>
-      <c r="I66" s="9">
+      <c r="I66" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:9">
-      <c r="A67" s="9">
+      <c r="A67" s="10">
         <v>102700102</v>
       </c>
-      <c r="B67" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C67" s="10">
-        <v>20</v>
-      </c>
-      <c r="D67" s="11">
-        <v>25</v>
-      </c>
-      <c r="E67" s="11">
-        <v>0</v>
-      </c>
-      <c r="F67" s="12" t="s">
+      <c r="B67" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67" s="11">
+        <v>20</v>
+      </c>
+      <c r="D67" s="12">
+        <v>25</v>
+      </c>
+      <c r="E67" s="12">
+        <v>0</v>
+      </c>
+      <c r="F67" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G67" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H67" s="9">
-        <v>25</v>
-      </c>
-      <c r="I67" s="9">
+      <c r="G67" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H67" s="10">
+        <v>25</v>
+      </c>
+      <c r="I67" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:9">
-      <c r="A68" s="9">
+      <c r="A68" s="10">
         <v>102700103</v>
       </c>
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C68" s="10">
+      <c r="C68" s="11">
         <v>50</v>
       </c>
-      <c r="D68" s="11">
+      <c r="D68" s="12">
         <v>60</v>
       </c>
-      <c r="E68" s="11">
-        <v>0</v>
-      </c>
-      <c r="F68" s="12" t="s">
+      <c r="E68" s="12">
+        <v>0</v>
+      </c>
+      <c r="F68" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G68" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H68" s="9">
+      <c r="G68" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H68" s="10">
         <v>60</v>
       </c>
-      <c r="I68" s="9">
+      <c r="I68" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:9">
-      <c r="A69" s="9">
+      <c r="A69" s="10">
         <v>102700104</v>
       </c>
-      <c r="B69" s="9" t="s">
+      <c r="B69" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C69" s="10">
+      <c r="C69" s="11">
         <v>250</v>
       </c>
-      <c r="D69" s="11">
+      <c r="D69" s="12">
         <v>300</v>
       </c>
-      <c r="E69" s="11">
-        <v>0</v>
-      </c>
-      <c r="F69" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G69" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H69" s="9">
+      <c r="E69" s="12">
+        <v>0</v>
+      </c>
+      <c r="F69" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G69" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H69" s="10">
         <v>300</v>
       </c>
-      <c r="I69" s="9">
+      <c r="I69" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:9">
-      <c r="A70" s="9">
+      <c r="A70" s="10">
         <v>103700101</v>
       </c>
-      <c r="B70" s="9" t="s">
+      <c r="B70" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C70" s="10">
-        <v>0</v>
-      </c>
-      <c r="D70" s="11">
-        <v>0</v>
-      </c>
-      <c r="E70" s="11">
+      <c r="C70" s="11">
+        <v>0</v>
+      </c>
+      <c r="D70" s="12">
+        <v>0</v>
+      </c>
+      <c r="E70" s="12">
         <v>1000</v>
       </c>
-      <c r="F70" s="12" t="s">
+      <c r="F70" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G70" s="9">
-        <v>0</v>
-      </c>
-      <c r="H70" s="9">
+      <c r="G70" s="10">
+        <v>0</v>
+      </c>
+      <c r="H70" s="10">
         <v>1</v>
       </c>
-      <c r="I70" s="9">
+      <c r="I70" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:9">
-      <c r="A71" s="9">
+      <c r="A71" s="10">
         <v>103100101</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C71" s="10">
+      <c r="C71" s="11">
         <v>10</v>
       </c>
-      <c r="D71" s="11">
+      <c r="D71" s="12">
         <v>15</v>
       </c>
-      <c r="E71" s="11">
-        <v>0</v>
-      </c>
-      <c r="F71" s="12" t="s">
+      <c r="E71" s="12">
+        <v>0</v>
+      </c>
+      <c r="F71" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G71" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H71" s="9">
+      <c r="G71" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H71" s="10">
         <v>15</v>
       </c>
-      <c r="I71" s="9">
+      <c r="I71" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="72" ht="16.5" spans="1:9">
-      <c r="A72" s="9">
+      <c r="A72" s="10">
         <v>103100102</v>
       </c>
-      <c r="B72" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C72" s="10">
-        <v>20</v>
-      </c>
-      <c r="D72" s="11">
-        <v>25</v>
-      </c>
-      <c r="E72" s="11">
-        <v>0</v>
-      </c>
-      <c r="F72" s="12" t="s">
+      <c r="B72" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72" s="11">
+        <v>20</v>
+      </c>
+      <c r="D72" s="12">
+        <v>25</v>
+      </c>
+      <c r="E72" s="12">
+        <v>0</v>
+      </c>
+      <c r="F72" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G72" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H72" s="9">
-        <v>25</v>
-      </c>
-      <c r="I72" s="9">
+      <c r="G72" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H72" s="10">
+        <v>25</v>
+      </c>
+      <c r="I72" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:9">
-      <c r="A73" s="9">
+      <c r="A73" s="10">
         <v>103100103</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C73" s="10">
+      <c r="C73" s="11">
         <v>50</v>
       </c>
-      <c r="D73" s="11">
+      <c r="D73" s="12">
         <v>60</v>
       </c>
-      <c r="E73" s="11">
-        <v>0</v>
-      </c>
-      <c r="F73" s="12" t="s">
+      <c r="E73" s="12">
+        <v>0</v>
+      </c>
+      <c r="F73" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G73" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H73" s="9">
+      <c r="G73" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H73" s="10">
         <v>60</v>
       </c>
-      <c r="I73" s="9">
+      <c r="I73" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:9">
-      <c r="A74" s="9">
+      <c r="A74" s="10">
         <v>103100104</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C74" s="10">
+      <c r="C74" s="11">
         <v>250</v>
       </c>
-      <c r="D74" s="11">
+      <c r="D74" s="12">
         <v>300</v>
       </c>
-      <c r="E74" s="11">
-        <v>0</v>
-      </c>
-      <c r="F74" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G74" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H74" s="9">
+      <c r="E74" s="12">
+        <v>0</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G74" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H74" s="10">
         <v>300</v>
       </c>
-      <c r="I74" s="9">
+      <c r="I74" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:9">
-      <c r="A75" s="9">
+      <c r="A75" s="10">
         <v>104000101</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C75" s="10">
+      <c r="C75" s="11">
         <v>10</v>
       </c>
-      <c r="D75" s="11">
+      <c r="D75" s="12">
         <v>15</v>
       </c>
-      <c r="E75" s="11">
-        <v>0</v>
-      </c>
-      <c r="F75" s="12" t="s">
+      <c r="E75" s="12">
+        <v>0</v>
+      </c>
+      <c r="F75" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G75" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H75" s="9">
+      <c r="G75" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H75" s="10">
         <v>15</v>
       </c>
-      <c r="I75" s="9">
+      <c r="I75" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="76" ht="16.5" spans="1:9">
-      <c r="A76" s="9">
+      <c r="A76" s="10">
         <v>104000102</v>
       </c>
-      <c r="B76" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C76" s="10">
-        <v>20</v>
-      </c>
-      <c r="D76" s="11">
-        <v>25</v>
-      </c>
-      <c r="E76" s="11">
-        <v>0</v>
-      </c>
-      <c r="F76" s="12" t="s">
+      <c r="B76" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C76" s="11">
+        <v>20</v>
+      </c>
+      <c r="D76" s="12">
+        <v>25</v>
+      </c>
+      <c r="E76" s="12">
+        <v>0</v>
+      </c>
+      <c r="F76" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G76" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H76" s="9">
-        <v>25</v>
-      </c>
-      <c r="I76" s="9">
+      <c r="G76" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H76" s="10">
+        <v>25</v>
+      </c>
+      <c r="I76" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="77" ht="16.5" spans="1:9">
-      <c r="A77" s="9">
+      <c r="A77" s="10">
         <v>104000103</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C77" s="10">
+      <c r="C77" s="11">
         <v>50</v>
       </c>
-      <c r="D77" s="11">
+      <c r="D77" s="12">
         <v>60</v>
       </c>
-      <c r="E77" s="11">
-        <v>0</v>
-      </c>
-      <c r="F77" s="12" t="s">
+      <c r="E77" s="12">
+        <v>0</v>
+      </c>
+      <c r="F77" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G77" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H77" s="9">
+      <c r="G77" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H77" s="10">
         <v>60</v>
       </c>
-      <c r="I77" s="9">
+      <c r="I77" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:9">
-      <c r="A78" s="9">
+      <c r="A78" s="10">
         <v>104000104</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C78" s="10">
+      <c r="C78" s="11">
         <v>250</v>
       </c>
-      <c r="D78" s="11">
+      <c r="D78" s="12">
         <v>300</v>
       </c>
-      <c r="E78" s="11">
-        <v>0</v>
-      </c>
-      <c r="F78" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G78" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H78" s="9">
+      <c r="E78" s="12">
+        <v>0</v>
+      </c>
+      <c r="F78" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G78" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H78" s="10">
         <v>300</v>
       </c>
-      <c r="I78" s="9">
+      <c r="I78" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="79" ht="16.5" spans="1:9">
-      <c r="A79" s="9">
+      <c r="A79" s="10">
         <v>103900101</v>
       </c>
-      <c r="B79" s="9" t="s">
+      <c r="B79" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C79" s="10">
+      <c r="C79" s="11">
         <v>10</v>
       </c>
-      <c r="D79" s="11">
+      <c r="D79" s="12">
         <v>15</v>
       </c>
-      <c r="E79" s="11">
-        <v>0</v>
-      </c>
-      <c r="F79" s="12" t="s">
+      <c r="E79" s="12">
+        <v>0</v>
+      </c>
+      <c r="F79" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G79" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H79" s="9">
+      <c r="G79" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H79" s="10">
         <v>15</v>
       </c>
-      <c r="I79" s="9">
+      <c r="I79" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="80" ht="16.5" spans="1:9">
-      <c r="A80" s="9">
+      <c r="A80" s="10">
         <v>103900102</v>
       </c>
-      <c r="B80" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C80" s="10">
-        <v>20</v>
-      </c>
-      <c r="D80" s="11">
-        <v>25</v>
-      </c>
-      <c r="E80" s="11">
-        <v>0</v>
-      </c>
-      <c r="F80" s="12" t="s">
+      <c r="B80" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80" s="11">
+        <v>20</v>
+      </c>
+      <c r="D80" s="12">
+        <v>25</v>
+      </c>
+      <c r="E80" s="12">
+        <v>0</v>
+      </c>
+      <c r="F80" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G80" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H80" s="9">
-        <v>25</v>
-      </c>
-      <c r="I80" s="9">
+      <c r="G80" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H80" s="10">
+        <v>25</v>
+      </c>
+      <c r="I80" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="81" ht="16.5" spans="1:9">
-      <c r="A81" s="9">
+      <c r="A81" s="10">
         <v>103900103</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="B81" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C81" s="10">
+      <c r="C81" s="11">
         <v>50</v>
       </c>
-      <c r="D81" s="11">
+      <c r="D81" s="12">
         <v>60</v>
       </c>
-      <c r="E81" s="11">
-        <v>0</v>
-      </c>
-      <c r="F81" s="12" t="s">
+      <c r="E81" s="12">
+        <v>0</v>
+      </c>
+      <c r="F81" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G81" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H81" s="9">
+      <c r="G81" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H81" s="10">
         <v>60</v>
       </c>
-      <c r="I81" s="9">
+      <c r="I81" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:9">
-      <c r="A82" s="9">
+      <c r="A82" s="10">
         <v>103900104</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="B82" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C82" s="10">
+      <c r="C82" s="11">
         <v>250</v>
       </c>
-      <c r="D82" s="11">
+      <c r="D82" s="12">
         <v>300</v>
       </c>
-      <c r="E82" s="11">
-        <v>0</v>
-      </c>
-      <c r="F82" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G82" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H82" s="9">
+      <c r="E82" s="12">
+        <v>0</v>
+      </c>
+      <c r="F82" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G82" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H82" s="10">
         <v>300</v>
       </c>
-      <c r="I82" s="9">
+      <c r="I82" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:9">
-      <c r="A83" s="9">
+      <c r="A83" s="10">
         <v>101600101</v>
       </c>
-      <c r="B83" s="9" t="s">
+      <c r="B83" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C83" s="10">
+      <c r="C83" s="11">
         <v>10</v>
       </c>
-      <c r="D83" s="11">
+      <c r="D83" s="12">
         <v>15</v>
       </c>
-      <c r="E83" s="11">
-        <v>0</v>
-      </c>
-      <c r="F83" s="12" t="s">
+      <c r="E83" s="12">
+        <v>0</v>
+      </c>
+      <c r="F83" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G83" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H83" s="9">
+      <c r="G83" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H83" s="10">
         <v>15</v>
       </c>
-      <c r="I83" s="9">
+      <c r="I83" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="84" ht="16.5" spans="1:9">
-      <c r="A84" s="9">
+      <c r="A84" s="10">
         <v>101600102</v>
       </c>
-      <c r="B84" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C84" s="10">
-        <v>20</v>
-      </c>
-      <c r="D84" s="11">
-        <v>25</v>
-      </c>
-      <c r="E84" s="11">
-        <v>0</v>
-      </c>
-      <c r="F84" s="12" t="s">
+      <c r="B84" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84" s="11">
+        <v>20</v>
+      </c>
+      <c r="D84" s="12">
+        <v>25</v>
+      </c>
+      <c r="E84" s="12">
+        <v>0</v>
+      </c>
+      <c r="F84" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G84" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H84" s="9">
-        <v>25</v>
-      </c>
-      <c r="I84" s="9">
+      <c r="G84" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H84" s="10">
+        <v>25</v>
+      </c>
+      <c r="I84" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="85" ht="16.5" spans="1:9">
-      <c r="A85" s="9">
+      <c r="A85" s="10">
         <v>101600103</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B85" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C85" s="10">
+      <c r="C85" s="11">
         <v>50</v>
       </c>
-      <c r="D85" s="11">
+      <c r="D85" s="12">
         <v>60</v>
       </c>
-      <c r="E85" s="11">
-        <v>0</v>
-      </c>
-      <c r="F85" s="12" t="s">
+      <c r="E85" s="12">
+        <v>0</v>
+      </c>
+      <c r="F85" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G85" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H85" s="9">
+      <c r="G85" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H85" s="10">
         <v>60</v>
       </c>
-      <c r="I85" s="9">
+      <c r="I85" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="86" ht="16.5" spans="1:9">
-      <c r="A86" s="9">
+      <c r="A86" s="10">
         <v>101600104</v>
       </c>
-      <c r="B86" s="9" t="s">
+      <c r="B86" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C86" s="10">
+      <c r="C86" s="11">
         <v>250</v>
       </c>
-      <c r="D86" s="11">
+      <c r="D86" s="12">
         <v>300</v>
       </c>
-      <c r="E86" s="11">
-        <v>0</v>
-      </c>
-      <c r="F86" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G86" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H86" s="9">
+      <c r="E86" s="12">
+        <v>0</v>
+      </c>
+      <c r="F86" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G86" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H86" s="10">
         <v>300</v>
       </c>
-      <c r="I86" s="9">
+      <c r="I86" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="87" ht="16.5" spans="1:9">
-      <c r="A87" s="9">
+      <c r="A87" s="10">
         <v>101500101</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B87" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C87" s="10">
+      <c r="C87" s="11">
         <v>10</v>
       </c>
-      <c r="D87" s="11">
+      <c r="D87" s="12">
         <v>15</v>
       </c>
-      <c r="E87" s="11">
-        <v>0</v>
-      </c>
-      <c r="F87" s="12" t="s">
+      <c r="E87" s="12">
+        <v>0</v>
+      </c>
+      <c r="F87" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G87" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H87" s="9">
+      <c r="G87" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H87" s="10">
         <v>15</v>
       </c>
-      <c r="I87" s="9">
+      <c r="I87" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="88" ht="16.5" spans="1:9">
-      <c r="A88" s="9">
+      <c r="A88" s="10">
         <v>101500102</v>
       </c>
-      <c r="B88" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C88" s="10">
-        <v>20</v>
-      </c>
-      <c r="D88" s="11">
-        <v>25</v>
-      </c>
-      <c r="E88" s="11">
-        <v>0</v>
-      </c>
-      <c r="F88" s="12" t="s">
+      <c r="B88" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C88" s="11">
+        <v>20</v>
+      </c>
+      <c r="D88" s="12">
+        <v>25</v>
+      </c>
+      <c r="E88" s="12">
+        <v>0</v>
+      </c>
+      <c r="F88" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G88" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H88" s="9">
-        <v>25</v>
-      </c>
-      <c r="I88" s="9">
+      <c r="G88" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H88" s="10">
+        <v>25</v>
+      </c>
+      <c r="I88" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="89" ht="16.5" spans="1:9">
-      <c r="A89" s="9">
+      <c r="A89" s="10">
         <v>101500103</v>
       </c>
-      <c r="B89" s="9" t="s">
+      <c r="B89" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C89" s="10">
+      <c r="C89" s="11">
         <v>50</v>
       </c>
-      <c r="D89" s="11">
+      <c r="D89" s="12">
         <v>60</v>
       </c>
-      <c r="E89" s="11">
-        <v>0</v>
-      </c>
-      <c r="F89" s="12" t="s">
+      <c r="E89" s="12">
+        <v>0</v>
+      </c>
+      <c r="F89" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G89" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H89" s="9">
+      <c r="G89" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H89" s="10">
         <v>60</v>
       </c>
-      <c r="I89" s="9">
+      <c r="I89" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:9">
-      <c r="A90" s="9">
+      <c r="A90" s="10">
         <v>101500104</v>
       </c>
-      <c r="B90" s="9" t="s">
+      <c r="B90" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C90" s="10">
+      <c r="C90" s="11">
         <v>250</v>
       </c>
-      <c r="D90" s="11">
+      <c r="D90" s="12">
         <v>300</v>
       </c>
-      <c r="E90" s="11">
-        <v>0</v>
-      </c>
-      <c r="F90" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G90" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H90" s="9">
+      <c r="E90" s="12">
+        <v>0</v>
+      </c>
+      <c r="F90" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G90" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H90" s="10">
         <v>300</v>
       </c>
-      <c r="I90" s="9">
+      <c r="I90" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:9">
-      <c r="A91" s="9">
+      <c r="A91" s="10">
         <v>102600101</v>
       </c>
-      <c r="B91" s="9" t="s">
+      <c r="B91" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C91" s="10">
+      <c r="C91" s="11">
         <v>10</v>
       </c>
-      <c r="D91" s="11">
+      <c r="D91" s="12">
         <v>15</v>
       </c>
-      <c r="E91" s="11">
-        <v>0</v>
-      </c>
-      <c r="F91" s="12" t="s">
+      <c r="E91" s="12">
+        <v>0</v>
+      </c>
+      <c r="F91" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G91" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H91" s="9">
+      <c r="G91" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H91" s="10">
         <v>15</v>
       </c>
-      <c r="I91" s="9">
+      <c r="I91" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:9">
-      <c r="A92" s="9">
+      <c r="A92" s="10">
         <v>102600102</v>
       </c>
-      <c r="B92" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C92" s="10">
-        <v>20</v>
-      </c>
-      <c r="D92" s="11">
-        <v>25</v>
-      </c>
-      <c r="E92" s="11">
-        <v>0</v>
-      </c>
-      <c r="F92" s="12" t="s">
+      <c r="B92" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C92" s="11">
+        <v>20</v>
+      </c>
+      <c r="D92" s="12">
+        <v>25</v>
+      </c>
+      <c r="E92" s="12">
+        <v>0</v>
+      </c>
+      <c r="F92" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G92" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H92" s="9">
-        <v>25</v>
-      </c>
-      <c r="I92" s="9">
+      <c r="G92" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H92" s="10">
+        <v>25</v>
+      </c>
+      <c r="I92" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:9">
-      <c r="A93" s="9">
+      <c r="A93" s="10">
         <v>102600103</v>
       </c>
-      <c r="B93" s="9" t="s">
+      <c r="B93" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C93" s="10">
+      <c r="C93" s="11">
         <v>50</v>
       </c>
-      <c r="D93" s="11">
+      <c r="D93" s="12">
         <v>60</v>
       </c>
-      <c r="E93" s="11">
-        <v>0</v>
-      </c>
-      <c r="F93" s="12" t="s">
+      <c r="E93" s="12">
+        <v>0</v>
+      </c>
+      <c r="F93" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G93" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H93" s="9">
+      <c r="G93" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H93" s="10">
         <v>60</v>
       </c>
-      <c r="I93" s="9">
+      <c r="I93" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:9">
-      <c r="A94" s="9">
+      <c r="A94" s="10">
         <v>102600104</v>
       </c>
-      <c r="B94" s="9" t="s">
+      <c r="B94" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C94" s="10">
+      <c r="C94" s="11">
         <v>250</v>
       </c>
-      <c r="D94" s="11">
+      <c r="D94" s="12">
         <v>300</v>
       </c>
-      <c r="E94" s="11">
-        <v>0</v>
-      </c>
-      <c r="F94" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G94" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H94" s="9">
+      <c r="E94" s="12">
+        <v>0</v>
+      </c>
+      <c r="F94" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G94" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H94" s="10">
         <v>300</v>
       </c>
-      <c r="I94" s="9">
+      <c r="I94" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="95" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A95" s="9">
+      <c r="A95" s="10">
         <v>105000101</v>
       </c>
-      <c r="B95" s="9" t="s">
+      <c r="B95" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C95" s="10">
+      <c r="C95" s="11">
         <v>10</v>
       </c>
-      <c r="D95" s="11">
+      <c r="D95" s="12">
         <v>15</v>
       </c>
-      <c r="E95" s="11">
-        <v>0</v>
-      </c>
-      <c r="F95" s="12" t="s">
+      <c r="E95" s="12">
+        <v>0</v>
+      </c>
+      <c r="F95" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G95" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H95" s="9">
+      <c r="G95" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H95" s="10">
         <v>15</v>
       </c>
-      <c r="I95" s="9">
+      <c r="I95" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="96" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A96" s="9">
+      <c r="A96" s="10">
         <v>105000102</v>
       </c>
-      <c r="B96" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C96" s="10">
-        <v>20</v>
-      </c>
-      <c r="D96" s="11">
-        <v>25</v>
-      </c>
-      <c r="E96" s="11">
-        <v>0</v>
-      </c>
-      <c r="F96" s="12" t="s">
+      <c r="B96" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C96" s="11">
+        <v>20</v>
+      </c>
+      <c r="D96" s="12">
+        <v>25</v>
+      </c>
+      <c r="E96" s="12">
+        <v>0</v>
+      </c>
+      <c r="F96" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G96" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H96" s="9">
-        <v>25</v>
-      </c>
-      <c r="I96" s="9">
+      <c r="G96" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H96" s="10">
+        <v>25</v>
+      </c>
+      <c r="I96" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="97" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A97" s="9">
+      <c r="A97" s="10">
         <v>105000103</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B97" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C97" s="10">
+      <c r="C97" s="11">
         <v>50</v>
       </c>
-      <c r="D97" s="11">
+      <c r="D97" s="12">
         <v>60</v>
       </c>
-      <c r="E97" s="11">
-        <v>0</v>
-      </c>
-      <c r="F97" s="12" t="s">
+      <c r="E97" s="12">
+        <v>0</v>
+      </c>
+      <c r="F97" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G97" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H97" s="9">
+      <c r="G97" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H97" s="10">
         <v>60</v>
       </c>
-      <c r="I97" s="9">
+      <c r="I97" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="98" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A98" s="9">
+      <c r="A98" s="10">
         <v>105000104</v>
       </c>
-      <c r="B98" s="9" t="s">
+      <c r="B98" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C98" s="10">
+      <c r="C98" s="11">
         <v>250</v>
       </c>
-      <c r="D98" s="11">
+      <c r="D98" s="12">
         <v>300</v>
       </c>
-      <c r="E98" s="11">
-        <v>0</v>
-      </c>
-      <c r="F98" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G98" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H98" s="9">
+      <c r="E98" s="12">
+        <v>0</v>
+      </c>
+      <c r="F98" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G98" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H98" s="10">
         <v>300</v>
       </c>
-      <c r="I98" s="9">
+      <c r="I98" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="99" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A99" s="9">
+      <c r="A99" s="10">
         <v>105100101</v>
       </c>
-      <c r="B99" s="9" t="s">
+      <c r="B99" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C99" s="10">
+      <c r="C99" s="11">
         <v>10</v>
       </c>
-      <c r="D99" s="11">
+      <c r="D99" s="12">
         <v>15</v>
       </c>
-      <c r="E99" s="11">
-        <v>0</v>
-      </c>
-      <c r="F99" s="12" t="s">
+      <c r="E99" s="12">
+        <v>0</v>
+      </c>
+      <c r="F99" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G99" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H99" s="9">
+      <c r="G99" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H99" s="10">
         <v>15</v>
       </c>
-      <c r="I99" s="9">
+      <c r="I99" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="100" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A100" s="9">
+      <c r="A100" s="10">
         <v>105100102</v>
       </c>
-      <c r="B100" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C100" s="10">
-        <v>20</v>
-      </c>
-      <c r="D100" s="11">
-        <v>25</v>
-      </c>
-      <c r="E100" s="11">
-        <v>0</v>
-      </c>
-      <c r="F100" s="12" t="s">
+      <c r="B100" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C100" s="11">
+        <v>20</v>
+      </c>
+      <c r="D100" s="12">
+        <v>25</v>
+      </c>
+      <c r="E100" s="12">
+        <v>0</v>
+      </c>
+      <c r="F100" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G100" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H100" s="9">
-        <v>25</v>
-      </c>
-      <c r="I100" s="9">
+      <c r="G100" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H100" s="10">
+        <v>25</v>
+      </c>
+      <c r="I100" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="101" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A101" s="9">
+      <c r="A101" s="10">
         <v>105100103</v>
       </c>
-      <c r="B101" s="9" t="s">
+      <c r="B101" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C101" s="10">
+      <c r="C101" s="11">
         <v>50</v>
       </c>
-      <c r="D101" s="11">
+      <c r="D101" s="12">
         <v>60</v>
       </c>
-      <c r="E101" s="11">
-        <v>0</v>
-      </c>
-      <c r="F101" s="12" t="s">
+      <c r="E101" s="12">
+        <v>0</v>
+      </c>
+      <c r="F101" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G101" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H101" s="9">
+      <c r="G101" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H101" s="10">
         <v>60</v>
       </c>
-      <c r="I101" s="9">
+      <c r="I101" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="102" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A102" s="9">
+      <c r="A102" s="10">
         <v>105100104</v>
       </c>
-      <c r="B102" s="9" t="s">
+      <c r="B102" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C102" s="10">
+      <c r="C102" s="11">
         <v>250</v>
       </c>
-      <c r="D102" s="11">
+      <c r="D102" s="12">
         <v>300</v>
       </c>
-      <c r="E102" s="11">
-        <v>0</v>
-      </c>
-      <c r="F102" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G102" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H102" s="9">
+      <c r="E102" s="12">
+        <v>0</v>
+      </c>
+      <c r="F102" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G102" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H102" s="10">
         <v>300</v>
       </c>
-      <c r="I102" s="9">
+      <c r="I102" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="103" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A103" s="9">
+      <c r="A103" s="10">
         <v>105400101</v>
       </c>
-      <c r="B103" s="9" t="s">
+      <c r="B103" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C103" s="10">
+      <c r="C103" s="11">
         <v>10</v>
       </c>
-      <c r="D103" s="11">
+      <c r="D103" s="12">
         <v>15</v>
       </c>
-      <c r="E103" s="11">
-        <v>0</v>
-      </c>
-      <c r="F103" s="12" t="s">
+      <c r="E103" s="12">
+        <v>0</v>
+      </c>
+      <c r="F103" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G103" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H103" s="9">
+      <c r="G103" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H103" s="10">
         <v>1500</v>
       </c>
-      <c r="I103" s="9">
+      <c r="I103" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="104" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A104" s="9">
+      <c r="A104" s="10">
         <v>105400102</v>
       </c>
-      <c r="B104" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C104" s="10">
-        <v>20</v>
-      </c>
-      <c r="D104" s="11">
-        <v>25</v>
-      </c>
-      <c r="E104" s="11">
-        <v>0</v>
-      </c>
-      <c r="F104" s="12" t="s">
+      <c r="B104" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C104" s="11">
+        <v>20</v>
+      </c>
+      <c r="D104" s="12">
+        <v>25</v>
+      </c>
+      <c r="E104" s="12">
+        <v>0</v>
+      </c>
+      <c r="F104" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G104" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H104" s="9">
+      <c r="G104" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H104" s="10">
         <v>2500</v>
       </c>
-      <c r="I104" s="9">
+      <c r="I104" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="105" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A105" s="9">
+      <c r="A105" s="10">
         <v>105400103</v>
       </c>
-      <c r="B105" s="9" t="s">
+      <c r="B105" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C105" s="10">
+      <c r="C105" s="11">
         <v>50</v>
       </c>
-      <c r="D105" s="11">
+      <c r="D105" s="12">
         <v>60</v>
       </c>
-      <c r="E105" s="11">
-        <v>0</v>
-      </c>
-      <c r="F105" s="12" t="s">
+      <c r="E105" s="12">
+        <v>0</v>
+      </c>
+      <c r="F105" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G105" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H105" s="9">
+      <c r="G105" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H105" s="10">
         <v>6000</v>
       </c>
-      <c r="I105" s="9">
+      <c r="I105" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="106" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A106" s="9">
+      <c r="A106" s="10">
         <v>105400104</v>
       </c>
-      <c r="B106" s="9" t="s">
+      <c r="B106" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C106" s="10">
+      <c r="C106" s="11">
         <v>250</v>
       </c>
-      <c r="D106" s="11">
+      <c r="D106" s="12">
         <v>300</v>
       </c>
-      <c r="E106" s="11">
-        <v>0</v>
-      </c>
-      <c r="F106" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G106" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H106" s="9">
+      <c r="E106" s="12">
+        <v>0</v>
+      </c>
+      <c r="F106" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G106" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H106" s="10">
         <v>30000</v>
       </c>
-      <c r="I106" s="9">
+      <c r="I106" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="107" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A107" s="9">
+      <c r="A107" s="10">
         <v>100800101</v>
       </c>
-      <c r="B107" s="17" t="s">
+      <c r="B107" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C107" s="10">
+      <c r="C107" s="11">
         <v>10</v>
       </c>
-      <c r="D107" s="11">
+      <c r="D107" s="12">
         <v>15</v>
       </c>
-      <c r="E107" s="11">
-        <v>0</v>
-      </c>
-      <c r="F107" s="12" t="s">
+      <c r="E107" s="12">
+        <v>0</v>
+      </c>
+      <c r="F107" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G107" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H107" s="9">
+      <c r="G107" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H107" s="10">
         <v>1500</v>
       </c>
-      <c r="I107" s="9">
+      <c r="I107" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="108" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A108" s="9">
+      <c r="A108" s="10">
         <v>100800102</v>
       </c>
-      <c r="B108" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C108" s="10">
-        <v>20</v>
-      </c>
-      <c r="D108" s="11">
-        <v>25</v>
-      </c>
-      <c r="E108" s="11">
-        <v>0</v>
-      </c>
-      <c r="F108" s="12" t="s">
+      <c r="B108" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C108" s="11">
+        <v>20</v>
+      </c>
+      <c r="D108" s="12">
+        <v>25</v>
+      </c>
+      <c r="E108" s="12">
+        <v>0</v>
+      </c>
+      <c r="F108" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G108" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H108" s="9">
+      <c r="G108" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H108" s="10">
         <v>2500</v>
       </c>
-      <c r="I108" s="9">
+      <c r="I108" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="109" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A109" s="18">
+      <c r="A109" s="19">
         <v>100800103</v>
       </c>
-      <c r="B109" s="17" t="s">
+      <c r="B109" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C109" s="10">
+      <c r="C109" s="11">
         <v>50</v>
       </c>
-      <c r="D109" s="11">
+      <c r="D109" s="12">
         <v>60</v>
       </c>
-      <c r="E109" s="11">
-        <v>0</v>
-      </c>
-      <c r="F109" s="12" t="s">
+      <c r="E109" s="12">
+        <v>0</v>
+      </c>
+      <c r="F109" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G109" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H109" s="9">
+      <c r="G109" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H109" s="10">
         <v>6000</v>
       </c>
-      <c r="I109" s="9">
+      <c r="I109" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="110" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A110" s="18">
+      <c r="A110" s="19">
         <v>100800104</v>
       </c>
-      <c r="B110" s="17" t="s">
+      <c r="B110" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C110" s="10">
+      <c r="C110" s="11">
         <v>250</v>
       </c>
-      <c r="D110" s="11">
+      <c r="D110" s="12">
         <v>300</v>
       </c>
-      <c r="E110" s="11">
-        <v>0</v>
-      </c>
-      <c r="F110" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G110" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H110" s="9">
+      <c r="E110" s="12">
+        <v>0</v>
+      </c>
+      <c r="F110" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G110" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H110" s="10">
         <v>30000</v>
       </c>
-      <c r="I110" s="9">
+      <c r="I110" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="111" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A111" s="18">
+      <c r="A111" s="19">
         <v>105700101</v>
       </c>
-      <c r="B111" s="17" t="s">
+      <c r="B111" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C111" s="10">
+      <c r="C111" s="11">
         <v>10</v>
       </c>
-      <c r="D111" s="11">
+      <c r="D111" s="12">
         <v>15</v>
       </c>
-      <c r="E111" s="11">
-        <v>0</v>
-      </c>
-      <c r="F111" s="12" t="s">
+      <c r="E111" s="12">
+        <v>0</v>
+      </c>
+      <c r="F111" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G111" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H111" s="9">
+      <c r="G111" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H111" s="10">
         <v>1500</v>
       </c>
-      <c r="I111" s="9">
+      <c r="I111" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="112" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A112" s="18">
+      <c r="A112" s="19">
         <v>105700102</v>
       </c>
-      <c r="B112" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C112" s="10">
-        <v>20</v>
-      </c>
-      <c r="D112" s="11">
-        <v>25</v>
-      </c>
-      <c r="E112" s="11">
-        <v>0</v>
-      </c>
-      <c r="F112" s="12" t="s">
+      <c r="B112" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C112" s="11">
+        <v>20</v>
+      </c>
+      <c r="D112" s="12">
+        <v>25</v>
+      </c>
+      <c r="E112" s="12">
+        <v>0</v>
+      </c>
+      <c r="F112" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G112" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H112" s="9">
+      <c r="G112" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H112" s="10">
         <v>2500</v>
       </c>
-      <c r="I112" s="9">
+      <c r="I112" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="113" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A113" s="18">
+      <c r="A113" s="19">
         <v>105700103</v>
       </c>
-      <c r="B113" s="17" t="s">
+      <c r="B113" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C113" s="10">
+      <c r="C113" s="11">
         <v>50</v>
       </c>
-      <c r="D113" s="11">
+      <c r="D113" s="12">
         <v>60</v>
       </c>
-      <c r="E113" s="11">
-        <v>0</v>
-      </c>
-      <c r="F113" s="12" t="s">
+      <c r="E113" s="12">
+        <v>0</v>
+      </c>
+      <c r="F113" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G113" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H113" s="9">
+      <c r="G113" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H113" s="10">
         <v>6000</v>
       </c>
-      <c r="I113" s="9">
+      <c r="I113" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="114" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A114" s="18">
+      <c r="A114" s="19">
         <v>105700104</v>
       </c>
-      <c r="B114" s="17" t="s">
+      <c r="B114" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C114" s="10">
+      <c r="C114" s="11">
         <v>250</v>
       </c>
-      <c r="D114" s="11">
+      <c r="D114" s="12">
         <v>300</v>
       </c>
-      <c r="E114" s="11">
-        <v>0</v>
-      </c>
-      <c r="F114" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G114" s="9">
-        <v>1700</v>
-      </c>
-      <c r="H114" s="9">
+      <c r="E114" s="12">
+        <v>0</v>
+      </c>
+      <c r="F114" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G114" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H114" s="10">
         <v>30000</v>
       </c>
-      <c r="I114" s="9">
+      <c r="I114" s="10">
         <v>1440</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A115" s="18">
+      <c r="A115" s="19">
         <v>105800101</v>
       </c>
-      <c r="B115" s="9" t="s">
+      <c r="B115" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C115" s="10">
-        <v>0</v>
-      </c>
-      <c r="D115" s="11">
-        <v>0</v>
-      </c>
-      <c r="E115" s="11">
+      <c r="C115" s="11">
+        <v>0</v>
+      </c>
+      <c r="D115" s="12">
+        <v>0</v>
+      </c>
+      <c r="E115" s="12">
         <v>5000</v>
       </c>
-      <c r="F115" s="12" t="s">
+      <c r="F115" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G115" s="9">
-        <v>0</v>
-      </c>
-      <c r="H115" s="9">
+      <c r="G115" s="10">
+        <v>0</v>
+      </c>
+      <c r="H115" s="10">
         <v>50</v>
       </c>
-      <c r="I115" s="9">
+      <c r="I115" s="10">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="116" s="2" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A116" s="20">
+        <v>105500101</v>
+      </c>
+      <c r="B116" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C116" s="11">
+        <v>0</v>
+      </c>
+      <c r="D116" s="12">
+        <v>0</v>
+      </c>
+      <c r="E116" s="12">
+        <v>1000</v>
+      </c>
+      <c r="F116" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G116" s="10">
+        <v>0</v>
+      </c>
+      <c r="H116" s="10">
+        <v>1</v>
+      </c>
+      <c r="I116" s="10">
         <v>1440</v>
       </c>
     </row>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="32">
   <si>
     <t>奖池ID</t>
   </si>
@@ -414,13 +414,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -433,6 +439,11 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -441,17 +452,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1345,7 +1345,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I116"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -4419,7 +4419,7 @@
         <v>1700</v>
       </c>
       <c r="H107" s="10">
-        <v>1500</v>
+        <v>15</v>
       </c>
       <c r="I107" s="10">
         <v>1440</v>
@@ -4448,7 +4448,7 @@
         <v>1700</v>
       </c>
       <c r="H108" s="10">
-        <v>2500</v>
+        <v>25</v>
       </c>
       <c r="I108" s="10">
         <v>1440</v>
@@ -4477,7 +4477,7 @@
         <v>1700</v>
       </c>
       <c r="H109" s="10">
-        <v>6000</v>
+        <v>60</v>
       </c>
       <c r="I109" s="10">
         <v>1440</v>
@@ -4506,7 +4506,7 @@
         <v>1700</v>
       </c>
       <c r="H110" s="10">
-        <v>30000</v>
+        <v>300</v>
       </c>
       <c r="I110" s="10">
         <v>1440</v>
@@ -4535,7 +4535,7 @@
         <v>1700</v>
       </c>
       <c r="H111" s="10">
-        <v>1500</v>
+        <v>15</v>
       </c>
       <c r="I111" s="10">
         <v>1440</v>
@@ -4564,7 +4564,7 @@
         <v>1700</v>
       </c>
       <c r="H112" s="10">
-        <v>2500</v>
+        <v>25</v>
       </c>
       <c r="I112" s="10">
         <v>1440</v>
@@ -4593,7 +4593,7 @@
         <v>1700</v>
       </c>
       <c r="H113" s="10">
-        <v>6000</v>
+        <v>60</v>
       </c>
       <c r="I113" s="10">
         <v>1440</v>
@@ -4622,7 +4622,7 @@
         <v>1700</v>
       </c>
       <c r="H114" s="10">
-        <v>30000</v>
+        <v>300</v>
       </c>
       <c r="I114" s="10">
         <v>1440</v>
@@ -4683,6 +4683,151 @@
         <v>1</v>
       </c>
       <c r="I116" s="10">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="117" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A117" s="19">
+        <v>104800101</v>
+      </c>
+      <c r="B117" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C117" s="11">
+        <v>10</v>
+      </c>
+      <c r="D117" s="12">
+        <v>15</v>
+      </c>
+      <c r="E117" s="12">
+        <v>0</v>
+      </c>
+      <c r="F117" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G117" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H117" s="10">
+        <v>15</v>
+      </c>
+      <c r="I117" s="10">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="118" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A118" s="19">
+        <v>104800102</v>
+      </c>
+      <c r="B118" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C118" s="11">
+        <v>20</v>
+      </c>
+      <c r="D118" s="12">
+        <v>25</v>
+      </c>
+      <c r="E118" s="12">
+        <v>0</v>
+      </c>
+      <c r="F118" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G118" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H118" s="10">
+        <v>25</v>
+      </c>
+      <c r="I118" s="10">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="119" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A119" s="19">
+        <v>104800103</v>
+      </c>
+      <c r="B119" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C119" s="11">
+        <v>50</v>
+      </c>
+      <c r="D119" s="12">
+        <v>60</v>
+      </c>
+      <c r="E119" s="12">
+        <v>0</v>
+      </c>
+      <c r="F119" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G119" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H119" s="10">
+        <v>60</v>
+      </c>
+      <c r="I119" s="10">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="120" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A120" s="19">
+        <v>104800104</v>
+      </c>
+      <c r="B120" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C120" s="11">
+        <v>250</v>
+      </c>
+      <c r="D120" s="12">
+        <v>300</v>
+      </c>
+      <c r="E120" s="12">
+        <v>0</v>
+      </c>
+      <c r="F120" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G120" s="10">
+        <v>1700</v>
+      </c>
+      <c r="H120" s="10">
+        <v>300</v>
+      </c>
+      <c r="I120" s="10">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="121" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A121" s="20">
+        <v>105501101</v>
+      </c>
+      <c r="B121" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C121" s="11">
+        <v>0</v>
+      </c>
+      <c r="D121" s="12">
+        <v>0</v>
+      </c>
+      <c r="E121" s="12">
+        <v>1000</v>
+      </c>
+      <c r="F121" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G121" s="10">
+        <v>0</v>
+      </c>
+      <c r="H121" s="10">
+        <v>1</v>
+      </c>
+      <c r="I121" s="10">
         <v>1440</v>
       </c>
     </row>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
@@ -113,8 +113,32 @@
           </rPr>
           <t xml:space="preserve">
 玩家在奖池的累计贡献金额 =  玩家累计押注金额 * 押注抽水入奖池万分比 - 玩家累计获的此奖池奖金额
-中奖概率 = 玩家在奖池的累计贡献金额 ➗   当前真奖池金额 ➗  系数
-</t>
+中奖概率 = 玩家在奖池的累计贡献金额 ➗   当前真奖池金额 ➗  系数 × 10000
+奖池标准值是最低下注的5000倍，最高下注的250倍
+中奖模式触发概率为 0.1%
+最低下注实际中奖概率  0.1%/5000*10000/系数为1 = 0.2%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+单位：分钟</t>
         </r>
       </text>
     </comment>
@@ -390,15 +414,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -415,6 +438,7 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -908,7 +932,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -940,8 +964,8 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -953,6 +977,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1"/>
@@ -1299,8 +1326,7 @@
     <col min="5" max="5" width="20.125" customWidth="1"/>
     <col min="6" max="6" width="20.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.875" customWidth="1"/>
-    <col min="8" max="8" width="10.625" customWidth="1"/>
-    <col min="9" max="9" width="10.625" customWidth="1"/>
+    <col min="8" max="9" width="10.625" customWidth="1"/>
     <col min="10" max="11" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1406,10 +1432,10 @@
         <v>1700</v>
       </c>
       <c r="H5" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I5" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:11">
@@ -1435,10 +1461,11 @@
         <v>1700</v>
       </c>
       <c r="H6" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I6" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:11">
@@ -1464,10 +1491,11 @@
         <v>1700</v>
       </c>
       <c r="H7" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I7" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:11">
@@ -1493,10 +1521,11 @@
         <v>1700</v>
       </c>
       <c r="H8" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I8" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:11">
@@ -1521,11 +1550,11 @@
       <c r="G9" s="14">
         <v>0</v>
       </c>
-      <c r="H9" s="14">
-        <v>15</v>
+      <c r="H9" s="9">
+        <v>1</v>
       </c>
       <c r="I9" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:11">
@@ -1550,11 +1579,12 @@
       <c r="G10" s="14">
         <v>0</v>
       </c>
-      <c r="H10" s="14">
-        <v>25</v>
+      <c r="H10" s="9">
+        <v>2</v>
       </c>
       <c r="I10" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:11">
@@ -1579,11 +1609,12 @@
       <c r="G11" s="14">
         <v>0</v>
       </c>
-      <c r="H11" s="14">
-        <v>60</v>
+      <c r="H11" s="9">
+        <v>6</v>
       </c>
       <c r="I11" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:11">
@@ -1608,11 +1639,12 @@
       <c r="G12" s="14">
         <v>0</v>
       </c>
-      <c r="H12" s="14">
-        <v>300</v>
+      <c r="H12" s="9">
+        <v>30</v>
       </c>
       <c r="I12" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:11">
@@ -1638,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="9">
-        <v>1</v>
-      </c>
-      <c r="I13" s="13">
+        <v>10</v>
+      </c>
+      <c r="I13" s="18">
         <v>1440</v>
       </c>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
     </row>
     <row r="14" ht="16.5" spans="1:11">
       <c r="A14" s="9">
@@ -1669,13 +1701,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="9">
-        <v>1</v>
-      </c>
-      <c r="I14" s="13">
+        <v>10</v>
+      </c>
+      <c r="I14" s="18">
         <v>1440</v>
       </c>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
     </row>
     <row r="15" ht="16.5" spans="1:11">
       <c r="A15" s="9">
@@ -1700,10 +1732,10 @@
         <v>1700</v>
       </c>
       <c r="H15" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I15" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:11">
@@ -1729,10 +1761,11 @@
         <v>1700</v>
       </c>
       <c r="H16" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I16" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
@@ -1758,10 +1791,11 @@
         <v>1700</v>
       </c>
       <c r="H17" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I17" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
@@ -1787,10 +1821,11 @@
         <v>1700</v>
       </c>
       <c r="H18" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I18" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
@@ -1816,10 +1851,10 @@
         <v>1700</v>
       </c>
       <c r="H19" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I19" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
@@ -1845,10 +1880,11 @@
         <v>1700</v>
       </c>
       <c r="H20" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I20" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:9">
@@ -1874,10 +1910,11 @@
         <v>1700</v>
       </c>
       <c r="H21" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I21" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
@@ -1903,10 +1940,11 @@
         <v>1700</v>
       </c>
       <c r="H22" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I22" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:9">
@@ -1932,10 +1970,10 @@
         <v>1700</v>
       </c>
       <c r="H23" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I23" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:9">
@@ -1961,10 +1999,11 @@
         <v>1700</v>
       </c>
       <c r="H24" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I24" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:9">
@@ -1990,10 +2029,11 @@
         <v>1700</v>
       </c>
       <c r="H25" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I25" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:9">
@@ -2019,10 +2059,11 @@
         <v>1700</v>
       </c>
       <c r="H26" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I26" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:9">
@@ -2048,10 +2089,10 @@
         <v>1700</v>
       </c>
       <c r="H27" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I27" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:9">
@@ -2077,10 +2118,11 @@
         <v>1700</v>
       </c>
       <c r="H28" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I28" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:9">
@@ -2106,10 +2148,11 @@
         <v>1700</v>
       </c>
       <c r="H29" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I29" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:9">
@@ -2135,10 +2178,11 @@
         <v>1700</v>
       </c>
       <c r="H30" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I30" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:9">
@@ -2164,10 +2208,10 @@
         <v>1700</v>
       </c>
       <c r="H31" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I31" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:9">
@@ -2193,10 +2237,11 @@
         <v>1700</v>
       </c>
       <c r="H32" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I32" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:9">
@@ -2222,10 +2267,11 @@
         <v>1700</v>
       </c>
       <c r="H33" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I33" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:9">
@@ -2251,10 +2297,11 @@
         <v>1700</v>
       </c>
       <c r="H34" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I34" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:9">
@@ -2280,10 +2327,10 @@
         <v>1700</v>
       </c>
       <c r="H35" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I35" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:9">
@@ -2309,10 +2356,11 @@
         <v>1700</v>
       </c>
       <c r="H36" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I36" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:9">
@@ -2338,10 +2386,11 @@
         <v>1700</v>
       </c>
       <c r="H37" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I37" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:9">
@@ -2367,10 +2416,11 @@
         <v>1700</v>
       </c>
       <c r="H38" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I38" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:9">
@@ -2396,10 +2446,10 @@
         <v>1700</v>
       </c>
       <c r="H39" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I39" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:9">
@@ -2425,10 +2475,11 @@
         <v>1700</v>
       </c>
       <c r="H40" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I40" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:9">
@@ -2454,10 +2505,11 @@
         <v>1700</v>
       </c>
       <c r="H41" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I41" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:9">
@@ -2483,10 +2535,11 @@
         <v>1700</v>
       </c>
       <c r="H42" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I42" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:9">
@@ -2512,9 +2565,9 @@
         <v>0</v>
       </c>
       <c r="H43" s="9">
-        <v>1</v>
-      </c>
-      <c r="I43" s="13">
+        <v>10</v>
+      </c>
+      <c r="I43" s="18">
         <v>1440</v>
       </c>
     </row>
@@ -2541,9 +2594,9 @@
         <v>0</v>
       </c>
       <c r="H44" s="9">
-        <v>1</v>
-      </c>
-      <c r="I44" s="13">
+        <v>10</v>
+      </c>
+      <c r="I44" s="18">
         <v>1440</v>
       </c>
     </row>
@@ -2570,10 +2623,10 @@
         <v>1700</v>
       </c>
       <c r="H45" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I45" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:9">
@@ -2599,10 +2652,11 @@
         <v>1700</v>
       </c>
       <c r="H46" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I46" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:9">
@@ -2628,10 +2682,11 @@
         <v>1700</v>
       </c>
       <c r="H47" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I47" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:9">
@@ -2657,10 +2712,11 @@
         <v>1700</v>
       </c>
       <c r="H48" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I48" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:9">
@@ -2686,10 +2742,10 @@
         <v>1700</v>
       </c>
       <c r="H49" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I49" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:9">
@@ -2715,10 +2771,11 @@
         <v>1700</v>
       </c>
       <c r="H50" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I50" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:9">
@@ -2744,10 +2801,11 @@
         <v>1700</v>
       </c>
       <c r="H51" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I51" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:9">
@@ -2773,10 +2831,11 @@
         <v>1700</v>
       </c>
       <c r="H52" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I52" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:9">
@@ -2802,9 +2861,9 @@
         <v>0</v>
       </c>
       <c r="H53" s="9">
-        <v>1</v>
-      </c>
-      <c r="I53" s="13">
+        <v>10</v>
+      </c>
+      <c r="I53" s="18">
         <v>1440</v>
       </c>
     </row>
@@ -2831,10 +2890,10 @@
         <v>1700</v>
       </c>
       <c r="H54" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I54" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:9">
@@ -2860,10 +2919,11 @@
         <v>1700</v>
       </c>
       <c r="H55" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I55" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="1:9">
@@ -2889,10 +2949,11 @@
         <v>1700</v>
       </c>
       <c r="H56" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I56" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:9">
@@ -2918,10 +2979,11 @@
         <v>1700</v>
       </c>
       <c r="H57" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I57" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:9">
@@ -2947,10 +3009,10 @@
         <v>1700</v>
       </c>
       <c r="H58" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I58" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:9">
@@ -2976,10 +3038,11 @@
         <v>1700</v>
       </c>
       <c r="H59" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I59" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:9">
@@ -3005,10 +3068,11 @@
         <v>1700</v>
       </c>
       <c r="H60" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I60" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:9">
@@ -3034,10 +3098,11 @@
         <v>1700</v>
       </c>
       <c r="H61" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I61" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:9">
@@ -3063,10 +3128,10 @@
         <v>1700</v>
       </c>
       <c r="H62" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I62" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:9">
@@ -3092,10 +3157,11 @@
         <v>1700</v>
       </c>
       <c r="H63" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I63" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:9">
@@ -3121,10 +3187,11 @@
         <v>1700</v>
       </c>
       <c r="H64" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I64" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:9">
@@ -3150,10 +3217,11 @@
         <v>1700</v>
       </c>
       <c r="H65" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I65" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:9">
@@ -3179,10 +3247,10 @@
         <v>1700</v>
       </c>
       <c r="H66" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I66" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:9">
@@ -3208,10 +3276,11 @@
         <v>1700</v>
       </c>
       <c r="H67" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I67" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:9">
@@ -3237,10 +3306,11 @@
         <v>1700</v>
       </c>
       <c r="H68" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I68" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:9">
@@ -3266,10 +3336,11 @@
         <v>1700</v>
       </c>
       <c r="H69" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I69" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:9">
@@ -3295,9 +3366,9 @@
         <v>0</v>
       </c>
       <c r="H70" s="9">
-        <v>1</v>
-      </c>
-      <c r="I70" s="13">
+        <v>10</v>
+      </c>
+      <c r="I70" s="18">
         <v>1440</v>
       </c>
     </row>
@@ -3324,10 +3395,10 @@
         <v>1700</v>
       </c>
       <c r="H71" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I71" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" ht="16.5" spans="1:9">
@@ -3353,10 +3424,11 @@
         <v>1700</v>
       </c>
       <c r="H72" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I72" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:9">
@@ -3382,10 +3454,11 @@
         <v>1700</v>
       </c>
       <c r="H73" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I73" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:9">
@@ -3411,10 +3484,11 @@
         <v>1700</v>
       </c>
       <c r="H74" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I74" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:9">
@@ -3440,10 +3514,10 @@
         <v>1700</v>
       </c>
       <c r="H75" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I75" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76" ht="16.5" spans="1:9">
@@ -3469,10 +3543,11 @@
         <v>1700</v>
       </c>
       <c r="H76" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I76" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="77" ht="16.5" spans="1:9">
@@ -3498,10 +3573,11 @@
         <v>1700</v>
       </c>
       <c r="H77" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I77" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:9">
@@ -3527,10 +3603,11 @@
         <v>1700</v>
       </c>
       <c r="H78" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I78" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="79" ht="16.5" spans="1:9">
@@ -3556,10 +3633,10 @@
         <v>1700</v>
       </c>
       <c r="H79" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I79" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80" ht="16.5" spans="1:9">
@@ -3585,10 +3662,11 @@
         <v>1700</v>
       </c>
       <c r="H80" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I80" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="81" ht="16.5" spans="1:11">
@@ -3614,10 +3692,11 @@
         <v>1700</v>
       </c>
       <c r="H81" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I81" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:11">
@@ -3643,10 +3722,11 @@
         <v>1700</v>
       </c>
       <c r="H82" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I82" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:11">
@@ -3672,10 +3752,10 @@
         <v>1700</v>
       </c>
       <c r="H83" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I83" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84" ht="16.5" spans="1:11">
@@ -3701,10 +3781,11 @@
         <v>1700</v>
       </c>
       <c r="H84" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I84" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="85" ht="16.5" spans="1:11">
@@ -3730,10 +3811,11 @@
         <v>1700</v>
       </c>
       <c r="H85" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I85" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="86" ht="16.5" spans="1:11">
@@ -3759,10 +3841,11 @@
         <v>1700</v>
       </c>
       <c r="H86" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I86" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="87" ht="16.5" spans="1:11">
@@ -3788,10 +3871,10 @@
         <v>1700</v>
       </c>
       <c r="H87" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I87" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="88" ht="16.5" spans="1:11">
@@ -3817,10 +3900,11 @@
         <v>1700</v>
       </c>
       <c r="H88" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I88" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="89" ht="16.5" spans="1:11">
@@ -3846,10 +3930,11 @@
         <v>1700</v>
       </c>
       <c r="H89" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I89" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:11">
@@ -3875,10 +3960,11 @@
         <v>1700</v>
       </c>
       <c r="H90" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I90" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:11">
@@ -3904,10 +3990,10 @@
         <v>1700</v>
       </c>
       <c r="H91" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I91" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:11">
@@ -3933,10 +4019,11 @@
         <v>1700</v>
       </c>
       <c r="H92" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I92" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:11">
@@ -3962,10 +4049,11 @@
         <v>1700</v>
       </c>
       <c r="H93" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I93" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:11">
@@ -3991,10 +4079,11 @@
         <v>1700</v>
       </c>
       <c r="H94" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I94" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="95" customFormat="1" ht="16.5" spans="1:11">
@@ -4020,10 +4109,10 @@
         <v>1700</v>
       </c>
       <c r="H95" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I95" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
@@ -4051,10 +4140,11 @@
         <v>1700</v>
       </c>
       <c r="H96" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I96" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
@@ -4082,10 +4172,11 @@
         <v>1700</v>
       </c>
       <c r="H97" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I97" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
@@ -4113,10 +4204,11 @@
         <v>1700</v>
       </c>
       <c r="H98" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I98" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
@@ -4144,10 +4236,10 @@
         <v>1700</v>
       </c>
       <c r="H99" s="9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I99" s="13">
-        <v>1440</v>
+        <v>60</v>
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
@@ -4175,10 +4267,11 @@
         <v>1700</v>
       </c>
       <c r="H100" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I100" s="13">
-        <v>1440</v>
+        <f>2*60</f>
+        <v>120</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2"/>
@@ -4206,10 +4299,11 @@
         <v>1700</v>
       </c>
       <c r="H101" s="9">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I101" s="13">
-        <v>1440</v>
+        <f>5*60</f>
+        <v>300</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2"/>
@@ -4237,10 +4331,11 @@
         <v>1700</v>
       </c>
       <c r="H102" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I102" s="13">
-        <v>1440</v>
+        <f>25*60</f>
+        <v>1500</v>
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="2"/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\slot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_A0795AC57BF4F5997F800E2757D8E77EFD126536" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3FD90C-3BBD-4019-A2B0-E1F99D00EF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="3585" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="32">
   <si>
     <t>奖池ID</t>
   </si>
@@ -232,10 +232,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="179" formatCode="0_ "/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,6 +320,22 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -396,7 +412,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -406,10 +422,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -418,10 +434,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -430,10 +446,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -447,6 +463,21 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1656,7 +1687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:I122"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -5141,6 +5172,35 @@
         <v>1440</v>
       </c>
     </row>
+    <row r="122" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A122" s="19">
+        <v>105502101</v>
+      </c>
+      <c r="B122" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C122" s="21">
+        <v>0</v>
+      </c>
+      <c r="D122" s="22">
+        <v>0</v>
+      </c>
+      <c r="E122" s="22">
+        <v>1000</v>
+      </c>
+      <c r="F122" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="G122" s="20">
+        <v>0</v>
+      </c>
+      <c r="H122" s="20">
+        <v>1</v>
+      </c>
+      <c r="I122" s="20">
+        <v>1440</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="A13">

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
@@ -113,32 +113,8 @@
           </rPr>
           <t xml:space="preserve">
 玩家在奖池的累计贡献金额 =  玩家累计押注金额 * 押注抽水入奖池万分比 - 玩家累计获的此奖池奖金额
-中奖概率 = 玩家在奖池的累计贡献金额 ➗   当前真奖池金额 ➗  系数 × 10000
-奖池标准值是最低下注的5000倍，最高下注的250倍
-中奖模式触发概率为 0.1%
-最低下注实际中奖概率  0.1%/5000*10000/系数为1 = 0.2%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-单位：分钟</t>
+中奖概率 = 玩家在奖池的累计贡献金额 ➗   当前真奖池金额 ➗  系数
+</t>
         </r>
       </text>
     </comment>
@@ -414,14 +390,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -438,7 +415,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -932,7 +908,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -964,8 +940,8 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -977,9 +953,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1"/>
@@ -1326,7 +1299,8 @@
     <col min="5" max="5" width="20.125" customWidth="1"/>
     <col min="6" max="6" width="20.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.875" customWidth="1"/>
-    <col min="8" max="9" width="10.625" customWidth="1"/>
+    <col min="8" max="8" width="10.625" customWidth="1"/>
+    <col min="9" max="9" width="10.625" customWidth="1"/>
     <col min="10" max="11" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1432,10 +1406,10 @@
         <v>1700</v>
       </c>
       <c r="H5" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I5" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:11">
@@ -1461,11 +1435,10 @@
         <v>1700</v>
       </c>
       <c r="H6" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I6" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:11">
@@ -1491,11 +1464,10 @@
         <v>1700</v>
       </c>
       <c r="H7" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I7" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:11">
@@ -1521,11 +1493,10 @@
         <v>1700</v>
       </c>
       <c r="H8" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I8" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:11">
@@ -1550,11 +1521,11 @@
       <c r="G9" s="14">
         <v>0</v>
       </c>
-      <c r="H9" s="9">
-        <v>1</v>
+      <c r="H9" s="14">
+        <v>15</v>
       </c>
       <c r="I9" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:11">
@@ -1579,12 +1550,11 @@
       <c r="G10" s="14">
         <v>0</v>
       </c>
-      <c r="H10" s="9">
-        <v>2</v>
+      <c r="H10" s="14">
+        <v>25</v>
       </c>
       <c r="I10" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:11">
@@ -1609,12 +1579,11 @@
       <c r="G11" s="14">
         <v>0</v>
       </c>
-      <c r="H11" s="9">
-        <v>6</v>
+      <c r="H11" s="14">
+        <v>60</v>
       </c>
       <c r="I11" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:11">
@@ -1639,12 +1608,11 @@
       <c r="G12" s="14">
         <v>0</v>
       </c>
-      <c r="H12" s="9">
-        <v>30</v>
+      <c r="H12" s="14">
+        <v>300</v>
       </c>
       <c r="I12" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:11">
@@ -1670,13 +1638,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="9">
-        <v>10</v>
-      </c>
-      <c r="I13" s="18">
-        <v>1440</v>
-      </c>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="I13" s="13">
+        <v>1440</v>
+      </c>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
     </row>
     <row r="14" ht="16.5" spans="1:11">
       <c r="A14" s="9">
@@ -1701,13 +1669,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="9">
-        <v>10</v>
-      </c>
-      <c r="I14" s="18">
-        <v>1440</v>
-      </c>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="I14" s="13">
+        <v>1440</v>
+      </c>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
     </row>
     <row r="15" ht="16.5" spans="1:11">
       <c r="A15" s="9">
@@ -1732,10 +1700,10 @@
         <v>1700</v>
       </c>
       <c r="H15" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I15" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:11">
@@ -1761,11 +1729,10 @@
         <v>1700</v>
       </c>
       <c r="H16" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I16" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
@@ -1791,11 +1758,10 @@
         <v>1700</v>
       </c>
       <c r="H17" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I17" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
@@ -1821,11 +1787,10 @@
         <v>1700</v>
       </c>
       <c r="H18" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I18" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
@@ -1851,10 +1816,10 @@
         <v>1700</v>
       </c>
       <c r="H19" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I19" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
@@ -1880,11 +1845,10 @@
         <v>1700</v>
       </c>
       <c r="H20" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I20" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:9">
@@ -1910,11 +1874,10 @@
         <v>1700</v>
       </c>
       <c r="H21" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I21" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
@@ -1940,11 +1903,10 @@
         <v>1700</v>
       </c>
       <c r="H22" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I22" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:9">
@@ -1970,10 +1932,10 @@
         <v>1700</v>
       </c>
       <c r="H23" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I23" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:9">
@@ -1999,11 +1961,10 @@
         <v>1700</v>
       </c>
       <c r="H24" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I24" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:9">
@@ -2029,11 +1990,10 @@
         <v>1700</v>
       </c>
       <c r="H25" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I25" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:9">
@@ -2059,11 +2019,10 @@
         <v>1700</v>
       </c>
       <c r="H26" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I26" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:9">
@@ -2089,10 +2048,10 @@
         <v>1700</v>
       </c>
       <c r="H27" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I27" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:9">
@@ -2118,11 +2077,10 @@
         <v>1700</v>
       </c>
       <c r="H28" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I28" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:9">
@@ -2148,11 +2106,10 @@
         <v>1700</v>
       </c>
       <c r="H29" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I29" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:9">
@@ -2178,11 +2135,10 @@
         <v>1700</v>
       </c>
       <c r="H30" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I30" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:9">
@@ -2208,10 +2164,10 @@
         <v>1700</v>
       </c>
       <c r="H31" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I31" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:9">
@@ -2237,11 +2193,10 @@
         <v>1700</v>
       </c>
       <c r="H32" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I32" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:9">
@@ -2267,11 +2222,10 @@
         <v>1700</v>
       </c>
       <c r="H33" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I33" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:9">
@@ -2297,11 +2251,10 @@
         <v>1700</v>
       </c>
       <c r="H34" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I34" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:9">
@@ -2327,10 +2280,10 @@
         <v>1700</v>
       </c>
       <c r="H35" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I35" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:9">
@@ -2356,11 +2309,10 @@
         <v>1700</v>
       </c>
       <c r="H36" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I36" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:9">
@@ -2386,11 +2338,10 @@
         <v>1700</v>
       </c>
       <c r="H37" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I37" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:9">
@@ -2416,11 +2367,10 @@
         <v>1700</v>
       </c>
       <c r="H38" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I38" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:9">
@@ -2446,10 +2396,10 @@
         <v>1700</v>
       </c>
       <c r="H39" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I39" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:9">
@@ -2475,11 +2425,10 @@
         <v>1700</v>
       </c>
       <c r="H40" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I40" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:9">
@@ -2505,11 +2454,10 @@
         <v>1700</v>
       </c>
       <c r="H41" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I41" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:9">
@@ -2535,11 +2483,10 @@
         <v>1700</v>
       </c>
       <c r="H42" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I42" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:9">
@@ -2565,9 +2512,9 @@
         <v>0</v>
       </c>
       <c r="H43" s="9">
-        <v>10</v>
-      </c>
-      <c r="I43" s="18">
+        <v>1</v>
+      </c>
+      <c r="I43" s="13">
         <v>1440</v>
       </c>
     </row>
@@ -2594,9 +2541,9 @@
         <v>0</v>
       </c>
       <c r="H44" s="9">
-        <v>10</v>
-      </c>
-      <c r="I44" s="18">
+        <v>1</v>
+      </c>
+      <c r="I44" s="13">
         <v>1440</v>
       </c>
     </row>
@@ -2623,10 +2570,10 @@
         <v>1700</v>
       </c>
       <c r="H45" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I45" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:9">
@@ -2652,11 +2599,10 @@
         <v>1700</v>
       </c>
       <c r="H46" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I46" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:9">
@@ -2682,11 +2628,10 @@
         <v>1700</v>
       </c>
       <c r="H47" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I47" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:9">
@@ -2712,11 +2657,10 @@
         <v>1700</v>
       </c>
       <c r="H48" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I48" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:9">
@@ -2742,10 +2686,10 @@
         <v>1700</v>
       </c>
       <c r="H49" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I49" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:9">
@@ -2771,11 +2715,10 @@
         <v>1700</v>
       </c>
       <c r="H50" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I50" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:9">
@@ -2801,11 +2744,10 @@
         <v>1700</v>
       </c>
       <c r="H51" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I51" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:9">
@@ -2831,11 +2773,10 @@
         <v>1700</v>
       </c>
       <c r="H52" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I52" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:9">
@@ -2861,9 +2802,9 @@
         <v>0</v>
       </c>
       <c r="H53" s="9">
-        <v>10</v>
-      </c>
-      <c r="I53" s="18">
+        <v>1</v>
+      </c>
+      <c r="I53" s="13">
         <v>1440</v>
       </c>
     </row>
@@ -2890,10 +2831,10 @@
         <v>1700</v>
       </c>
       <c r="H54" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I54" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:9">
@@ -2919,11 +2860,10 @@
         <v>1700</v>
       </c>
       <c r="H55" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I55" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="1:9">
@@ -2949,11 +2889,10 @@
         <v>1700</v>
       </c>
       <c r="H56" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I56" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:9">
@@ -2979,11 +2918,10 @@
         <v>1700</v>
       </c>
       <c r="H57" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I57" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:9">
@@ -3009,10 +2947,10 @@
         <v>1700</v>
       </c>
       <c r="H58" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I58" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:9">
@@ -3038,11 +2976,10 @@
         <v>1700</v>
       </c>
       <c r="H59" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I59" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:9">
@@ -3068,11 +3005,10 @@
         <v>1700</v>
       </c>
       <c r="H60" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I60" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:9">
@@ -3098,11 +3034,10 @@
         <v>1700</v>
       </c>
       <c r="H61" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I61" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:9">
@@ -3128,10 +3063,10 @@
         <v>1700</v>
       </c>
       <c r="H62" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I62" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:9">
@@ -3157,11 +3092,10 @@
         <v>1700</v>
       </c>
       <c r="H63" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I63" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:9">
@@ -3187,11 +3121,10 @@
         <v>1700</v>
       </c>
       <c r="H64" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I64" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:9">
@@ -3217,11 +3150,10 @@
         <v>1700</v>
       </c>
       <c r="H65" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I65" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:9">
@@ -3247,10 +3179,10 @@
         <v>1700</v>
       </c>
       <c r="H66" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I66" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:9">
@@ -3276,11 +3208,10 @@
         <v>1700</v>
       </c>
       <c r="H67" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I67" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:9">
@@ -3306,11 +3237,10 @@
         <v>1700</v>
       </c>
       <c r="H68" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I68" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:9">
@@ -3336,11 +3266,10 @@
         <v>1700</v>
       </c>
       <c r="H69" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I69" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:9">
@@ -3366,9 +3295,9 @@
         <v>0</v>
       </c>
       <c r="H70" s="9">
-        <v>10</v>
-      </c>
-      <c r="I70" s="18">
+        <v>1</v>
+      </c>
+      <c r="I70" s="13">
         <v>1440</v>
       </c>
     </row>
@@ -3395,10 +3324,10 @@
         <v>1700</v>
       </c>
       <c r="H71" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I71" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="72" ht="16.5" spans="1:9">
@@ -3424,11 +3353,10 @@
         <v>1700</v>
       </c>
       <c r="H72" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I72" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:9">
@@ -3454,11 +3382,10 @@
         <v>1700</v>
       </c>
       <c r="H73" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I73" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:9">
@@ -3484,11 +3411,10 @@
         <v>1700</v>
       </c>
       <c r="H74" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I74" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:9">
@@ -3514,10 +3440,10 @@
         <v>1700</v>
       </c>
       <c r="H75" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I75" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="76" ht="16.5" spans="1:9">
@@ -3543,11 +3469,10 @@
         <v>1700</v>
       </c>
       <c r="H76" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I76" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="77" ht="16.5" spans="1:9">
@@ -3573,11 +3498,10 @@
         <v>1700</v>
       </c>
       <c r="H77" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I77" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:9">
@@ -3603,11 +3527,10 @@
         <v>1700</v>
       </c>
       <c r="H78" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I78" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="79" ht="16.5" spans="1:9">
@@ -3633,10 +3556,10 @@
         <v>1700</v>
       </c>
       <c r="H79" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I79" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="80" ht="16.5" spans="1:9">
@@ -3662,11 +3585,10 @@
         <v>1700</v>
       </c>
       <c r="H80" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I80" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="81" ht="16.5" spans="1:11">
@@ -3692,11 +3614,10 @@
         <v>1700</v>
       </c>
       <c r="H81" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I81" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:11">
@@ -3722,11 +3643,10 @@
         <v>1700</v>
       </c>
       <c r="H82" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I82" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:11">
@@ -3752,10 +3672,10 @@
         <v>1700</v>
       </c>
       <c r="H83" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I83" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="84" ht="16.5" spans="1:11">
@@ -3781,11 +3701,10 @@
         <v>1700</v>
       </c>
       <c r="H84" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I84" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="85" ht="16.5" spans="1:11">
@@ -3811,11 +3730,10 @@
         <v>1700</v>
       </c>
       <c r="H85" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I85" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="86" ht="16.5" spans="1:11">
@@ -3841,11 +3759,10 @@
         <v>1700</v>
       </c>
       <c r="H86" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I86" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="87" ht="16.5" spans="1:11">
@@ -3871,10 +3788,10 @@
         <v>1700</v>
       </c>
       <c r="H87" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I87" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="88" ht="16.5" spans="1:11">
@@ -3900,11 +3817,10 @@
         <v>1700</v>
       </c>
       <c r="H88" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I88" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="89" ht="16.5" spans="1:11">
@@ -3930,11 +3846,10 @@
         <v>1700</v>
       </c>
       <c r="H89" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I89" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:11">
@@ -3960,11 +3875,10 @@
         <v>1700</v>
       </c>
       <c r="H90" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I90" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:11">
@@ -3990,10 +3904,10 @@
         <v>1700</v>
       </c>
       <c r="H91" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I91" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:11">
@@ -4019,11 +3933,10 @@
         <v>1700</v>
       </c>
       <c r="H92" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I92" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:11">
@@ -4049,11 +3962,10 @@
         <v>1700</v>
       </c>
       <c r="H93" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I93" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:11">
@@ -4079,11 +3991,10 @@
         <v>1700</v>
       </c>
       <c r="H94" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I94" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="95" customFormat="1" ht="16.5" spans="1:11">
@@ -4109,10 +4020,10 @@
         <v>1700</v>
       </c>
       <c r="H95" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I95" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
@@ -4140,11 +4051,10 @@
         <v>1700</v>
       </c>
       <c r="H96" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I96" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
@@ -4172,11 +4082,10 @@
         <v>1700</v>
       </c>
       <c r="H97" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I97" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
@@ -4204,11 +4113,10 @@
         <v>1700</v>
       </c>
       <c r="H98" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I98" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
@@ -4236,10 +4144,10 @@
         <v>1700</v>
       </c>
       <c r="H99" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I99" s="13">
-        <v>60</v>
+        <v>1440</v>
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
@@ -4267,11 +4175,10 @@
         <v>1700</v>
       </c>
       <c r="H100" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I100" s="13">
-        <f>2*60</f>
-        <v>120</v>
+        <v>1440</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2"/>
@@ -4299,11 +4206,10 @@
         <v>1700</v>
       </c>
       <c r="H101" s="9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I101" s="13">
-        <f>5*60</f>
-        <v>300</v>
+        <v>1440</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2"/>
@@ -4331,11 +4237,10 @@
         <v>1700</v>
       </c>
       <c r="H102" s="9">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I102" s="13">
-        <f>25*60</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="2"/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\slot\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3FD90C-3BBD-4019-A2B0-E1F99D00EF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="3585" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="13980" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
@@ -33,14 +27,14 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
     <author>Administrator</author>
     <author>Microsoft Office User</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -65,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="D1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -87,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -105,17 +99,17 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G1" authorId="1">
       <text/>
     </comment>
-    <comment ref="H1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="H1" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 玩家在奖池的累计贡献金额 =  玩家累计押注金额 * 押注抽水入奖池万分比 - 玩家累计获的此奖池奖金额
@@ -129,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="32">
   <si>
     <t>奖池ID</t>
   </si>
@@ -230,12 +224,16 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="6">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,22 +270,172 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -300,6 +448,7 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -310,34 +459,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -352,12 +484,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -406,11 +724,253 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -464,948 +1024,76 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="51">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 73" xfId="50"/>
   </cellStyles>
-  <dxfs count="93">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1421,9 +1109,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1681,14 +1366,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I122"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I130"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -1700,7 +1385,7 @@
     <col min="8" max="8" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" ht="16.5" spans="1:9">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1727,7 +1412,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1753,7 +1438,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1779,7 +1464,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" ht="16.5" spans="1:9">
       <c r="A5" s="8">
         <v>100100101</v>
       </c>
@@ -1808,7 +1493,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="6" ht="16.5" spans="1:9">
       <c r="A6" s="8">
         <v>100100102</v>
       </c>
@@ -1837,7 +1522,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="7" ht="16.5" spans="1:9">
       <c r="A7" s="8">
         <v>100100103</v>
       </c>
@@ -1866,7 +1551,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="8" ht="16.5" spans="1:9">
       <c r="A8" s="8">
         <v>100100104</v>
       </c>
@@ -1895,7 +1580,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="9" ht="16.5" spans="1:9">
       <c r="A9" s="12">
         <v>100300101</v>
       </c>
@@ -1924,7 +1609,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="10" ht="16.5" spans="1:9">
       <c r="A10" s="12">
         <v>100300102</v>
       </c>
@@ -1953,7 +1638,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="11" ht="16.5" spans="1:9">
       <c r="A11" s="12">
         <v>100300103</v>
       </c>
@@ -1982,7 +1667,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="12" ht="16.5" spans="1:9">
       <c r="A12" s="12">
         <v>100300104</v>
       </c>
@@ -2011,7 +1696,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="13" ht="16.5" spans="1:9">
       <c r="A13" s="8">
         <v>101200101</v>
       </c>
@@ -2040,7 +1725,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="14" ht="16.5" spans="1:9">
       <c r="A14" s="8">
         <v>101400101</v>
       </c>
@@ -2069,7 +1754,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="15" ht="16.5" spans="1:9">
       <c r="A15" s="8">
         <v>102400101</v>
       </c>
@@ -2098,7 +1783,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="16" ht="16.5" spans="1:9">
       <c r="A16" s="8">
         <v>102400102</v>
       </c>
@@ -2127,7 +1812,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="17" ht="16.5" spans="1:9">
       <c r="A17" s="8">
         <v>102400103</v>
       </c>
@@ -2156,7 +1841,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="18" ht="16.5" spans="1:9">
       <c r="A18" s="8">
         <v>102400104</v>
       </c>
@@ -2185,7 +1870,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="19" ht="16.5" spans="1:9">
       <c r="A19" s="8">
         <v>101700101</v>
       </c>
@@ -2214,7 +1899,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="20" ht="16.5" spans="1:9">
       <c r="A20" s="8">
         <v>101700102</v>
       </c>
@@ -2243,7 +1928,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="21" ht="16.5" spans="1:9">
       <c r="A21" s="8">
         <v>101700103</v>
       </c>
@@ -2272,7 +1957,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="22" ht="16.5" spans="1:9">
       <c r="A22" s="8">
         <v>101700104</v>
       </c>
@@ -2301,7 +1986,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="23" ht="16.5" spans="1:9">
       <c r="A23" s="8">
         <v>102200101</v>
       </c>
@@ -2330,7 +2015,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="24" ht="16.5" spans="1:9">
       <c r="A24" s="8">
         <v>102200102</v>
       </c>
@@ -2359,7 +2044,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="25" ht="16.5" spans="1:9">
       <c r="A25" s="8">
         <v>102200103</v>
       </c>
@@ -2388,7 +2073,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="26" ht="16.5" spans="1:9">
       <c r="A26" s="8">
         <v>102200104</v>
       </c>
@@ -2417,7 +2102,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="27" ht="16.5" spans="1:9">
       <c r="A27" s="8">
         <v>102100101</v>
       </c>
@@ -2446,7 +2131,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="28" ht="16.5" spans="1:9">
       <c r="A28" s="8">
         <v>102100102</v>
       </c>
@@ -2475,7 +2160,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="29" ht="16.5" spans="1:9">
       <c r="A29" s="8">
         <v>102100103</v>
       </c>
@@ -2504,7 +2189,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="30" ht="16.5" spans="1:9">
       <c r="A30" s="8">
         <v>102100104</v>
       </c>
@@ -2533,7 +2218,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="31" ht="16.5" spans="1:9">
       <c r="A31" s="8">
         <v>101800101</v>
       </c>
@@ -2562,7 +2247,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="32" ht="16.5" spans="1:9">
       <c r="A32" s="8">
         <v>101800102</v>
       </c>
@@ -2591,7 +2276,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="33" ht="16.5" spans="1:9">
       <c r="A33" s="8">
         <v>101800103</v>
       </c>
@@ -2620,7 +2305,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="34" ht="16.5" spans="1:9">
       <c r="A34" s="8">
         <v>101800104</v>
       </c>
@@ -2649,7 +2334,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="35" ht="16.5" spans="1:9">
       <c r="A35" s="8">
         <v>102500101</v>
       </c>
@@ -2678,7 +2363,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="36" ht="16.5" spans="1:9">
       <c r="A36" s="8">
         <v>102500102</v>
       </c>
@@ -2707,7 +2392,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="37" ht="16.5" spans="1:9">
       <c r="A37" s="8">
         <v>102500103</v>
       </c>
@@ -2736,7 +2421,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="38" ht="16.5" spans="1:9">
       <c r="A38" s="8">
         <v>102500104</v>
       </c>
@@ -2765,7 +2450,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="39" ht="16.5" spans="1:9">
       <c r="A39" s="8">
         <v>102300101</v>
       </c>
@@ -2794,7 +2479,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="40" ht="16.5" spans="1:9">
       <c r="A40" s="8">
         <v>102300102</v>
       </c>
@@ -2823,7 +2508,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="41" ht="16.5" spans="1:9">
       <c r="A41" s="8">
         <v>102300103</v>
       </c>
@@ -2852,7 +2537,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="42" ht="16.5" spans="1:9">
       <c r="A42" s="8">
         <v>102300104</v>
       </c>
@@ -2881,7 +2566,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="43" ht="16.5" spans="1:9">
       <c r="A43" s="8">
         <v>103400101</v>
       </c>
@@ -2910,7 +2595,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="44" ht="16.5" spans="1:9">
       <c r="A44" s="8">
         <v>103401101</v>
       </c>
@@ -2939,7 +2624,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="45" ht="16.5" spans="1:9">
       <c r="A45" s="8">
         <v>103500101</v>
       </c>
@@ -2968,7 +2653,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="46" ht="16.5" spans="1:9">
       <c r="A46" s="8">
         <v>103500102</v>
       </c>
@@ -2997,7 +2682,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="47" ht="16.5" spans="1:9">
       <c r="A47" s="8">
         <v>103500103</v>
       </c>
@@ -3026,7 +2711,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="48" ht="16.5" spans="1:9">
       <c r="A48" s="8">
         <v>103500104</v>
       </c>
@@ -3055,7 +2740,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="49" ht="16.5" spans="1:9">
       <c r="A49" s="8">
         <v>103501101</v>
       </c>
@@ -3084,7 +2769,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="50" ht="16.5" spans="1:9">
       <c r="A50" s="8">
         <v>103501102</v>
       </c>
@@ -3113,7 +2798,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="51" ht="16.5" spans="1:9">
       <c r="A51" s="8">
         <v>103501103</v>
       </c>
@@ -3142,7 +2827,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="52" ht="16.5" spans="1:9">
       <c r="A52" s="8">
         <v>103501104</v>
       </c>
@@ -3171,7 +2856,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="53" ht="16.5" spans="1:9">
       <c r="A53" s="8">
         <v>103600101</v>
       </c>
@@ -3200,7 +2885,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="54" ht="16.5" spans="1:9">
       <c r="A54" s="8">
         <v>102800101</v>
       </c>
@@ -3229,7 +2914,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="55" ht="16.5" spans="1:9">
       <c r="A55" s="8">
         <v>102800102</v>
       </c>
@@ -3258,7 +2943,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="56" ht="16.5" spans="1:9">
       <c r="A56" s="8">
         <v>102800103</v>
       </c>
@@ -3287,7 +2972,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="57" ht="16.5" spans="1:9">
       <c r="A57" s="8">
         <v>102800104</v>
       </c>
@@ -3316,7 +3001,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="58" ht="16.5" spans="1:9">
       <c r="A58" s="8">
         <v>102000101</v>
       </c>
@@ -3345,7 +3030,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="59" ht="16.5" spans="1:9">
       <c r="A59" s="8">
         <v>102000102</v>
       </c>
@@ -3374,7 +3059,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="60" ht="16.5" spans="1:9">
       <c r="A60" s="8">
         <v>102000103</v>
       </c>
@@ -3403,7 +3088,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="61" ht="16.5" spans="1:9">
       <c r="A61" s="8">
         <v>102000104</v>
       </c>
@@ -3432,7 +3117,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="62" ht="16.5" spans="1:9">
       <c r="A62" s="8">
         <v>103800101</v>
       </c>
@@ -3461,7 +3146,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="63" ht="16.5" spans="1:9">
       <c r="A63" s="8">
         <v>103800102</v>
       </c>
@@ -3490,7 +3175,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="64" ht="16.5" spans="1:9">
       <c r="A64" s="8">
         <v>103800103</v>
       </c>
@@ -3519,7 +3204,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="65" ht="16.5" spans="1:9">
       <c r="A65" s="8">
         <v>103800104</v>
       </c>
@@ -3548,7 +3233,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="66" ht="16.5" spans="1:9">
       <c r="A66" s="8">
         <v>102700101</v>
       </c>
@@ -3577,7 +3262,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="67" ht="16.5" spans="1:9">
       <c r="A67" s="8">
         <v>102700102</v>
       </c>
@@ -3606,7 +3291,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="68" ht="16.5" spans="1:9">
       <c r="A68" s="8">
         <v>102700103</v>
       </c>
@@ -3635,7 +3320,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="69" ht="16.5" spans="1:9">
       <c r="A69" s="8">
         <v>102700104</v>
       </c>
@@ -3664,7 +3349,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="70" ht="16.5" spans="1:9">
       <c r="A70" s="8">
         <v>103700101</v>
       </c>
@@ -3693,7 +3378,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="71" ht="16.5" spans="1:9">
       <c r="A71" s="8">
         <v>103100101</v>
       </c>
@@ -3722,7 +3407,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="72" ht="16.5" spans="1:9">
       <c r="A72" s="8">
         <v>103100102</v>
       </c>
@@ -3751,7 +3436,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="73" ht="16.5" spans="1:9">
       <c r="A73" s="8">
         <v>103100103</v>
       </c>
@@ -3780,7 +3465,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="74" ht="16.5" spans="1:9">
       <c r="A74" s="8">
         <v>103100104</v>
       </c>
@@ -3809,7 +3494,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="75" ht="16.5" spans="1:9">
       <c r="A75" s="8">
         <v>104000101</v>
       </c>
@@ -3838,7 +3523,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="76" ht="16.5" spans="1:9">
       <c r="A76" s="8">
         <v>104000102</v>
       </c>
@@ -3867,7 +3552,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="77" ht="16.5" spans="1:9">
       <c r="A77" s="8">
         <v>104000103</v>
       </c>
@@ -3896,7 +3581,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="78" ht="16.5" spans="1:9">
       <c r="A78" s="8">
         <v>104000104</v>
       </c>
@@ -3925,7 +3610,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="79" ht="16.5" spans="1:9">
       <c r="A79" s="8">
         <v>103900101</v>
       </c>
@@ -3954,7 +3639,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="80" ht="16.5" spans="1:9">
       <c r="A80" s="8">
         <v>103900102</v>
       </c>
@@ -3983,7 +3668,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="81" ht="16.5" spans="1:9">
       <c r="A81" s="8">
         <v>103900103</v>
       </c>
@@ -4012,7 +3697,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="82" ht="16.5" spans="1:9">
       <c r="A82" s="8">
         <v>103900104</v>
       </c>
@@ -4041,7 +3726,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="83" ht="16.5" spans="1:9">
       <c r="A83" s="8">
         <v>101600101</v>
       </c>
@@ -4070,7 +3755,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="84" ht="16.5" spans="1:9">
       <c r="A84" s="8">
         <v>101600102</v>
       </c>
@@ -4099,7 +3784,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="85" ht="16.5" spans="1:9">
       <c r="A85" s="8">
         <v>101600103</v>
       </c>
@@ -4128,7 +3813,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="86" ht="16.5" spans="1:9">
       <c r="A86" s="8">
         <v>101600104</v>
       </c>
@@ -4157,7 +3842,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="87" ht="16.5" spans="1:9">
       <c r="A87" s="8">
         <v>101500101</v>
       </c>
@@ -4186,7 +3871,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="88" ht="16.5" spans="1:9">
       <c r="A88" s="8">
         <v>101500102</v>
       </c>
@@ -4215,7 +3900,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="89" ht="16.5" spans="1:9">
       <c r="A89" s="8">
         <v>101500103</v>
       </c>
@@ -4244,7 +3929,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="90" ht="16.5" spans="1:9">
       <c r="A90" s="8">
         <v>101500104</v>
       </c>
@@ -4273,7 +3958,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="91" ht="16.5" spans="1:9">
       <c r="A91" s="8">
         <v>102600101</v>
       </c>
@@ -4302,7 +3987,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="92" ht="16.5" spans="1:9">
       <c r="A92" s="8">
         <v>102600102</v>
       </c>
@@ -4331,7 +4016,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="93" ht="16.5" spans="1:9">
       <c r="A93" s="8">
         <v>102600103</v>
       </c>
@@ -4360,7 +4045,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="94" ht="16.5" spans="1:9">
       <c r="A94" s="8">
         <v>102600104</v>
       </c>
@@ -4389,7 +4074,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="95" ht="16.5" spans="1:9">
       <c r="A95" s="8">
         <v>105000101</v>
       </c>
@@ -4418,7 +4103,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="96" ht="16.5" spans="1:9">
       <c r="A96" s="8">
         <v>105000102</v>
       </c>
@@ -4447,7 +4132,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="97" ht="16.5" spans="1:9">
       <c r="A97" s="8">
         <v>105000103</v>
       </c>
@@ -4476,7 +4161,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="98" ht="16.5" spans="1:9">
       <c r="A98" s="8">
         <v>105000104</v>
       </c>
@@ -4505,7 +4190,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="99" ht="16.5" spans="1:9">
       <c r="A99" s="8">
         <v>105100101</v>
       </c>
@@ -4534,7 +4219,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="100" ht="16.5" spans="1:9">
       <c r="A100" s="8">
         <v>105100102</v>
       </c>
@@ -4563,7 +4248,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="101" ht="16.5" spans="1:9">
       <c r="A101" s="8">
         <v>105100103</v>
       </c>
@@ -4592,7 +4277,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="102" ht="16.5" spans="1:9">
       <c r="A102" s="8">
         <v>105100104</v>
       </c>
@@ -4621,7 +4306,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="103" ht="16.5" spans="1:9">
       <c r="A103" s="8">
         <v>105400101</v>
       </c>
@@ -4650,7 +4335,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="104" ht="16.5" spans="1:9">
       <c r="A104" s="8">
         <v>105400102</v>
       </c>
@@ -4679,7 +4364,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="105" ht="16.5" spans="1:9">
       <c r="A105" s="8">
         <v>105400103</v>
       </c>
@@ -4708,7 +4393,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="106" ht="16.5" spans="1:9">
       <c r="A106" s="8">
         <v>105400104</v>
       </c>
@@ -4737,7 +4422,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="107" ht="16.5" spans="1:9">
       <c r="A107" s="8">
         <v>100800101</v>
       </c>
@@ -4766,7 +4451,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="108" ht="16.5" spans="1:9">
       <c r="A108" s="8">
         <v>100800102</v>
       </c>
@@ -4795,7 +4480,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="109" ht="16.5" spans="1:9">
       <c r="A109" s="17">
         <v>100800103</v>
       </c>
@@ -4824,7 +4509,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="110" ht="16.5" spans="1:9">
       <c r="A110" s="17">
         <v>100800104</v>
       </c>
@@ -4853,7 +4538,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="111" ht="16.5" spans="1:9">
       <c r="A111" s="17">
         <v>105700101</v>
       </c>
@@ -4882,7 +4567,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="112" ht="16.5" spans="1:9">
       <c r="A112" s="17">
         <v>105700102</v>
       </c>
@@ -4911,7 +4596,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="113" ht="16.5" spans="1:9">
       <c r="A113" s="17">
         <v>105700103</v>
       </c>
@@ -4940,7 +4625,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="114" ht="16.5" spans="1:9">
       <c r="A114" s="17">
         <v>105700104</v>
       </c>
@@ -4969,7 +4654,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="115" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="115" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A115" s="17">
         <v>105800101</v>
       </c>
@@ -4998,7 +4683,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="116" spans="1:9" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="116" s="2" customFormat="1" ht="16.5" spans="1:9">
       <c r="A116" s="18">
         <v>105500101</v>
       </c>
@@ -5027,7 +4712,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="117" ht="16.5" spans="1:9">
       <c r="A117" s="17">
         <v>104800101</v>
       </c>
@@ -5056,7 +4741,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="118" ht="16.5" spans="1:9">
       <c r="A118" s="17">
         <v>104800102</v>
       </c>
@@ -5085,7 +4770,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="119" ht="16.5" spans="1:9">
       <c r="A119" s="17">
         <v>104800103</v>
       </c>
@@ -5114,7 +4799,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="120" ht="16.5" spans="1:9">
       <c r="A120" s="17">
         <v>104800104</v>
       </c>
@@ -5143,7 +4828,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="121" ht="16.5" spans="1:9">
       <c r="A121" s="18">
         <v>105501101</v>
       </c>
@@ -5172,7 +4857,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="122" ht="16.5" spans="1:9">
       <c r="A122" s="19">
         <v>105502101</v>
       </c>
@@ -5201,288 +4886,520 @@
         <v>1440</v>
       </c>
     </row>
+    <row r="123" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A123" s="17">
+        <v>104100101</v>
+      </c>
+      <c r="B123" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C123" s="9">
+        <v>10</v>
+      </c>
+      <c r="D123" s="10">
+        <v>15</v>
+      </c>
+      <c r="E123" s="10">
+        <v>0</v>
+      </c>
+      <c r="F123" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G123" s="8">
+        <v>1700</v>
+      </c>
+      <c r="H123" s="8">
+        <v>15</v>
+      </c>
+      <c r="I123" s="8">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="124" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A124" s="17">
+        <v>104100102</v>
+      </c>
+      <c r="B124" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C124" s="9">
+        <v>20</v>
+      </c>
+      <c r="D124" s="10">
+        <v>25</v>
+      </c>
+      <c r="E124" s="10">
+        <v>0</v>
+      </c>
+      <c r="F124" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G124" s="8">
+        <v>1700</v>
+      </c>
+      <c r="H124" s="8">
+        <v>25</v>
+      </c>
+      <c r="I124" s="8">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="125" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A125" s="17">
+        <v>104100103</v>
+      </c>
+      <c r="B125" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C125" s="9">
+        <v>50</v>
+      </c>
+      <c r="D125" s="10">
+        <v>60</v>
+      </c>
+      <c r="E125" s="10">
+        <v>0</v>
+      </c>
+      <c r="F125" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G125" s="8">
+        <v>1700</v>
+      </c>
+      <c r="H125" s="8">
+        <v>60</v>
+      </c>
+      <c r="I125" s="8">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="126" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A126" s="17">
+        <v>104100104</v>
+      </c>
+      <c r="B126" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C126" s="9">
+        <v>250</v>
+      </c>
+      <c r="D126" s="10">
+        <v>300</v>
+      </c>
+      <c r="E126" s="10">
+        <v>0</v>
+      </c>
+      <c r="F126" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G126" s="8">
+        <v>1700</v>
+      </c>
+      <c r="H126" s="8">
+        <v>300</v>
+      </c>
+      <c r="I126" s="8">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="127" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A127" s="17">
+        <v>104200101</v>
+      </c>
+      <c r="B127" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C127" s="9">
+        <v>10</v>
+      </c>
+      <c r="D127" s="10">
+        <v>15</v>
+      </c>
+      <c r="E127" s="10">
+        <v>0</v>
+      </c>
+      <c r="F127" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G127" s="8">
+        <v>1700</v>
+      </c>
+      <c r="H127" s="8">
+        <v>15</v>
+      </c>
+      <c r="I127" s="8">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="128" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A128" s="17">
+        <v>104200102</v>
+      </c>
+      <c r="B128" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C128" s="9">
+        <v>20</v>
+      </c>
+      <c r="D128" s="10">
+        <v>25</v>
+      </c>
+      <c r="E128" s="10">
+        <v>0</v>
+      </c>
+      <c r="F128" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G128" s="8">
+        <v>1700</v>
+      </c>
+      <c r="H128" s="8">
+        <v>25</v>
+      </c>
+      <c r="I128" s="8">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="129" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A129" s="17">
+        <v>104200103</v>
+      </c>
+      <c r="B129" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C129" s="9">
+        <v>50</v>
+      </c>
+      <c r="D129" s="10">
+        <v>60</v>
+      </c>
+      <c r="E129" s="10">
+        <v>0</v>
+      </c>
+      <c r="F129" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G129" s="8">
+        <v>1700</v>
+      </c>
+      <c r="H129" s="8">
+        <v>60</v>
+      </c>
+      <c r="I129" s="8">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="130" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A130" s="17">
+        <v>104200104</v>
+      </c>
+      <c r="B130" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C130" s="9">
+        <v>250</v>
+      </c>
+      <c r="D130" s="10">
+        <v>300</v>
+      </c>
+      <c r="E130" s="10">
+        <v>0</v>
+      </c>
+      <c r="F130" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G130" s="8">
+        <v>1700</v>
+      </c>
+      <c r="H130" s="8">
+        <v>300</v>
+      </c>
+      <c r="I130" s="8">
+        <v>1440</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="105"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="97"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="92" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="100"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="91" priority="104"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19:A21">
-    <cfRule type="duplicateValues" dxfId="90" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="104"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B18">
+    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="89" priority="93"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A25">
-    <cfRule type="duplicateValues" dxfId="88" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="93"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="87" priority="89"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27:A29">
-    <cfRule type="duplicateValues" dxfId="86" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30">
-    <cfRule type="duplicateValues" dxfId="85" priority="85"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31:A34">
-    <cfRule type="duplicateValues" dxfId="84" priority="82"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A38">
-    <cfRule type="duplicateValues" dxfId="83" priority="78"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A39:A52">
-    <cfRule type="duplicateValues" dxfId="82" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="0" priority="76"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44">
+    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52">
+    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53">
-    <cfRule type="duplicateValues" dxfId="81" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="72"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53">
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
-    <cfRule type="duplicateValues" dxfId="80" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B54">
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
-    <cfRule type="duplicateValues" dxfId="79" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55">
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
-    <cfRule type="duplicateValues" dxfId="78" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B56">
+    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
-    <cfRule type="duplicateValues" dxfId="77" priority="57"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A58:A61">
-    <cfRule type="duplicateValues" dxfId="76" priority="52"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A62:A65">
-    <cfRule type="duplicateValues" dxfId="75" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A66:A69">
-    <cfRule type="duplicateValues" dxfId="74" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B57">
+    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B58">
+    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59">
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B60">
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B61">
+    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B62">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B64">
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B65">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B66">
+    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B68">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B69">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70">
-    <cfRule type="duplicateValues" dxfId="73" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A71:A74">
-    <cfRule type="duplicateValues" dxfId="72" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A75:A78">
-    <cfRule type="duplicateValues" dxfId="71" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A79:A82">
-    <cfRule type="duplicateValues" dxfId="70" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A83:A86">
-    <cfRule type="duplicateValues" dxfId="69" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A87:A90">
-    <cfRule type="duplicateValues" dxfId="68" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A91:A94">
-    <cfRule type="duplicateValues" dxfId="67" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1 A5:B7">
-    <cfRule type="duplicateValues" dxfId="66" priority="106"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A8:B8">
-    <cfRule type="duplicateValues" dxfId="65" priority="105"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:B11">
-    <cfRule type="duplicateValues" dxfId="64" priority="98"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A12:B12">
-    <cfRule type="duplicateValues" dxfId="63" priority="97"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15:B17">
-    <cfRule type="duplicateValues" dxfId="62" priority="96"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:B18">
-    <cfRule type="duplicateValues" dxfId="61" priority="95"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="60" priority="99"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="59" priority="101"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
-    <cfRule type="duplicateValues" dxfId="58" priority="92"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="57" priority="91"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B25">
-    <cfRule type="duplicateValues" dxfId="56" priority="88"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="55" priority="87"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B29">
-    <cfRule type="duplicateValues" dxfId="54" priority="84"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="53" priority="83"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B33">
-    <cfRule type="duplicateValues" dxfId="52" priority="80"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="51" priority="79"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B37">
-    <cfRule type="duplicateValues" dxfId="50" priority="77"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="49" priority="76"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B39:B41">
-    <cfRule type="duplicateValues" dxfId="48" priority="74"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42:B43">
-    <cfRule type="duplicateValues" dxfId="47" priority="73"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B45:B47">
-    <cfRule type="duplicateValues" dxfId="45" priority="70"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="44" priority="69"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B49:B51">
-    <cfRule type="duplicateValues" dxfId="43" priority="68"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="42" priority="67"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="41" priority="71"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="40" priority="56"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="39" priority="55"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B56">
-    <cfRule type="duplicateValues" dxfId="38" priority="54"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B57">
-    <cfRule type="duplicateValues" dxfId="37" priority="53"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="36" priority="48"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="35" priority="47"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="34" priority="46"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="33" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B62">
-    <cfRule type="duplicateValues" dxfId="32" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="31" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="30" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="29" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="28" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="27" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="26" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="25" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="24" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="23" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="22" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="21" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B74">
-    <cfRule type="duplicateValues" dxfId="20" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75">
-    <cfRule type="duplicateValues" dxfId="19" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="18" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B77">
-    <cfRule type="duplicateValues" dxfId="17" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B78">
-    <cfRule type="duplicateValues" dxfId="16" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B79">
-    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B80">
-    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B81">
-    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B82">
-    <cfRule type="duplicateValues" dxfId="12" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B83">
-    <cfRule type="duplicateValues" dxfId="11" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B84">
-    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85">
-    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B86">
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87">
-    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B88">
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B89">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B90">
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B91">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A19:A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:A29">
+    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:A34">
+    <cfRule type="duplicateValues" dxfId="0" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="78"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39:A52">
+    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A58:A61">
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62:A65">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A66:A69">
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A71:A74">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A75:A78">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A79:A82">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A83:A86">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A87:A90">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A91:A94">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B21">
+    <cfRule type="duplicateValues" dxfId="0" priority="92"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="88"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="84"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="80"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B37">
+    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39:B41">
+    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42:B43">
+    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B45:B47">
+    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49:B51">
+    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B1 A5:B7">
+    <cfRule type="duplicateValues" dxfId="0" priority="106"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:B11">
+    <cfRule type="duplicateValues" dxfId="0" priority="98"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:B17">
+    <cfRule type="duplicateValues" dxfId="0" priority="96"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13980" windowHeight="11655"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
@@ -233,7 +233,7 @@
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,20 +266,6 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -428,25 +414,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -458,7 +432,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -468,8 +443,19 @@
       <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -533,12 +519,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -840,139 +820,139 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1023,21 +1003,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="51">
@@ -1487,10 +1452,10 @@
         <v>1700</v>
       </c>
       <c r="H5" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I5" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:9">
@@ -1516,10 +1481,10 @@
         <v>1700</v>
       </c>
       <c r="H6" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I6" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
@@ -1545,10 +1510,10 @@
         <v>1700</v>
       </c>
       <c r="H7" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I7" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:9">
@@ -1574,10 +1539,10 @@
         <v>1700</v>
       </c>
       <c r="H8" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I8" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:9">
@@ -1602,11 +1567,11 @@
       <c r="G9" s="12">
         <v>0</v>
       </c>
-      <c r="H9" s="12">
-        <v>15</v>
+      <c r="H9" s="8">
+        <v>1</v>
       </c>
       <c r="I9" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:9">
@@ -1631,11 +1596,11 @@
       <c r="G10" s="12">
         <v>0</v>
       </c>
-      <c r="H10" s="12">
-        <v>25</v>
+      <c r="H10" s="8">
+        <v>2</v>
       </c>
       <c r="I10" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:9">
@@ -1660,11 +1625,11 @@
       <c r="G11" s="12">
         <v>0</v>
       </c>
-      <c r="H11" s="12">
-        <v>60</v>
+      <c r="H11" s="8">
+        <v>6</v>
       </c>
       <c r="I11" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
@@ -1689,11 +1654,11 @@
       <c r="G12" s="12">
         <v>0</v>
       </c>
-      <c r="H12" s="12">
-        <v>300</v>
+      <c r="H12" s="8">
+        <v>30</v>
       </c>
       <c r="I12" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
@@ -1777,10 +1742,10 @@
         <v>1700</v>
       </c>
       <c r="H15" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I15" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:9">
@@ -1806,10 +1771,10 @@
         <v>1700</v>
       </c>
       <c r="H16" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I16" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
@@ -1835,10 +1800,10 @@
         <v>1700</v>
       </c>
       <c r="H17" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I17" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
@@ -1864,10 +1829,10 @@
         <v>1700</v>
       </c>
       <c r="H18" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I18" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
@@ -1893,10 +1858,10 @@
         <v>1700</v>
       </c>
       <c r="H19" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I19" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
@@ -1922,10 +1887,10 @@
         <v>1700</v>
       </c>
       <c r="H20" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I20" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:9">
@@ -1951,10 +1916,10 @@
         <v>1700</v>
       </c>
       <c r="H21" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I21" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
@@ -1980,10 +1945,10 @@
         <v>1700</v>
       </c>
       <c r="H22" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I22" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:9">
@@ -2009,10 +1974,10 @@
         <v>1700</v>
       </c>
       <c r="H23" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I23" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:9">
@@ -2038,10 +2003,10 @@
         <v>1700</v>
       </c>
       <c r="H24" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I24" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:9">
@@ -2067,10 +2032,10 @@
         <v>1700</v>
       </c>
       <c r="H25" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I25" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:9">
@@ -2096,10 +2061,10 @@
         <v>1700</v>
       </c>
       <c r="H26" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I26" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:9">
@@ -2125,10 +2090,10 @@
         <v>1700</v>
       </c>
       <c r="H27" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I27" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:9">
@@ -2154,10 +2119,10 @@
         <v>1700</v>
       </c>
       <c r="H28" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I28" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:9">
@@ -2183,10 +2148,10 @@
         <v>1700</v>
       </c>
       <c r="H29" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I29" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:9">
@@ -2212,10 +2177,10 @@
         <v>1700</v>
       </c>
       <c r="H30" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I30" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:9">
@@ -2241,10 +2206,10 @@
         <v>1700</v>
       </c>
       <c r="H31" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I31" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:9">
@@ -2270,10 +2235,10 @@
         <v>1700</v>
       </c>
       <c r="H32" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I32" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:9">
@@ -2299,10 +2264,10 @@
         <v>1700</v>
       </c>
       <c r="H33" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I33" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:9">
@@ -2328,10 +2293,10 @@
         <v>1700</v>
       </c>
       <c r="H34" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I34" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:9">
@@ -2357,10 +2322,10 @@
         <v>1700</v>
       </c>
       <c r="H35" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I35" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:9">
@@ -2386,10 +2351,10 @@
         <v>1700</v>
       </c>
       <c r="H36" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I36" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:9">
@@ -2415,10 +2380,10 @@
         <v>1700</v>
       </c>
       <c r="H37" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I37" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:9">
@@ -2444,10 +2409,10 @@
         <v>1700</v>
       </c>
       <c r="H38" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I38" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:9">
@@ -2473,10 +2438,10 @@
         <v>1700</v>
       </c>
       <c r="H39" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I39" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:9">
@@ -2502,10 +2467,10 @@
         <v>1700</v>
       </c>
       <c r="H40" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I40" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:9">
@@ -2531,10 +2496,10 @@
         <v>1700</v>
       </c>
       <c r="H41" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I41" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:9">
@@ -2560,10 +2525,10 @@
         <v>1700</v>
       </c>
       <c r="H42" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I42" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:9">
@@ -2647,10 +2612,10 @@
         <v>1700</v>
       </c>
       <c r="H45" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I45" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:9">
@@ -2676,10 +2641,10 @@
         <v>1700</v>
       </c>
       <c r="H46" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I46" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:9">
@@ -2705,10 +2670,10 @@
         <v>1700</v>
       </c>
       <c r="H47" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I47" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:9">
@@ -2734,10 +2699,10 @@
         <v>1700</v>
       </c>
       <c r="H48" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I48" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:9">
@@ -2763,10 +2728,10 @@
         <v>1700</v>
       </c>
       <c r="H49" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I49" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:9">
@@ -2792,10 +2757,10 @@
         <v>1700</v>
       </c>
       <c r="H50" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I50" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:9">
@@ -2821,10 +2786,10 @@
         <v>1700</v>
       </c>
       <c r="H51" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I51" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:9">
@@ -2850,10 +2815,10 @@
         <v>1700</v>
       </c>
       <c r="H52" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I52" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:9">
@@ -2908,10 +2873,10 @@
         <v>1700</v>
       </c>
       <c r="H54" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I54" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:9">
@@ -2937,10 +2902,10 @@
         <v>1700</v>
       </c>
       <c r="H55" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I55" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="1:9">
@@ -2966,10 +2931,10 @@
         <v>1700</v>
       </c>
       <c r="H56" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I56" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:9">
@@ -2995,10 +2960,10 @@
         <v>1700</v>
       </c>
       <c r="H57" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I57" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:9">
@@ -3024,10 +2989,10 @@
         <v>1700</v>
       </c>
       <c r="H58" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I58" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:9">
@@ -3053,10 +3018,10 @@
         <v>1700</v>
       </c>
       <c r="H59" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I59" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:9">
@@ -3082,10 +3047,10 @@
         <v>1700</v>
       </c>
       <c r="H60" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I60" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:9">
@@ -3111,10 +3076,10 @@
         <v>1700</v>
       </c>
       <c r="H61" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I61" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:9">
@@ -3140,10 +3105,10 @@
         <v>1700</v>
       </c>
       <c r="H62" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I62" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:9">
@@ -3169,10 +3134,10 @@
         <v>1700</v>
       </c>
       <c r="H63" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I63" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:9">
@@ -3198,10 +3163,10 @@
         <v>1700</v>
       </c>
       <c r="H64" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I64" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:9">
@@ -3227,10 +3192,10 @@
         <v>1700</v>
       </c>
       <c r="H65" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I65" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:9">
@@ -3256,10 +3221,10 @@
         <v>1700</v>
       </c>
       <c r="H66" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I66" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:9">
@@ -3285,10 +3250,10 @@
         <v>1700</v>
       </c>
       <c r="H67" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I67" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:9">
@@ -3314,10 +3279,10 @@
         <v>1700</v>
       </c>
       <c r="H68" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I68" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:9">
@@ -3343,10 +3308,10 @@
         <v>1700</v>
       </c>
       <c r="H69" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I69" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:9">
@@ -3401,10 +3366,10 @@
         <v>1700</v>
       </c>
       <c r="H71" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I71" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" ht="16.5" spans="1:9">
@@ -3430,10 +3395,10 @@
         <v>1700</v>
       </c>
       <c r="H72" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I72" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:9">
@@ -3459,10 +3424,10 @@
         <v>1700</v>
       </c>
       <c r="H73" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I73" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:9">
@@ -3488,10 +3453,10 @@
         <v>1700</v>
       </c>
       <c r="H74" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I74" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:9">
@@ -3517,10 +3482,10 @@
         <v>1700</v>
       </c>
       <c r="H75" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I75" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76" ht="16.5" spans="1:9">
@@ -3546,10 +3511,10 @@
         <v>1700</v>
       </c>
       <c r="H76" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I76" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="77" ht="16.5" spans="1:9">
@@ -3575,10 +3540,10 @@
         <v>1700</v>
       </c>
       <c r="H77" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I77" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:9">
@@ -3604,10 +3569,10 @@
         <v>1700</v>
       </c>
       <c r="H78" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I78" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="79" ht="16.5" spans="1:9">
@@ -3633,10 +3598,10 @@
         <v>1700</v>
       </c>
       <c r="H79" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I79" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80" ht="16.5" spans="1:9">
@@ -3662,10 +3627,10 @@
         <v>1700</v>
       </c>
       <c r="H80" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I80" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="81" ht="16.5" spans="1:9">
@@ -3691,10 +3656,10 @@
         <v>1700</v>
       </c>
       <c r="H81" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I81" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:9">
@@ -3720,10 +3685,10 @@
         <v>1700</v>
       </c>
       <c r="H82" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I82" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:9">
@@ -3749,10 +3714,10 @@
         <v>1700</v>
       </c>
       <c r="H83" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I83" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84" ht="16.5" spans="1:9">
@@ -3778,10 +3743,10 @@
         <v>1700</v>
       </c>
       <c r="H84" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I84" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="85" ht="16.5" spans="1:9">
@@ -3807,10 +3772,10 @@
         <v>1700</v>
       </c>
       <c r="H85" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I85" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="86" ht="16.5" spans="1:9">
@@ -3836,10 +3801,10 @@
         <v>1700</v>
       </c>
       <c r="H86" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I86" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="87" ht="16.5" spans="1:9">
@@ -3865,10 +3830,10 @@
         <v>1700</v>
       </c>
       <c r="H87" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I87" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="88" ht="16.5" spans="1:9">
@@ -3894,10 +3859,10 @@
         <v>1700</v>
       </c>
       <c r="H88" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I88" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="89" ht="16.5" spans="1:9">
@@ -3923,10 +3888,10 @@
         <v>1700</v>
       </c>
       <c r="H89" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I89" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:9">
@@ -3952,10 +3917,10 @@
         <v>1700</v>
       </c>
       <c r="H90" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I90" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:9">
@@ -3981,10 +3946,10 @@
         <v>1700</v>
       </c>
       <c r="H91" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I91" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:9">
@@ -4010,10 +3975,10 @@
         <v>1700</v>
       </c>
       <c r="H92" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I92" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:9">
@@ -4039,10 +4004,10 @@
         <v>1700</v>
       </c>
       <c r="H93" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I93" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:9">
@@ -4068,10 +4033,10 @@
         <v>1700</v>
       </c>
       <c r="H94" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I94" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="95" ht="16.5" spans="1:9">
@@ -4097,10 +4062,10 @@
         <v>1700</v>
       </c>
       <c r="H95" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I95" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="96" ht="16.5" spans="1:9">
@@ -4126,10 +4091,10 @@
         <v>1700</v>
       </c>
       <c r="H96" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I96" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="97" ht="16.5" spans="1:9">
@@ -4155,10 +4120,10 @@
         <v>1700</v>
       </c>
       <c r="H97" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I97" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="98" ht="16.5" spans="1:9">
@@ -4184,10 +4149,10 @@
         <v>1700</v>
       </c>
       <c r="H98" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I98" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="99" ht="16.5" spans="1:9">
@@ -4213,10 +4178,10 @@
         <v>1700</v>
       </c>
       <c r="H99" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I99" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="100" ht="16.5" spans="1:9">
@@ -4242,10 +4207,10 @@
         <v>1700</v>
       </c>
       <c r="H100" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I100" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="101" ht="16.5" spans="1:9">
@@ -4271,10 +4236,10 @@
         <v>1700</v>
       </c>
       <c r="H101" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I101" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="102" ht="16.5" spans="1:9">
@@ -4300,10 +4265,10 @@
         <v>1700</v>
       </c>
       <c r="H102" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I102" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="103" ht="16.5" spans="1:9">
@@ -4329,10 +4294,10 @@
         <v>1700</v>
       </c>
       <c r="H103" s="8">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I103" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="104" ht="16.5" spans="1:9">
@@ -4358,10 +4323,10 @@
         <v>1700</v>
       </c>
       <c r="H104" s="8">
-        <v>2500</v>
+        <v>2</v>
       </c>
       <c r="I104" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="105" ht="16.5" spans="1:9">
@@ -4387,10 +4352,10 @@
         <v>1700</v>
       </c>
       <c r="H105" s="8">
-        <v>6000</v>
+        <v>6</v>
       </c>
       <c r="I105" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="106" ht="16.5" spans="1:9">
@@ -4416,10 +4381,10 @@
         <v>1700</v>
       </c>
       <c r="H106" s="8">
-        <v>30000</v>
+        <v>30</v>
       </c>
       <c r="I106" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="107" ht="16.5" spans="1:9">
@@ -4445,10 +4410,10 @@
         <v>1700</v>
       </c>
       <c r="H107" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I107" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="108" ht="16.5" spans="1:9">
@@ -4474,10 +4439,10 @@
         <v>1700</v>
       </c>
       <c r="H108" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I108" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="109" ht="16.5" spans="1:9">
@@ -4503,10 +4468,10 @@
         <v>1700</v>
       </c>
       <c r="H109" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I109" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="110" ht="16.5" spans="1:9">
@@ -4532,10 +4497,10 @@
         <v>1700</v>
       </c>
       <c r="H110" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I110" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="111" ht="16.5" spans="1:9">
@@ -4561,10 +4526,10 @@
         <v>1700</v>
       </c>
       <c r="H111" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I111" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="112" ht="16.5" spans="1:9">
@@ -4590,10 +4555,10 @@
         <v>1700</v>
       </c>
       <c r="H112" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I112" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="113" ht="16.5" spans="1:9">
@@ -4619,10 +4584,10 @@
         <v>1700</v>
       </c>
       <c r="H113" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I113" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="114" ht="16.5" spans="1:9">
@@ -4648,10 +4613,10 @@
         <v>1700</v>
       </c>
       <c r="H114" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I114" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" ht="16.5" spans="1:9">
@@ -4735,10 +4700,10 @@
         <v>1700</v>
       </c>
       <c r="H117" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I117" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="118" ht="16.5" spans="1:9">
@@ -4764,10 +4729,10 @@
         <v>1700</v>
       </c>
       <c r="H118" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I118" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="119" ht="16.5" spans="1:9">
@@ -4793,10 +4758,10 @@
         <v>1700</v>
       </c>
       <c r="H119" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I119" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="120" ht="16.5" spans="1:9">
@@ -4822,10 +4787,10 @@
         <v>1700</v>
       </c>
       <c r="H120" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I120" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="121" ht="16.5" spans="1:9">
@@ -4858,31 +4823,31 @@
       </c>
     </row>
     <row r="122" ht="16.5" spans="1:9">
-      <c r="A122" s="19">
+      <c r="A122" s="18">
         <v>105502101</v>
       </c>
-      <c r="B122" s="20" t="s">
+      <c r="B122" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C122" s="21">
-        <v>0</v>
-      </c>
-      <c r="D122" s="22">
-        <v>0</v>
-      </c>
-      <c r="E122" s="22">
+      <c r="C122" s="9">
+        <v>0</v>
+      </c>
+      <c r="D122" s="10">
+        <v>0</v>
+      </c>
+      <c r="E122" s="10">
         <v>1000</v>
       </c>
-      <c r="F122" s="23" t="s">
+      <c r="F122" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G122" s="20">
-        <v>0</v>
-      </c>
-      <c r="H122" s="20">
+      <c r="G122" s="8">
+        <v>0</v>
+      </c>
+      <c r="H122" s="8">
         <v>1</v>
       </c>
-      <c r="I122" s="20">
+      <c r="I122" s="8">
         <v>1440</v>
       </c>
     </row>
@@ -4909,10 +4874,10 @@
         <v>1700</v>
       </c>
       <c r="H123" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I123" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="124" customFormat="1" ht="16.5" spans="1:9">
@@ -4938,10 +4903,10 @@
         <v>1700</v>
       </c>
       <c r="H124" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I124" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="125" customFormat="1" ht="16.5" spans="1:9">
@@ -4967,10 +4932,10 @@
         <v>1700</v>
       </c>
       <c r="H125" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I125" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="126" customFormat="1" ht="16.5" spans="1:9">
@@ -4996,10 +4961,10 @@
         <v>1700</v>
       </c>
       <c r="H126" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I126" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="127" customFormat="1" ht="16.5" spans="1:9">
@@ -5025,10 +4990,10 @@
         <v>1700</v>
       </c>
       <c r="H127" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I127" s="8">
-        <v>1440</v>
+        <v>60</v>
       </c>
     </row>
     <row r="128" customFormat="1" ht="16.5" spans="1:9">
@@ -5054,10 +5019,10 @@
         <v>1700</v>
       </c>
       <c r="H128" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I128" s="8">
-        <v>1440</v>
+        <v>120</v>
       </c>
     </row>
     <row r="129" customFormat="1" ht="16.5" spans="1:9">
@@ -5083,10 +5048,10 @@
         <v>1700</v>
       </c>
       <c r="H129" s="8">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I129" s="8">
-        <v>1440</v>
+        <v>300</v>
       </c>
     </row>
     <row r="130" customFormat="1" ht="16.5" spans="1:9">
@@ -5112,10 +5077,10 @@
         <v>1700</v>
       </c>
       <c r="H130" s="8">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I130" s="8">
-        <v>1440</v>
+        <v>1500</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="32">
   <si>
     <t>奖池ID</t>
   </si>
@@ -414,6 +414,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -421,9 +427,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -435,12 +441,6 @@
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1337,7 +1337,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I130"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -5083,6 +5083,122 @@
         <v>1500</v>
       </c>
     </row>
+    <row r="131" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A131" s="17">
+        <v>101900101</v>
+      </c>
+      <c r="B131" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C131" s="9">
+        <v>10</v>
+      </c>
+      <c r="D131" s="10">
+        <v>15</v>
+      </c>
+      <c r="E131" s="10">
+        <v>0</v>
+      </c>
+      <c r="F131" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G131" s="8">
+        <v>1700</v>
+      </c>
+      <c r="H131" s="8">
+        <v>1</v>
+      </c>
+      <c r="I131" s="8">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="132" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A132" s="17">
+        <v>101900102</v>
+      </c>
+      <c r="B132" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C132" s="9">
+        <v>20</v>
+      </c>
+      <c r="D132" s="10">
+        <v>25</v>
+      </c>
+      <c r="E132" s="10">
+        <v>0</v>
+      </c>
+      <c r="F132" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G132" s="8">
+        <v>1700</v>
+      </c>
+      <c r="H132" s="8">
+        <v>2</v>
+      </c>
+      <c r="I132" s="8">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="133" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A133" s="17">
+        <v>101900103</v>
+      </c>
+      <c r="B133" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C133" s="9">
+        <v>50</v>
+      </c>
+      <c r="D133" s="10">
+        <v>60</v>
+      </c>
+      <c r="E133" s="10">
+        <v>0</v>
+      </c>
+      <c r="F133" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G133" s="8">
+        <v>1700</v>
+      </c>
+      <c r="H133" s="8">
+        <v>6</v>
+      </c>
+      <c r="I133" s="8">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="134" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A134" s="17">
+        <v>101900104</v>
+      </c>
+      <c r="B134" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C134" s="9">
+        <v>250</v>
+      </c>
+      <c r="D134" s="10">
+        <v>300</v>
+      </c>
+      <c r="E134" s="10">
+        <v>0</v>
+      </c>
+      <c r="F134" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G134" s="8">
+        <v>1700</v>
+      </c>
+      <c r="H134" s="8">
+        <v>30</v>
+      </c>
+      <c r="I134" s="8">
+        <v>1500</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
     <cfRule type="duplicateValues" dxfId="0" priority="105"/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="32">
   <si>
     <t>奖池ID</t>
   </si>
@@ -414,12 +414,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -427,9 +421,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -441,6 +435,12 @@
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1337,7 +1337,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I134"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -5083,122 +5083,6 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="131" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A131" s="17">
-        <v>101900101</v>
-      </c>
-      <c r="B131" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C131" s="9">
-        <v>10</v>
-      </c>
-      <c r="D131" s="10">
-        <v>15</v>
-      </c>
-      <c r="E131" s="10">
-        <v>0</v>
-      </c>
-      <c r="F131" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G131" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H131" s="8">
-        <v>1</v>
-      </c>
-      <c r="I131" s="8">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="132" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A132" s="17">
-        <v>101900102</v>
-      </c>
-      <c r="B132" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C132" s="9">
-        <v>20</v>
-      </c>
-      <c r="D132" s="10">
-        <v>25</v>
-      </c>
-      <c r="E132" s="10">
-        <v>0</v>
-      </c>
-      <c r="F132" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G132" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H132" s="8">
-        <v>2</v>
-      </c>
-      <c r="I132" s="8">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="133" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A133" s="17">
-        <v>101900103</v>
-      </c>
-      <c r="B133" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C133" s="9">
-        <v>50</v>
-      </c>
-      <c r="D133" s="10">
-        <v>60</v>
-      </c>
-      <c r="E133" s="10">
-        <v>0</v>
-      </c>
-      <c r="F133" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G133" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H133" s="8">
-        <v>6</v>
-      </c>
-      <c r="I133" s="8">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="134" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A134" s="17">
-        <v>101900104</v>
-      </c>
-      <c r="B134" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C134" s="9">
-        <v>250</v>
-      </c>
-      <c r="D134" s="10">
-        <v>300</v>
-      </c>
-      <c r="E134" s="10">
-        <v>0</v>
-      </c>
-      <c r="F134" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G134" s="8">
-        <v>1700</v>
-      </c>
-      <c r="H134" s="8">
-        <v>30</v>
-      </c>
-      <c r="I134" s="8">
-        <v>1500</v>
-      </c>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
     <cfRule type="duplicateValues" dxfId="0" priority="105"/>

--- a/slots/resources/sample/Pool.xlsx
+++ b/slots/resources/sample/Pool.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17055"/>
   </bookViews>
   <sheets>
     <sheet name="Pool" sheetId="1" r:id="rId1"/>
@@ -118,12 +118,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="J1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+玩家中JACKPOT奖池后，根据玩家的下注金额，中奖金额上限为该所填倍数</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="34">
   <si>
     <t>奖池ID</t>
   </si>
@@ -147,6 +169,9 @@
   </si>
   <si>
     <t>间隔时间</t>
+  </si>
+  <si>
+    <t>真奖池奖金倍数上限</t>
   </si>
   <si>
     <t>int</t>
@@ -177,6 +202,9 @@
   </si>
   <si>
     <t>min</t>
+  </si>
+  <si>
+    <t>maxMultiple</t>
   </si>
   <si>
     <t>mini</t>
@@ -414,6 +442,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -427,17 +461,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -445,6 +468,11 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1337,7 +1365,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I134"/>
+  <dimension ref="A1:J134"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -1348,9 +1376,10 @@
     <col min="6" max="6" width="20.25" style="3" customWidth="1"/>
     <col min="7" max="7" width="18.875" customWidth="1"/>
     <col min="8" max="8" width="10.625" customWidth="1"/>
+    <col min="10" max="10" width="20.975" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:9">
+    <row r="1" ht="16.5" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1376,65 +1405,74 @@
       <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
       <c r="H2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>9</v>
+      </c>
+      <c r="J2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:9">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="8">
         <v>100100101</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" s="9">
         <v>10</v>
@@ -1446,7 +1484,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5" s="8">
         <v>1700</v>
@@ -1457,13 +1495,14 @@
       <c r="I5" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:9">
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="8">
         <v>100100102</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" s="9">
         <v>20</v>
@@ -1475,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G6" s="8">
         <v>1700</v>
@@ -1486,13 +1525,14 @@
       <c r="I6" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:9">
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="8">
         <v>100100103</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="9">
         <v>50</v>
@@ -1504,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G7" s="8">
         <v>1700</v>
@@ -1515,13 +1555,14 @@
       <c r="I7" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:9">
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="8">
         <v>100100104</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" s="9">
         <v>250</v>
@@ -1533,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G8" s="8">
         <v>1700</v>
@@ -1544,13 +1585,14 @@
       <c r="I8" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:9">
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="12">
         <v>100300101</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" s="13">
         <v>10</v>
@@ -1562,7 +1604,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G9" s="12">
         <v>0</v>
@@ -1573,13 +1615,14 @@
       <c r="I9" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:9">
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="12">
         <v>100300102</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C10" s="13">
         <v>20</v>
@@ -1591,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G10" s="12">
         <v>0</v>
@@ -1602,13 +1645,14 @@
       <c r="I10" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:9">
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="12">
         <v>100300103</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C11" s="13">
         <v>50</v>
@@ -1620,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G11" s="12">
         <v>0</v>
@@ -1631,13 +1675,14 @@
       <c r="I11" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:9">
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:10">
       <c r="A12" s="12">
         <v>100300104</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12" s="13">
         <v>250</v>
@@ -1649,7 +1694,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G12" s="12">
         <v>0</v>
@@ -1660,13 +1705,14 @@
       <c r="I12" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:9">
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:10">
       <c r="A13" s="8">
         <v>101200101</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13" s="9">
         <v>0</v>
@@ -1678,7 +1724,7 @@
         <v>1000</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G13" s="8">
         <v>0</v>
@@ -1689,13 +1735,16 @@
       <c r="I13" s="8">
         <v>1440</v>
       </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:9">
+      <c r="J13" s="8">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:10">
       <c r="A14" s="8">
         <v>101400101</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C14" s="9">
         <v>0</v>
@@ -1707,7 +1756,7 @@
         <v>1000</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G14" s="8">
         <v>0</v>
@@ -1718,13 +1767,16 @@
       <c r="I14" s="8">
         <v>1440</v>
       </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:9">
+      <c r="J14" s="8">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:10">
       <c r="A15" s="8">
         <v>102400101</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C15" s="9">
         <v>10</v>
@@ -1736,7 +1788,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G15" s="8">
         <v>1700</v>
@@ -1747,13 +1799,14 @@
       <c r="I15" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:9">
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:10">
       <c r="A16" s="8">
         <v>102400102</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C16" s="9">
         <v>20</v>
@@ -1765,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G16" s="8">
         <v>1700</v>
@@ -1776,13 +1829,14 @@
       <c r="I16" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:9">
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:10">
       <c r="A17" s="8">
         <v>102400103</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C17" s="9">
         <v>50</v>
@@ -1794,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G17" s="8">
         <v>1700</v>
@@ -1805,13 +1859,14 @@
       <c r="I17" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:9">
+      <c r="J17" s="8"/>
+    </row>
+    <row r="18" ht="16.5" spans="1:10">
       <c r="A18" s="8">
         <v>102400104</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C18" s="9">
         <v>250</v>
@@ -1823,7 +1878,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G18" s="8">
         <v>1700</v>
@@ -1834,13 +1889,14 @@
       <c r="I18" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:9">
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:10">
       <c r="A19" s="8">
         <v>101700101</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C19" s="9">
         <v>10</v>
@@ -1852,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G19" s="8">
         <v>1700</v>
@@ -1863,13 +1919,14 @@
       <c r="I19" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:9">
+      <c r="J19" s="8"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:10">
       <c r="A20" s="8">
         <v>101700102</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C20" s="9">
         <v>20</v>
@@ -1881,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G20" s="8">
         <v>1700</v>
@@ -1892,13 +1949,14 @@
       <c r="I20" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:9">
+      <c r="J20" s="8"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:10">
       <c r="A21" s="8">
         <v>101700103</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C21" s="9">
         <v>50</v>
@@ -1910,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G21" s="8">
         <v>1700</v>
@@ -1921,13 +1979,14 @@
       <c r="I21" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:9">
+      <c r="J21" s="8"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:10">
       <c r="A22" s="8">
         <v>101700104</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C22" s="9">
         <v>250</v>
@@ -1939,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G22" s="8">
         <v>1700</v>
@@ -1950,13 +2009,14 @@
       <c r="I22" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:9">
+      <c r="J22" s="8"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:10">
       <c r="A23" s="8">
         <v>102200101</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C23" s="9">
         <v>10</v>
@@ -1968,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G23" s="8">
         <v>1700</v>
@@ -1979,13 +2039,14 @@
       <c r="I23" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:9">
+      <c r="J23" s="8"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:10">
       <c r="A24" s="8">
         <v>102200102</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C24" s="9">
         <v>20</v>
@@ -1997,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G24" s="8">
         <v>1700</v>
@@ -2008,13 +2069,14 @@
       <c r="I24" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:9">
+      <c r="J24" s="8"/>
+    </row>
+    <row r="25" ht="16.5" spans="1:10">
       <c r="A25" s="8">
         <v>102200103</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C25" s="9">
         <v>50</v>
@@ -2026,7 +2088,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G25" s="8">
         <v>1700</v>
@@ -2037,13 +2099,14 @@
       <c r="I25" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="26" ht="16.5" spans="1:9">
+      <c r="J25" s="8"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:10">
       <c r="A26" s="8">
         <v>102200104</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C26" s="9">
         <v>250</v>
@@ -2055,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G26" s="8">
         <v>1700</v>
@@ -2066,13 +2129,14 @@
       <c r="I26" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="27" ht="16.5" spans="1:9">
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:10">
       <c r="A27" s="8">
         <v>102100101</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C27" s="9">
         <v>10</v>
@@ -2084,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G27" s="8">
         <v>1700</v>
@@ -2095,13 +2159,14 @@
       <c r="I27" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="28" ht="16.5" spans="1:9">
+      <c r="J27" s="8"/>
+    </row>
+    <row r="28" ht="16.5" spans="1:10">
       <c r="A28" s="8">
         <v>102100102</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C28" s="9">
         <v>20</v>
@@ -2113,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G28" s="8">
         <v>1700</v>
@@ -2124,13 +2189,14 @@
       <c r="I28" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="29" ht="16.5" spans="1:9">
+      <c r="J28" s="8"/>
+    </row>
+    <row r="29" ht="16.5" spans="1:10">
       <c r="A29" s="8">
         <v>102100103</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C29" s="9">
         <v>50</v>
@@ -2142,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G29" s="8">
         <v>1700</v>
@@ -2153,13 +2219,14 @@
       <c r="I29" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="30" ht="16.5" spans="1:9">
+      <c r="J29" s="8"/>
+    </row>
+    <row r="30" ht="16.5" spans="1:10">
       <c r="A30" s="8">
         <v>102100104</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C30" s="9">
         <v>250</v>
@@ -2171,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G30" s="8">
         <v>1700</v>
@@ -2182,13 +2249,14 @@
       <c r="I30" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="31" ht="16.5" spans="1:9">
+      <c r="J30" s="8"/>
+    </row>
+    <row r="31" ht="16.5" spans="1:10">
       <c r="A31" s="8">
         <v>101800101</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C31" s="9">
         <v>10</v>
@@ -2200,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G31" s="8">
         <v>1700</v>
@@ -2211,13 +2279,14 @@
       <c r="I31" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="32" ht="16.5" spans="1:9">
+      <c r="J31" s="8"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:10">
       <c r="A32" s="8">
         <v>101800102</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C32" s="9">
         <v>20</v>
@@ -2229,7 +2298,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G32" s="8">
         <v>1700</v>
@@ -2240,13 +2309,14 @@
       <c r="I32" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="33" ht="16.5" spans="1:9">
+      <c r="J32" s="8"/>
+    </row>
+    <row r="33" ht="16.5" spans="1:10">
       <c r="A33" s="8">
         <v>101800103</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C33" s="9">
         <v>50</v>
@@ -2258,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G33" s="8">
         <v>1700</v>
@@ -2269,13 +2339,14 @@
       <c r="I33" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="34" ht="16.5" spans="1:9">
+      <c r="J33" s="8"/>
+    </row>
+    <row r="34" ht="16.5" spans="1:10">
       <c r="A34" s="8">
         <v>101800104</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C34" s="9">
         <v>250</v>
@@ -2287,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G34" s="8">
         <v>1700</v>
@@ -2298,13 +2369,14 @@
       <c r="I34" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="35" ht="16.5" spans="1:9">
+      <c r="J34" s="8"/>
+    </row>
+    <row r="35" ht="16.5" spans="1:10">
       <c r="A35" s="8">
         <v>102500101</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C35" s="9">
         <v>10</v>
@@ -2316,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G35" s="8">
         <v>1700</v>
@@ -2327,13 +2399,14 @@
       <c r="I35" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="36" ht="16.5" spans="1:9">
+      <c r="J35" s="8"/>
+    </row>
+    <row r="36" ht="16.5" spans="1:10">
       <c r="A36" s="8">
         <v>102500102</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C36" s="9">
         <v>20</v>
@@ -2345,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G36" s="8">
         <v>1700</v>
@@ -2356,13 +2429,14 @@
       <c r="I36" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="37" ht="16.5" spans="1:9">
+      <c r="J36" s="8"/>
+    </row>
+    <row r="37" ht="16.5" spans="1:10">
       <c r="A37" s="8">
         <v>102500103</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C37" s="9">
         <v>50</v>
@@ -2374,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G37" s="8">
         <v>1700</v>
@@ -2385,13 +2459,14 @@
       <c r="I37" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="38" ht="16.5" spans="1:9">
+      <c r="J37" s="8"/>
+    </row>
+    <row r="38" ht="16.5" spans="1:10">
       <c r="A38" s="8">
         <v>102500104</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C38" s="9">
         <v>250</v>
@@ -2403,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G38" s="8">
         <v>1700</v>
@@ -2414,13 +2489,14 @@
       <c r="I38" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="39" ht="16.5" spans="1:9">
+      <c r="J38" s="8"/>
+    </row>
+    <row r="39" ht="16.5" spans="1:10">
       <c r="A39" s="8">
         <v>102300101</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C39" s="9">
         <v>10</v>
@@ -2432,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G39" s="8">
         <v>1700</v>
@@ -2443,13 +2519,14 @@
       <c r="I39" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="40" ht="16.5" spans="1:9">
+      <c r="J39" s="8"/>
+    </row>
+    <row r="40" ht="16.5" spans="1:10">
       <c r="A40" s="8">
         <v>102300102</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C40" s="9">
         <v>20</v>
@@ -2461,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G40" s="8">
         <v>1700</v>
@@ -2472,13 +2549,14 @@
       <c r="I40" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="41" ht="16.5" spans="1:9">
+      <c r="J40" s="8"/>
+    </row>
+    <row r="41" ht="16.5" spans="1:10">
       <c r="A41" s="8">
         <v>102300103</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C41" s="9">
         <v>50</v>
@@ -2490,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G41" s="8">
         <v>1700</v>
@@ -2501,13 +2579,14 @@
       <c r="I41" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="42" ht="16.5" spans="1:9">
+      <c r="J41" s="8"/>
+    </row>
+    <row r="42" ht="16.5" spans="1:10">
       <c r="A42" s="8">
         <v>102300104</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C42" s="9">
         <v>250</v>
@@ -2519,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G42" s="8">
         <v>1700</v>
@@ -2530,13 +2609,14 @@
       <c r="I42" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="43" ht="16.5" spans="1:9">
+      <c r="J42" s="8"/>
+    </row>
+    <row r="43" ht="16.5" spans="1:10">
       <c r="A43" s="8">
         <v>103400101</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C43" s="9">
         <v>0</v>
@@ -2548,7 +2628,7 @@
         <v>1000</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G43" s="8">
         <v>0</v>
@@ -2559,13 +2639,16 @@
       <c r="I43" s="8">
         <v>1440</v>
       </c>
-    </row>
-    <row r="44" ht="16.5" spans="1:9">
+      <c r="J43" s="8">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:10">
       <c r="A44" s="8">
         <v>103401101</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C44" s="9">
         <v>0</v>
@@ -2577,7 +2660,7 @@
         <v>1000</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G44" s="8">
         <v>0</v>
@@ -2588,13 +2671,16 @@
       <c r="I44" s="8">
         <v>1440</v>
       </c>
-    </row>
-    <row r="45" ht="16.5" spans="1:9">
+      <c r="J44" s="8">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="1:10">
       <c r="A45" s="8">
         <v>103500101</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C45" s="9">
         <v>10</v>
@@ -2606,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G45" s="8">
         <v>1700</v>
@@ -2617,13 +2703,14 @@
       <c r="I45" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="46" ht="16.5" spans="1:9">
+      <c r="J45" s="8"/>
+    </row>
+    <row r="46" ht="16.5" spans="1:10">
       <c r="A46" s="8">
         <v>103500102</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C46" s="9">
         <v>20</v>
@@ -2635,7 +2722,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G46" s="8">
         <v>1700</v>
@@ -2646,13 +2733,14 @@
       <c r="I46" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="47" ht="16.5" spans="1:9">
+      <c r="J46" s="8"/>
+    </row>
+    <row r="47" ht="16.5" spans="1:10">
       <c r="A47" s="8">
         <v>103500103</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C47" s="9">
         <v>50</v>
@@ -2664,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G47" s="8">
         <v>1700</v>
@@ -2675,13 +2763,14 @@
       <c r="I47" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="48" ht="16.5" spans="1:9">
+      <c r="J47" s="8"/>
+    </row>
+    <row r="48" ht="16.5" spans="1:10">
       <c r="A48" s="8">
         <v>103500104</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C48" s="9">
         <v>250</v>
@@ -2693,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G48" s="8">
         <v>1700</v>
@@ -2704,13 +2793,14 @@
       <c r="I48" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="49" ht="16.5" spans="1:9">
+      <c r="J48" s="8"/>
+    </row>
+    <row r="49" ht="16.5" spans="1:10">
       <c r="A49" s="8">
         <v>103501101</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C49" s="9">
         <v>10</v>
@@ -2722,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G49" s="8">
         <v>1700</v>
@@ -2733,13 +2823,14 @@
       <c r="I49" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="50" ht="16.5" spans="1:9">
+      <c r="J49" s="8"/>
+    </row>
+    <row r="50" ht="16.5" spans="1:10">
       <c r="A50" s="8">
         <v>103501102</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C50" s="9">
         <v>20</v>
@@ -2751,7 +2842,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G50" s="8">
         <v>1700</v>
@@ -2762,13 +2853,14 @@
       <c r="I50" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="51" ht="16.5" spans="1:9">
+      <c r="J50" s="8"/>
+    </row>
+    <row r="51" ht="16.5" spans="1:10">
       <c r="A51" s="8">
         <v>103501103</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C51" s="9">
         <v>50</v>
@@ -2780,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G51" s="8">
         <v>1700</v>
@@ -2791,13 +2883,14 @@
       <c r="I51" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="52" ht="16.5" spans="1:9">
+      <c r="J51" s="8"/>
+    </row>
+    <row r="52" ht="16.5" spans="1:10">
       <c r="A52" s="8">
         <v>103501104</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C52" s="9">
         <v>250</v>
@@ -2809,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G52" s="8">
         <v>1700</v>
@@ -2820,13 +2913,14 @@
       <c r="I52" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="53" ht="16.5" spans="1:9">
+      <c r="J52" s="8"/>
+    </row>
+    <row r="53" ht="16.5" spans="1:10">
       <c r="A53" s="8">
         <v>103600101</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C53" s="9">
         <v>0</v>
@@ -2838,7 +2932,7 @@
         <v>1000</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G53" s="8">
         <v>0</v>
@@ -2849,13 +2943,16 @@
       <c r="I53" s="8">
         <v>1440</v>
       </c>
-    </row>
-    <row r="54" ht="16.5" spans="1:9">
+      <c r="J53" s="8">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="1:10">
       <c r="A54" s="8">
         <v>102800101</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C54" s="9">
         <v>10</v>
@@ -2867,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G54" s="8">
         <v>1700</v>
@@ -2878,13 +2975,14 @@
       <c r="I54" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="55" ht="16.5" spans="1:9">
+      <c r="J54" s="8"/>
+    </row>
+    <row r="55" ht="16.5" spans="1:10">
       <c r="A55" s="8">
         <v>102800102</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C55" s="9">
         <v>20</v>
@@ -2896,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G55" s="8">
         <v>1700</v>
@@ -2907,13 +3005,14 @@
       <c r="I55" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="56" ht="16.5" spans="1:9">
+      <c r="J55" s="8"/>
+    </row>
+    <row r="56" ht="16.5" spans="1:10">
       <c r="A56" s="8">
         <v>102800103</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C56" s="9">
         <v>50</v>
@@ -2925,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G56" s="8">
         <v>1700</v>
@@ -2936,13 +3035,14 @@
       <c r="I56" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="57" ht="16.5" spans="1:9">
+      <c r="J56" s="8"/>
+    </row>
+    <row r="57" ht="16.5" spans="1:10">
       <c r="A57" s="8">
         <v>102800104</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C57" s="9">
         <v>250</v>
@@ -2954,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G57" s="8">
         <v>1700</v>
@@ -2965,13 +3065,14 @@
       <c r="I57" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="58" ht="16.5" spans="1:9">
+      <c r="J57" s="8"/>
+    </row>
+    <row r="58" ht="16.5" spans="1:10">
       <c r="A58" s="8">
         <v>102000101</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C58" s="9">
         <v>10</v>
@@ -2983,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G58" s="8">
         <v>1700</v>
@@ -2994,13 +3095,14 @@
       <c r="I58" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="59" ht="16.5" spans="1:9">
+      <c r="J58" s="8"/>
+    </row>
+    <row r="59" ht="16.5" spans="1:10">
       <c r="A59" s="8">
         <v>102000102</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C59" s="9">
         <v>20</v>
@@ -3012,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G59" s="8">
         <v>1700</v>
@@ -3023,13 +3125,14 @@
       <c r="I59" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="60" ht="16.5" spans="1:9">
+      <c r="J59" s="8"/>
+    </row>
+    <row r="60" ht="16.5" spans="1:10">
       <c r="A60" s="8">
         <v>102000103</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C60" s="9">
         <v>50</v>
@@ -3041,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G60" s="8">
         <v>1700</v>
@@ -3052,13 +3155,14 @@
       <c r="I60" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="61" ht="16.5" spans="1:9">
+      <c r="J60" s="8"/>
+    </row>
+    <row r="61" ht="16.5" spans="1:10">
       <c r="A61" s="8">
         <v>102000104</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C61" s="9">
         <v>250</v>
@@ -3070,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G61" s="8">
         <v>1700</v>
@@ -3081,13 +3185,14 @@
       <c r="I61" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="62" ht="16.5" spans="1:9">
+      <c r="J61" s="8"/>
+    </row>
+    <row r="62" ht="16.5" spans="1:10">
       <c r="A62" s="8">
         <v>103800101</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C62" s="9">
         <v>10</v>
@@ -3099,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G62" s="8">
         <v>1700</v>
@@ -3110,13 +3215,14 @@
       <c r="I62" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="63" ht="16.5" spans="1:9">
+      <c r="J62" s="8"/>
+    </row>
+    <row r="63" ht="16.5" spans="1:10">
       <c r="A63" s="8">
         <v>103800102</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C63" s="9">
         <v>20</v>
@@ -3128,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G63" s="8">
         <v>1700</v>
@@ -3139,13 +3245,14 @@
       <c r="I63" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="64" ht="16.5" spans="1:9">
+      <c r="J63" s="8"/>
+    </row>
+    <row r="64" ht="16.5" spans="1:10">
       <c r="A64" s="8">
         <v>103800103</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C64" s="9">
         <v>50</v>
@@ -3157,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G64" s="8">
         <v>1700</v>
@@ -3168,13 +3275,14 @@
       <c r="I64" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="65" ht="16.5" spans="1:9">
+      <c r="J64" s="8"/>
+    </row>
+    <row r="65" ht="16.5" spans="1:10">
       <c r="A65" s="8">
         <v>103800104</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C65" s="9">
         <v>250</v>
@@ -3186,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G65" s="8">
         <v>1700</v>
@@ -3197,13 +3305,14 @@
       <c r="I65" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="66" ht="16.5" spans="1:9">
+      <c r="J65" s="8"/>
+    </row>
+    <row r="66" ht="16.5" spans="1:10">
       <c r="A66" s="8">
         <v>102700101</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C66" s="9">
         <v>10</v>
@@ -3215,7 +3324,7 @@
         <v>0</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G66" s="8">
         <v>1700</v>
@@ -3226,13 +3335,14 @@
       <c r="I66" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="67" ht="16.5" spans="1:9">
+      <c r="J66" s="8"/>
+    </row>
+    <row r="67" ht="16.5" spans="1:10">
       <c r="A67" s="8">
         <v>102700102</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C67" s="9">
         <v>20</v>
@@ -3244,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G67" s="8">
         <v>1700</v>
@@ -3255,13 +3365,14 @@
       <c r="I67" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="68" ht="16.5" spans="1:9">
+      <c r="J67" s="8"/>
+    </row>
+    <row r="68" ht="16.5" spans="1:10">
       <c r="A68" s="8">
         <v>102700103</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C68" s="9">
         <v>50</v>
@@ -3273,7 +3384,7 @@
         <v>0</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G68" s="8">
         <v>1700</v>
@@ -3284,13 +3395,14 @@
       <c r="I68" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="69" ht="16.5" spans="1:9">
+      <c r="J68" s="8"/>
+    </row>
+    <row r="69" ht="16.5" spans="1:10">
       <c r="A69" s="8">
         <v>102700104</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C69" s="9">
         <v>250</v>
@@ -3302,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G69" s="8">
         <v>1700</v>
@@ -3313,13 +3425,14 @@
       <c r="I69" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="70" ht="16.5" spans="1:9">
+      <c r="J69" s="8"/>
+    </row>
+    <row r="70" ht="16.5" spans="1:10">
       <c r="A70" s="8">
         <v>103700101</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C70" s="9">
         <v>0</v>
@@ -3331,7 +3444,7 @@
         <v>1000</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G70" s="8">
         <v>0</v>
@@ -3342,13 +3455,16 @@
       <c r="I70" s="8">
         <v>1440</v>
       </c>
-    </row>
-    <row r="71" ht="16.5" spans="1:9">
+      <c r="J70" s="8">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="71" ht="16.5" spans="1:10">
       <c r="A71" s="8">
         <v>103100101</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C71" s="9">
         <v>10</v>
@@ -3360,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G71" s="8">
         <v>1700</v>
@@ -3371,13 +3487,14 @@
       <c r="I71" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="72" ht="16.5" spans="1:9">
+      <c r="J71" s="8"/>
+    </row>
+    <row r="72" ht="16.5" spans="1:10">
       <c r="A72" s="8">
         <v>103100102</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C72" s="9">
         <v>20</v>
@@ -3389,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G72" s="8">
         <v>1700</v>
@@ -3400,13 +3517,14 @@
       <c r="I72" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="73" ht="16.5" spans="1:9">
+      <c r="J72" s="8"/>
+    </row>
+    <row r="73" ht="16.5" spans="1:10">
       <c r="A73" s="8">
         <v>103100103</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C73" s="9">
         <v>50</v>
@@ -3418,7 +3536,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G73" s="8">
         <v>1700</v>
@@ -3429,13 +3547,14 @@
       <c r="I73" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="74" ht="16.5" spans="1:9">
+      <c r="J73" s="8"/>
+    </row>
+    <row r="74" ht="16.5" spans="1:10">
       <c r="A74" s="8">
         <v>103100104</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C74" s="9">
         <v>250</v>
@@ -3447,7 +3566,7 @@
         <v>0</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G74" s="8">
         <v>1700</v>
@@ -3458,13 +3577,14 @@
       <c r="I74" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="75" ht="16.5" spans="1:9">
+      <c r="J74" s="8"/>
+    </row>
+    <row r="75" ht="16.5" spans="1:10">
       <c r="A75" s="8">
         <v>104000101</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C75" s="9">
         <v>10</v>
@@ -3476,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G75" s="8">
         <v>1700</v>
@@ -3487,13 +3607,14 @@
       <c r="I75" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="76" ht="16.5" spans="1:9">
+      <c r="J75" s="8"/>
+    </row>
+    <row r="76" ht="16.5" spans="1:10">
       <c r="A76" s="8">
         <v>104000102</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C76" s="9">
         <v>20</v>
@@ -3505,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G76" s="8">
         <v>1700</v>
@@ -3516,13 +3637,14 @@
       <c r="I76" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="77" ht="16.5" spans="1:9">
+      <c r="J76" s="8"/>
+    </row>
+    <row r="77" ht="16.5" spans="1:10">
       <c r="A77" s="8">
         <v>104000103</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C77" s="9">
         <v>50</v>
@@ -3534,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G77" s="8">
         <v>1700</v>
@@ -3545,13 +3667,14 @@
       <c r="I77" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="78" ht="16.5" spans="1:9">
+      <c r="J77" s="8"/>
+    </row>
+    <row r="78" ht="16.5" spans="1:10">
       <c r="A78" s="8">
         <v>104000104</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C78" s="9">
         <v>250</v>
@@ -3563,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G78" s="8">
         <v>1700</v>
@@ -3574,13 +3697,14 @@
       <c r="I78" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="79" ht="16.5" spans="1:9">
+      <c r="J78" s="8"/>
+    </row>
+    <row r="79" ht="16.5" spans="1:10">
       <c r="A79" s="8">
         <v>103900101</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C79" s="9">
         <v>10</v>
@@ -3592,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G79" s="8">
         <v>1700</v>
@@ -3603,13 +3727,14 @@
       <c r="I79" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="80" ht="16.5" spans="1:9">
+      <c r="J79" s="8"/>
+    </row>
+    <row r="80" ht="16.5" spans="1:10">
       <c r="A80" s="8">
         <v>103900102</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C80" s="9">
         <v>20</v>
@@ -3621,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G80" s="8">
         <v>1700</v>
@@ -3632,13 +3757,14 @@
       <c r="I80" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="81" ht="16.5" spans="1:9">
+      <c r="J80" s="8"/>
+    </row>
+    <row r="81" ht="16.5" spans="1:10">
       <c r="A81" s="8">
         <v>103900103</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C81" s="9">
         <v>50</v>
@@ -3650,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G81" s="8">
         <v>1700</v>
@@ -3661,13 +3787,14 @@
       <c r="I81" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="82" ht="16.5" spans="1:9">
+      <c r="J81" s="8"/>
+    </row>
+    <row r="82" ht="16.5" spans="1:10">
       <c r="A82" s="8">
         <v>103900104</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C82" s="9">
         <v>250</v>
@@ -3679,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G82" s="8">
         <v>1700</v>
@@ -3690,13 +3817,14 @@
       <c r="I82" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="83" ht="16.5" spans="1:9">
+      <c r="J82" s="8"/>
+    </row>
+    <row r="83" ht="16.5" spans="1:10">
       <c r="A83" s="8">
         <v>101600101</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C83" s="9">
         <v>10</v>
@@ -3708,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G83" s="8">
         <v>1700</v>
@@ -3719,13 +3847,14 @@
       <c r="I83" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="84" ht="16.5" spans="1:9">
+      <c r="J83" s="8"/>
+    </row>
+    <row r="84" ht="16.5" spans="1:10">
       <c r="A84" s="8">
         <v>101600102</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C84" s="9">
         <v>20</v>
@@ -3737,7 +3866,7 @@
         <v>0</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G84" s="8">
         <v>1700</v>
@@ -3748,13 +3877,14 @@
       <c r="I84" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="85" ht="16.5" spans="1:9">
+      <c r="J84" s="8"/>
+    </row>
+    <row r="85" ht="16.5" spans="1:10">
       <c r="A85" s="8">
         <v>101600103</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C85" s="9">
         <v>50</v>
@@ -3766,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G85" s="8">
         <v>1700</v>
@@ -3777,13 +3907,14 @@
       <c r="I85" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="86" ht="16.5" spans="1:9">
+      <c r="J85" s="8"/>
+    </row>
+    <row r="86" ht="16.5" spans="1:10">
       <c r="A86" s="8">
         <v>101600104</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C86" s="9">
         <v>250</v>
@@ -3795,7 +3926,7 @@
         <v>0</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G86" s="8">
         <v>1700</v>
@@ -3806,13 +3937,14 @@
       <c r="I86" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="87" ht="16.5" spans="1:9">
+      <c r="J86" s="8"/>
+    </row>
+    <row r="87" ht="16.5" spans="1:10">
       <c r="A87" s="8">
         <v>101500101</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C87" s="9">
         <v>10</v>
@@ -3824,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G87" s="8">
         <v>1700</v>
@@ -3835,13 +3967,14 @@
       <c r="I87" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="88" ht="16.5" spans="1:9">
+      <c r="J87" s="8"/>
+    </row>
+    <row r="88" ht="16.5" spans="1:10">
       <c r="A88" s="8">
         <v>101500102</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C88" s="9">
         <v>20</v>
@@ -3853,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G88" s="8">
         <v>1700</v>
@@ -3864,13 +3997,14 @@
       <c r="I88" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="89" ht="16.5" spans="1:9">
+      <c r="J88" s="8"/>
+    </row>
+    <row r="89" ht="16.5" spans="1:10">
       <c r="A89" s="8">
         <v>101500103</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C89" s="9">
         <v>50</v>
@@ -3882,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G89" s="8">
         <v>1700</v>
@@ -3893,13 +4027,14 @@
       <c r="I89" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="90" ht="16.5" spans="1:9">
+      <c r="J89" s="8"/>
+    </row>
+    <row r="90" ht="16.5" spans="1:10">
       <c r="A90" s="8">
         <v>101500104</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C90" s="9">
         <v>250</v>
@@ -3911,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G90" s="8">
         <v>1700</v>
@@ -3922,13 +4057,14 @@
       <c r="I90" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="91" ht="16.5" spans="1:9">
+      <c r="J90" s="8"/>
+    </row>
+    <row r="91" ht="16.5" spans="1:10">
       <c r="A91" s="8">
         <v>102600101</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C91" s="9">
         <v>10</v>
@@ -3940,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G91" s="8">
         <v>1700</v>
@@ -3951,13 +4087,14 @@
       <c r="I91" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="92" ht="16.5" spans="1:9">
+      <c r="J91" s="8"/>
+    </row>
+    <row r="92" ht="16.5" spans="1:10">
       <c r="A92" s="8">
         <v>102600102</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C92" s="9">
         <v>20</v>
@@ -3969,7 +4106,7 @@
         <v>0</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G92" s="8">
         <v>1700</v>
@@ -3980,13 +4117,14 @@
       <c r="I92" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="93" ht="16.5" spans="1:9">
+      <c r="J92" s="8"/>
+    </row>
+    <row r="93" ht="16.5" spans="1:10">
       <c r="A93" s="8">
         <v>102600103</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C93" s="9">
         <v>50</v>
@@ -3998,7 +4136,7 @@
         <v>0</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G93" s="8">
         <v>1700</v>
@@ -4009,13 +4147,14 @@
       <c r="I93" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="94" ht="16.5" spans="1:9">
+      <c r="J93" s="8"/>
+    </row>
+    <row r="94" ht="16.5" spans="1:10">
       <c r="A94" s="8">
         <v>102600104</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C94" s="9">
         <v>250</v>
@@ -4027,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G94" s="8">
         <v>1700</v>
@@ -4038,13 +4177,14 @@
       <c r="I94" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="95" ht="16.5" spans="1:9">
+      <c r="J94" s="8"/>
+    </row>
+    <row r="95" ht="16.5" spans="1:10">
       <c r="A95" s="8">
         <v>105000101</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C95" s="9">
         <v>10</v>
@@ -4056,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G95" s="8">
         <v>1700</v>
@@ -4067,13 +4207,14 @@
       <c r="I95" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="96" ht="16.5" spans="1:9">
+      <c r="J95" s="8"/>
+    </row>
+    <row r="96" ht="16.5" spans="1:10">
       <c r="A96" s="8">
         <v>105000102</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C96" s="9">
         <v>20</v>
@@ -4085,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G96" s="8">
         <v>1700</v>
@@ -4096,13 +4237,14 @@
       <c r="I96" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="97" ht="16.5" spans="1:9">
+      <c r="J96" s="8"/>
+    </row>
+    <row r="97" ht="16.5" spans="1:10">
       <c r="A97" s="8">
         <v>105000103</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C97" s="9">
         <v>50</v>
@@ -4114,7 +4256,7 @@
         <v>0</v>
       </c>
       <c r="F97" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G97" s="8">
         <v>1700</v>
@@ -4125,13 +4267,14 @@
       <c r="I97" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="98" ht="16.5" spans="1:9">
+      <c r="J97" s="8"/>
+    </row>
+    <row r="98" ht="16.5" spans="1:10">
       <c r="A98" s="8">
         <v>105000104</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C98" s="9">
         <v>250</v>
@@ -4143,7 +4286,7 @@
         <v>0</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G98" s="8">
         <v>1700</v>
@@ -4154,13 +4297,14 @@
       <c r="I98" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="99" ht="16.5" spans="1:9">
+      <c r="J98" s="8"/>
+    </row>
+    <row r="99" ht="16.5" spans="1:10">
       <c r="A99" s="8">
         <v>105100101</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C99" s="9">
         <v>10</v>
@@ -4172,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G99" s="8">
         <v>1700</v>
@@ -4183,13 +4327,14 @@
       <c r="I99" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="100" ht="16.5" spans="1:9">
+      <c r="J99" s="8"/>
+    </row>
+    <row r="100" ht="16.5" spans="1:10">
       <c r="A100" s="8">
         <v>105100102</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C100" s="9">
         <v>20</v>
@@ -4201,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="F100" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G100" s="8">
         <v>1700</v>
@@ -4212,13 +4357,14 @@
       <c r="I100" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="101" ht="16.5" spans="1:9">
+      <c r="J100" s="8"/>
+    </row>
+    <row r="101" ht="16.5" spans="1:10">
       <c r="A101" s="8">
         <v>105100103</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C101" s="9">
         <v>50</v>
@@ -4230,7 +4376,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G101" s="8">
         <v>1700</v>
@@ -4241,13 +4387,14 @@
       <c r="I101" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="102" ht="16.5" spans="1:9">
+      <c r="J101" s="8"/>
+    </row>
+    <row r="102" ht="16.5" spans="1:10">
       <c r="A102" s="8">
         <v>105100104</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C102" s="9">
         <v>250</v>
@@ -4259,7 +4406,7 @@
         <v>0</v>
       </c>
       <c r="F102" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G102" s="8">
         <v>1700</v>
@@ -4270,13 +4417,14 @@
       <c r="I102" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="103" ht="16.5" spans="1:9">
+      <c r="J102" s="8"/>
+    </row>
+    <row r="103" ht="16.5" spans="1:10">
       <c r="A103" s="8">
         <v>105400101</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C103" s="9">
         <v>10</v>
@@ -4288,7 +4436,7 @@
         <v>0</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G103" s="8">
         <v>1700</v>
@@ -4299,13 +4447,14 @@
       <c r="I103" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="104" ht="16.5" spans="1:9">
+      <c r="J103" s="8"/>
+    </row>
+    <row r="104" ht="16.5" spans="1:10">
       <c r="A104" s="8">
         <v>105400102</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C104" s="9">
         <v>20</v>
@@ -4317,7 +4466,7 @@
         <v>0</v>
       </c>
       <c r="F104" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G104" s="8">
         <v>1700</v>
@@ -4328,13 +4477,14 @@
       <c r="I104" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="105" ht="16.5" spans="1:9">
+      <c r="J104" s="8"/>
+    </row>
+    <row r="105" ht="16.5" spans="1:10">
       <c r="A105" s="8">
         <v>105400103</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C105" s="9">
         <v>50</v>
@@ -4346,7 +4496,7 @@
         <v>0</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G105" s="8">
         <v>1700</v>
@@ -4357,13 +4507,14 @@
       <c r="I105" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="106" ht="16.5" spans="1:9">
+      <c r="J105" s="8"/>
+    </row>
+    <row r="106" ht="16.5" spans="1:10">
       <c r="A106" s="8">
         <v>105400104</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C106" s="9">
         <v>250</v>
@@ -4375,7 +4526,7 @@
         <v>0</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G106" s="8">
         <v>1700</v>
@@ -4386,13 +4537,14 @@
       <c r="I106" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="107" ht="16.5" spans="1:9">
+      <c r="J106" s="8"/>
+    </row>
+    <row r="107" ht="16.5" spans="1:10">
       <c r="A107" s="8">
         <v>100800101</v>
       </c>
       <c r="B107" s="16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C107" s="9">
         <v>10</v>
@@ -4404,7 +4556,7 @@
         <v>0</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G107" s="8">
         <v>1700</v>
@@ -4415,13 +4567,14 @@
       <c r="I107" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="108" ht="16.5" spans="1:9">
+      <c r="J107" s="8"/>
+    </row>
+    <row r="108" ht="16.5" spans="1:10">
       <c r="A108" s="8">
         <v>100800102</v>
       </c>
       <c r="B108" s="16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C108" s="9">
         <v>20</v>
@@ -4433,7 +4586,7 @@
         <v>0</v>
       </c>
       <c r="F108" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G108" s="8">
         <v>1700</v>
@@ -4444,13 +4597,14 @@
       <c r="I108" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="109" ht="16.5" spans="1:9">
+      <c r="J108" s="8"/>
+    </row>
+    <row r="109" ht="16.5" spans="1:10">
       <c r="A109" s="17">
         <v>100800103</v>
       </c>
       <c r="B109" s="16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C109" s="9">
         <v>50</v>
@@ -4462,7 +4616,7 @@
         <v>0</v>
       </c>
       <c r="F109" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G109" s="8">
         <v>1700</v>
@@ -4473,13 +4627,14 @@
       <c r="I109" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="110" ht="16.5" spans="1:9">
+      <c r="J109" s="8"/>
+    </row>
+    <row r="110" ht="16.5" spans="1:10">
       <c r="A110" s="17">
         <v>100800104</v>
       </c>
       <c r="B110" s="16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C110" s="9">
         <v>250</v>
@@ -4491,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G110" s="8">
         <v>1700</v>
@@ -4502,13 +4657,14 @@
       <c r="I110" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="111" ht="16.5" spans="1:9">
+      <c r="J110" s="8"/>
+    </row>
+    <row r="111" ht="16.5" spans="1:10">
       <c r="A111" s="17">
         <v>105700101</v>
       </c>
       <c r="B111" s="16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C111" s="9">
         <v>10</v>
@@ -4520,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G111" s="8">
         <v>1700</v>
@@ -4531,13 +4687,14 @@
       <c r="I111" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="112" ht="16.5" spans="1:9">
+      <c r="J111" s="8"/>
+    </row>
+    <row r="112" ht="16.5" spans="1:10">
       <c r="A112" s="17">
         <v>105700102</v>
       </c>
       <c r="B112" s="16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C112" s="9">
         <v>20</v>
@@ -4549,7 +4706,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G112" s="8">
         <v>1700</v>
@@ -4560,13 +4717,14 @@
       <c r="I112" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="113" ht="16.5" spans="1:9">
+      <c r="J112" s="8"/>
+    </row>
+    <row r="113" ht="16.5" spans="1:10">
       <c r="A113" s="17">
         <v>105700103</v>
       </c>
       <c r="B113" s="16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C113" s="9">
         <v>50</v>
@@ -4578,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G113" s="8">
         <v>1700</v>
@@ -4589,13 +4747,14 @@
       <c r="I113" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="114" ht="16.5" spans="1:9">
+      <c r="J113" s="8"/>
+    </row>
+    <row r="114" ht="16.5" spans="1:10">
       <c r="A114" s="17">
         <v>105700104</v>
       </c>
       <c r="B114" s="16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C114" s="9">
         <v>250</v>
@@ -4607,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G114" s="8">
         <v>1700</v>
@@ -4618,13 +4777,14 @@
       <c r="I114" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="115" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="J114" s="8"/>
+    </row>
+    <row r="115" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A115" s="17">
         <v>105800101</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C115" s="9">
         <v>0</v>
@@ -4636,7 +4796,7 @@
         <v>5000</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G115" s="8">
         <v>0</v>
@@ -4647,13 +4807,16 @@
       <c r="I115" s="8">
         <v>1440</v>
       </c>
-    </row>
-    <row r="116" s="2" customFormat="1" ht="16.5" spans="1:9">
+      <c r="J115" s="8">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="116" s="2" customFormat="1" ht="16.5" spans="1:10">
       <c r="A116" s="18">
         <v>105500101</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C116" s="9">
         <v>0</v>
@@ -4665,7 +4828,7 @@
         <v>1000</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G116" s="8">
         <v>0</v>
@@ -4676,13 +4839,16 @@
       <c r="I116" s="8">
         <v>1440</v>
       </c>
-    </row>
-    <row r="117" ht="16.5" spans="1:9">
+      <c r="J116" s="8">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="117" ht="16.5" spans="1:10">
       <c r="A117" s="17">
         <v>104800101</v>
       </c>
       <c r="B117" s="16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C117" s="9">
         <v>10</v>
@@ -4694,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G117" s="8">
         <v>1700</v>
@@ -4705,13 +4871,14 @@
       <c r="I117" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="118" ht="16.5" spans="1:9">
+      <c r="J117" s="8"/>
+    </row>
+    <row r="118" ht="16.5" spans="1:10">
       <c r="A118" s="17">
         <v>104800102</v>
       </c>
       <c r="B118" s="16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C118" s="9">
         <v>20</v>
@@ -4723,7 +4890,7 @@
         <v>0</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G118" s="8">
         <v>1700</v>
@@ -4734,13 +4901,14 @@
       <c r="I118" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="119" ht="16.5" spans="1:9">
+      <c r="J118" s="8"/>
+    </row>
+    <row r="119" ht="16.5" spans="1:10">
       <c r="A119" s="17">
         <v>104800103</v>
       </c>
       <c r="B119" s="16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C119" s="9">
         <v>50</v>
@@ -4752,7 +4920,7 @@
         <v>0</v>
       </c>
       <c r="F119" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G119" s="8">
         <v>1700</v>
@@ -4763,13 +4931,14 @@
       <c r="I119" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="120" ht="16.5" spans="1:9">
+      <c r="J119" s="8"/>
+    </row>
+    <row r="120" ht="16.5" spans="1:10">
       <c r="A120" s="17">
         <v>104800104</v>
       </c>
       <c r="B120" s="16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C120" s="9">
         <v>250</v>
@@ -4781,7 +4950,7 @@
         <v>0</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G120" s="8">
         <v>1700</v>
@@ -4792,13 +4961,14 @@
       <c r="I120" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="121" ht="16.5" spans="1:9">
+      <c r="J120" s="8"/>
+    </row>
+    <row r="121" ht="16.5" spans="1:10">
       <c r="A121" s="18">
         <v>105501101</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C121" s="9">
         <v>0</v>
@@ -4810,7 +4980,7 @@
         <v>1000</v>
       </c>
       <c r="F121" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G121" s="8">
         <v>0</v>
@@ -4821,13 +4991,16 @@
       <c r="I121" s="8">
         <v>1440</v>
       </c>
-    </row>
-    <row r="122" ht="16.5" spans="1:9">
+      <c r="J121" s="8">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="122" ht="16.5" spans="1:10">
       <c r="A122" s="18">
         <v>105502101</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C122" s="9">
         <v>0</v>
@@ -4839,7 +5012,7 @@
         <v>1000</v>
       </c>
       <c r="F122" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G122" s="8">
         <v>0</v>
@@ -4850,13 +5023,16 @@
       <c r="I122" s="8">
         <v>1440</v>
       </c>
-    </row>
-    <row r="123" customFormat="1" ht="16.5" spans="1:9">
+      <c r="J122" s="8">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="123" customFormat="1" ht="16.5" spans="1:10">
       <c r="A123" s="17">
         <v>104100101</v>
       </c>
       <c r="B123" s="16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C123" s="9">
         <v>10</v>
@@ -4868,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G123" s="8">
         <v>1700</v>
@@ -4879,13 +5055,14 @@
       <c r="I123" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="124" customFormat="1" ht="16.5" spans="1:9">
+      <c r="J123" s="8"/>
+    </row>
+    <row r="124" customFormat="1" ht="16.5" spans="1:10">
       <c r="A124" s="17">
         <v>104100102</v>
       </c>
       <c r="B124" s="16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C124" s="9">
         <v>20</v>
@@ -4897,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G124" s="8">
         <v>1700</v>
@@ -4908,13 +5085,14 @@
       <c r="I124" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="125" customFormat="1" ht="16.5" spans="1:9">
+      <c r="J124" s="8"/>
+    </row>
+    <row r="125" customFormat="1" ht="16.5" spans="1:10">
       <c r="A125" s="17">
         <v>104100103</v>
       </c>
       <c r="B125" s="16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C125" s="9">
         <v>50</v>
@@ -4926,7 +5104,7 @@
         <v>0</v>
       </c>
       <c r="F125" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G125" s="8">
         <v>1700</v>
@@ -4937,13 +5115,14 @@
       <c r="I125" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="126" customFormat="1" ht="16.5" spans="1:9">
+      <c r="J125" s="8"/>
+    </row>
+    <row r="126" customFormat="1" ht="16.5" spans="1:10">
       <c r="A126" s="17">
         <v>104100104</v>
       </c>
       <c r="B126" s="16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C126" s="9">
         <v>250</v>
@@ -4955,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G126" s="8">
         <v>1700</v>
@@ -4966,13 +5145,14 @@
       <c r="I126" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="127" customFormat="1" ht="16.5" spans="1:9">
+      <c r="J126" s="8"/>
+    </row>
+    <row r="127" customFormat="1" ht="16.5" spans="1:10">
       <c r="A127" s="17">
         <v>104200101</v>
       </c>
       <c r="B127" s="16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C127" s="9">
         <v>10</v>
@@ -4984,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G127" s="8">
         <v>1700</v>
@@ -4995,13 +5175,14 @@
       <c r="I127" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="128" customFormat="1" ht="16.5" spans="1:9">
+      <c r="J127" s="8"/>
+    </row>
+    <row r="128" customFormat="1" ht="16.5" spans="1:10">
       <c r="A128" s="17">
         <v>104200102</v>
       </c>
       <c r="B128" s="16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C128" s="9">
         <v>20</v>
@@ -5013,7 +5194,7 @@
         <v>0</v>
       </c>
       <c r="F128" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G128" s="8">
         <v>1700</v>
@@ -5024,13 +5205,14 @@
       <c r="I128" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="129" customFormat="1" ht="16.5" spans="1:9">
+      <c r="J128" s="8"/>
+    </row>
+    <row r="129" customFormat="1" ht="16.5" spans="1:10">
       <c r="A129" s="17">
         <v>104200103</v>
       </c>
       <c r="B129" s="16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C129" s="9">
         <v>50</v>
@@ -5042,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="F129" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G129" s="8">
         <v>1700</v>
@@ -5053,13 +5235,14 @@
       <c r="I129" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="130" customFormat="1" ht="16.5" spans="1:9">
+      <c r="J129" s="8"/>
+    </row>
+    <row r="130" customFormat="1" ht="16.5" spans="1:10">
       <c r="A130" s="17">
         <v>104200104</v>
       </c>
       <c r="B130" s="16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C130" s="9">
         <v>250</v>
@@ -5071,7 +5254,7 @@
         <v>0</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G130" s="8">
         <v>1700</v>
@@ -5082,13 +5265,14 @@
       <c r="I130" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="131" customFormat="1" ht="16.5" spans="1:9">
+      <c r="J130" s="8"/>
+    </row>
+    <row r="131" customFormat="1" ht="16.5" spans="1:10">
       <c r="A131" s="17">
         <v>101900101</v>
       </c>
       <c r="B131" s="16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C131" s="9">
         <v>10</v>
@@ -5100,7 +5284,7 @@
         <v>0</v>
       </c>
       <c r="F131" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G131" s="8">
         <v>1700</v>
@@ -5111,13 +5295,14 @@
       <c r="I131" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="132" customFormat="1" ht="16.5" spans="1:9">
+      <c r="J131" s="8"/>
+    </row>
+    <row r="132" customFormat="1" ht="16.5" spans="1:10">
       <c r="A132" s="17">
         <v>101900102</v>
       </c>
       <c r="B132" s="16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C132" s="9">
         <v>20</v>
@@ -5129,7 +5314,7 @@
         <v>0</v>
       </c>
       <c r="F132" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G132" s="8">
         <v>1700</v>
@@ -5140,13 +5325,14 @@
       <c r="I132" s="8">
         <v>120</v>
       </c>
-    </row>
-    <row r="133" customFormat="1" ht="16.5" spans="1:9">
+      <c r="J132" s="8"/>
+    </row>
+    <row r="133" customFormat="1" ht="16.5" spans="1:10">
       <c r="A133" s="17">
         <v>101900103</v>
       </c>
       <c r="B133" s="16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C133" s="9">
         <v>50</v>
@@ -5158,7 +5344,7 @@
         <v>0</v>
       </c>
       <c r="F133" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G133" s="8">
         <v>1700</v>
@@ -5169,13 +5355,14 @@
       <c r="I133" s="8">
         <v>300</v>
       </c>
-    </row>
-    <row r="134" customFormat="1" ht="16.5" spans="1:9">
+      <c r="J133" s="8"/>
+    </row>
+    <row r="134" customFormat="1" ht="16.5" spans="1:10">
       <c r="A134" s="17">
         <v>101900104</v>
       </c>
       <c r="B134" s="16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C134" s="9">
         <v>250</v>
@@ -5187,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G134" s="8">
         <v>1700</v>
@@ -5198,6 +5385,7 @@
       <c r="I134" s="8">
         <v>1500</v>
       </c>
+      <c r="J134" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A8:B8">
